--- a/artifacts/consolidado_valores_unicos_mapeo.xlsx
+++ b/artifacts/consolidado_valores_unicos_mapeo.xlsx
@@ -418,7 +418,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A416"/>
+  <dimension ref="A1:A474"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3330,6 +3330,412 @@
       <c r="A416" t="inlineStr">
         <is>
           <t>Total Población</t>
+        </is>
+      </c>
+    </row>
+    <row r="417">
+      <c r="A417" t="inlineStr">
+        <is>
+          <t>Plan Talento</t>
+        </is>
+      </c>
+    </row>
+    <row r="418">
+      <c r="A418" t="inlineStr">
+        <is>
+          <t>Certificación SGA sede los Colores</t>
+        </is>
+      </c>
+    </row>
+    <row r="419">
+      <c r="A419" t="inlineStr">
+        <is>
+          <t>Diseño del Modelo de Experiencia Institucional - Fase 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="420">
+      <c r="A420" t="inlineStr">
+        <is>
+          <t>Innovación curricular - Fase I</t>
+        </is>
+      </c>
+    </row>
+    <row r="421">
+      <c r="A421" t="inlineStr">
+        <is>
+          <t>Nuevo POLISIGS</t>
+        </is>
+      </c>
+    </row>
+    <row r="422">
+      <c r="A422" t="inlineStr">
+        <is>
+          <t>Equidad de Genero</t>
+        </is>
+      </c>
+    </row>
+    <row r="423">
+      <c r="A423" t="inlineStr">
+        <is>
+          <t>Portal Universitario</t>
+        </is>
+      </c>
+    </row>
+    <row r="424">
+      <c r="A424" t="inlineStr">
+        <is>
+          <t>Data Lake Institucional</t>
+        </is>
+      </c>
+    </row>
+    <row r="425">
+      <c r="A425" t="inlineStr">
+        <is>
+          <t>Catalogo de recursos virtuales</t>
+        </is>
+      </c>
+    </row>
+    <row r="426">
+      <c r="A426" t="inlineStr">
+        <is>
+          <t>Monarca - Ecosistema Banner</t>
+        </is>
+      </c>
+    </row>
+    <row r="427">
+      <c r="A427" t="inlineStr">
+        <is>
+          <t>Acreditación Institucional Sede Bogotá - Fase II - Condiciones iniciales</t>
+        </is>
+      </c>
+    </row>
+    <row r="428">
+      <c r="A428" t="inlineStr">
+        <is>
+          <t>Creación del Instituto de Educación para el trabajo y el desarrollo humano - Stand By</t>
+        </is>
+      </c>
+    </row>
+    <row r="429">
+      <c r="A429" t="inlineStr">
+        <is>
+          <t>Creación del colegio de educación media virtual  - Stand By</t>
+        </is>
+      </c>
+    </row>
+    <row r="430">
+      <c r="A430" t="inlineStr">
+        <is>
+          <t>Diseño del Modelo de Experiencia Institucional - Fase 2</t>
+        </is>
+      </c>
+    </row>
+    <row r="431">
+      <c r="A431" t="inlineStr">
+        <is>
+          <t>Prime</t>
+        </is>
+      </c>
+    </row>
+    <row r="432">
+      <c r="A432" t="inlineStr">
+        <is>
+          <t>Pricing</t>
+        </is>
+      </c>
+    </row>
+    <row r="433">
+      <c r="A433" t="inlineStr">
+        <is>
+          <t>Acreditación Institucional Sede Bogotá - Fase I</t>
+        </is>
+      </c>
+    </row>
+    <row r="434">
+      <c r="A434" t="inlineStr">
+        <is>
+          <t>Experiencia Institucional - Fase 3- Hub de experiencia</t>
+        </is>
+      </c>
+    </row>
+    <row r="435">
+      <c r="A435" t="inlineStr">
+        <is>
+          <t>Centro de Idiomas Fase I</t>
+        </is>
+      </c>
+    </row>
+    <row r="436">
+      <c r="A436" t="inlineStr">
+        <is>
+          <t>CREA Centro de Recursos y Experiencias para el aprendizaje - Fase de Adecuación</t>
+        </is>
+      </c>
+    </row>
+    <row r="437">
+      <c r="A437" t="inlineStr">
+        <is>
+          <t>Migración modelo de transporte rotativo</t>
+        </is>
+      </c>
+    </row>
+    <row r="438">
+      <c r="A438" t="inlineStr">
+        <is>
+          <t>Ecosistema E3</t>
+        </is>
+      </c>
+    </row>
+    <row r="439">
+      <c r="A439" t="inlineStr">
+        <is>
+          <t>Habilidades Poderosas</t>
+        </is>
+      </c>
+    </row>
+    <row r="440">
+      <c r="A440" t="inlineStr">
+        <is>
+          <t>Ser PRO</t>
+        </is>
+      </c>
+    </row>
+    <row r="441">
+      <c r="A441" t="inlineStr">
+        <is>
+          <t>Cultura de una buena docencia</t>
+        </is>
+      </c>
+    </row>
+    <row r="442">
+      <c r="A442" t="inlineStr">
+        <is>
+          <t>Proyecto Silver</t>
+        </is>
+      </c>
+    </row>
+    <row r="443">
+      <c r="A443" t="inlineStr">
+        <is>
+          <t>Hubspot CRM</t>
+        </is>
+      </c>
+    </row>
+    <row r="444">
+      <c r="A444" t="inlineStr">
+        <is>
+          <t>Centro de Idiomas Fase I - Stand By</t>
+        </is>
+      </c>
+    </row>
+    <row r="445">
+      <c r="A445" t="inlineStr">
+        <is>
+          <t>Acreditación Institucional  Fase III - Etapa de evaluación externa</t>
+        </is>
+      </c>
+    </row>
+    <row r="446">
+      <c r="A446" t="inlineStr">
+        <is>
+          <t>Fortalecimiento de la investigacion, la innovación y la creación</t>
+        </is>
+      </c>
+    </row>
+    <row r="447">
+      <c r="A447" t="inlineStr">
+        <is>
+          <t>Fortalecimiento de planta docente</t>
+        </is>
+      </c>
+    </row>
+    <row r="448">
+      <c r="A448" t="inlineStr">
+        <is>
+          <t>Plataforma de gestión de la información curricular Fase I</t>
+        </is>
+      </c>
+    </row>
+    <row r="449">
+      <c r="A449" t="inlineStr">
+        <is>
+          <t>Actualización de TRD y creación del Plan de gestión documental</t>
+        </is>
+      </c>
+    </row>
+    <row r="450">
+      <c r="A450" t="inlineStr">
+        <is>
+          <t>ADN Poli</t>
+        </is>
+      </c>
+    </row>
+    <row r="451">
+      <c r="A451" t="inlineStr">
+        <is>
+          <t>Gobierno de datos</t>
+        </is>
+      </c>
+    </row>
+    <row r="452">
+      <c r="A452" t="inlineStr">
+        <is>
+          <t>Herramientas de Gestión para el mejoramiento continuo</t>
+        </is>
+      </c>
+    </row>
+    <row r="453">
+      <c r="A453" t="inlineStr">
+        <is>
+          <t>Proyectos Ilumno Self Service S&amp;P</t>
+        </is>
+      </c>
+    </row>
+    <row r="454">
+      <c r="A454" t="inlineStr">
+        <is>
+          <t>Reingenieria de aplicaciones</t>
+        </is>
+      </c>
+    </row>
+    <row r="455">
+      <c r="A455" t="inlineStr">
+        <is>
+          <t>SOPHIA Sistema de optimización y programación horaria institucional</t>
+        </is>
+      </c>
+    </row>
+    <row r="456">
+      <c r="A456" t="inlineStr">
+        <is>
+          <t>Proyecto de permanencia institucional</t>
+        </is>
+      </c>
+    </row>
+    <row r="457">
+      <c r="A457" t="inlineStr">
+        <is>
+          <t>Centro Gastronómico</t>
+        </is>
+      </c>
+    </row>
+    <row r="458">
+      <c r="A458" t="inlineStr">
+        <is>
+          <t>Modelo de seguimiento al graduado</t>
+        </is>
+      </c>
+    </row>
+    <row r="459">
+      <c r="A459" t="inlineStr">
+        <is>
+          <t>Creación del colegio de educación media virtual</t>
+        </is>
+      </c>
+    </row>
+    <row r="460">
+      <c r="A460" t="inlineStr">
+        <is>
+          <t>Estudiantes Posgrado</t>
+        </is>
+      </c>
+    </row>
+    <row r="461">
+      <c r="A461" t="inlineStr">
+        <is>
+          <t>Lanzamiento de nuevos programas presencial</t>
+        </is>
+      </c>
+    </row>
+    <row r="462">
+      <c r="A462" t="inlineStr">
+        <is>
+          <t>Lanzamiento de nuevos programas virtual</t>
+        </is>
+      </c>
+    </row>
+    <row r="463">
+      <c r="A463" t="inlineStr">
+        <is>
+          <t>Estudiantes Presencial</t>
+        </is>
+      </c>
+    </row>
+    <row r="464">
+      <c r="A464" t="inlineStr">
+        <is>
+          <t>Estudiantes Virtual</t>
+        </is>
+      </c>
+    </row>
+    <row r="465">
+      <c r="A465" t="inlineStr">
+        <is>
+          <t>Estudiantes Pregrado</t>
+        </is>
+      </c>
+    </row>
+    <row r="466">
+      <c r="A466" t="inlineStr">
+        <is>
+          <t>B2B</t>
+        </is>
+      </c>
+    </row>
+    <row r="467">
+      <c r="A467" t="inlineStr">
+        <is>
+          <t>Total Ingresos B2G</t>
+        </is>
+      </c>
+    </row>
+    <row r="468">
+      <c r="A468" t="inlineStr">
+        <is>
+          <t>Otros ingresos (Cursos -Opciones de grado)</t>
+        </is>
+      </c>
+    </row>
+    <row r="469">
+      <c r="A469" t="inlineStr">
+        <is>
+          <t>Número de programas registrados en la SED</t>
+        </is>
+      </c>
+    </row>
+    <row r="470">
+      <c r="A470" t="inlineStr">
+        <is>
+          <t>Total Ingresos B2B</t>
+        </is>
+      </c>
+    </row>
+    <row r="471">
+      <c r="A471" t="inlineStr">
+        <is>
+          <t>Titulación Autogestionada</t>
+        </is>
+      </c>
+    </row>
+    <row r="472">
+      <c r="A472" t="inlineStr">
+        <is>
+          <t>Número de visitas a Pagina Web</t>
+        </is>
+      </c>
+    </row>
+    <row r="473">
+      <c r="A473" t="inlineStr">
+        <is>
+          <t>Fortalecimiento del proceso de visibilidad nacional e internacional</t>
+        </is>
+      </c>
+    </row>
+    <row r="474">
+      <c r="A474" t="inlineStr">
+        <is>
+          <t>Sistema de medición de resultados de aprendizaje</t>
         </is>
       </c>
     </row>
@@ -3344,7 +3750,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A144"/>
+  <dimension ref="A1:A185"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4065,6 +4471,211 @@
     <row r="144">
       <c r="A144" t="n">
         <v>55756</v>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="n">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="n">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="n">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="n">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="n">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="n">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="n">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="n">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="n">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="n">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="n">
+        <v>4638</v>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="n">
+        <v>14271</v>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="n">
+        <v>85163</v>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="n">
+        <v>94796</v>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="n">
+        <v>15442</v>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="n">
+        <v>88422</v>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="n">
+        <v>98342</v>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="n">
+        <v>5522</v>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="n">
+        <v>1357.778</v>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="n">
+        <v>7082.002999999999</v>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="n">
+        <v>5657.94</v>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="n">
+        <v>16080</v>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="n">
+        <v>87439</v>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="n">
+        <v>97371</v>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="n">
+        <v>6148</v>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="n">
+        <v>3424.207396199999</v>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="n">
+        <v>7711.1257611</v>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="n">
+        <v>4372.159942699999</v>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="n">
+        <v>16671</v>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="n">
+        <v>92409</v>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="n">
+        <v>98816</v>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="n">
+        <v>7856</v>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="n">
+        <v>9719.024715200001</v>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="n">
+        <v>27575.2022841</v>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="n">
+        <v>19404.5414027</v>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="n">
+        <v>894.406923</v>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="n">
+        <v>5335.242827</v>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="n">
+        <v>7446.830696</v>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="n">
+        <v>3805.662141</v>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="n">
+        <v>5568.779319</v>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="n">
+        <v>4042.632396</v>
       </c>
     </row>
   </sheetData>
@@ -4078,7 +4689,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A412"/>
+  <dimension ref="A1:A475"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6139,6 +6750,321 @@
     <row r="412">
       <c r="A412" t="n">
         <v>1.018849989238826</v>
+      </c>
+    </row>
+    <row r="413">
+      <c r="A413" t="n">
+        <v>1.045454545454545</v>
+      </c>
+    </row>
+    <row r="414">
+      <c r="A414" t="n">
+        <v>0.9487179487179487</v>
+      </c>
+    </row>
+    <row r="415">
+      <c r="A415" t="n">
+        <v>1.245614035087719</v>
+      </c>
+    </row>
+    <row r="416">
+      <c r="A416" t="n">
+        <v>0.9693877551020408</v>
+      </c>
+    </row>
+    <row r="417">
+      <c r="A417" t="n">
+        <v>0.8571428571428571</v>
+      </c>
+    </row>
+    <row r="418">
+      <c r="A418" t="n">
+        <v>0.8271604938271605</v>
+      </c>
+    </row>
+    <row r="419">
+      <c r="A419" t="n">
+        <v>0.7846153846153846</v>
+      </c>
+    </row>
+    <row r="420">
+      <c r="A420" t="n">
+        <v>0.7368421052631579</v>
+      </c>
+    </row>
+    <row r="421">
+      <c r="A421" t="n">
+        <v>0.8780487804878049</v>
+      </c>
+    </row>
+    <row r="422">
+      <c r="A422" t="n">
+        <v>0.9795918367346939</v>
+      </c>
+    </row>
+    <row r="423">
+      <c r="A423" t="n">
+        <v>0.9578947368421052</v>
+      </c>
+    </row>
+    <row r="424">
+      <c r="A424" t="n">
+        <v>0.987012987012987</v>
+      </c>
+    </row>
+    <row r="425">
+      <c r="A425" t="n">
+        <v>0.9890109890109891</v>
+      </c>
+    </row>
+    <row r="426">
+      <c r="A426" t="n">
+        <v>0.9333333333333333</v>
+      </c>
+    </row>
+    <row r="427">
+      <c r="A427" t="n">
+        <v>0.9574468085106383</v>
+      </c>
+    </row>
+    <row r="428">
+      <c r="A428" t="n">
+        <v>0.75</v>
+      </c>
+    </row>
+    <row r="429">
+      <c r="A429" t="n">
+        <v>0.95</v>
+      </c>
+    </row>
+    <row r="430">
+      <c r="A430" t="n">
+        <v>0.9690721649484536</v>
+      </c>
+    </row>
+    <row r="431">
+      <c r="A431" t="n">
+        <v>0.9666666666666667</v>
+      </c>
+    </row>
+    <row r="432">
+      <c r="A432" t="n">
+        <v>0.9444444444444444</v>
+      </c>
+    </row>
+    <row r="433">
+      <c r="A433" t="n">
+        <v>1.022988505747126</v>
+      </c>
+    </row>
+    <row r="434">
+      <c r="A434" t="n">
+        <v>1.079775765416128</v>
+      </c>
+    </row>
+    <row r="435">
+      <c r="A435" t="n">
+        <v>1.005952380952381</v>
+      </c>
+    </row>
+    <row r="436">
+      <c r="A436" t="n">
+        <v>0.85</v>
+      </c>
+    </row>
+    <row r="437">
+      <c r="A437" t="n">
+        <v>1.064396328218065</v>
+      </c>
+    </row>
+    <row r="438">
+      <c r="A438" t="n">
+        <v>1.010509258715639</v>
+      </c>
+    </row>
+    <row r="439">
+      <c r="A439" t="n">
+        <v>1.015232710240938</v>
+      </c>
+    </row>
+    <row r="440">
+      <c r="A440" t="n">
+        <v>0.3333333333333333</v>
+      </c>
+    </row>
+    <row r="441">
+      <c r="A441" t="n">
+        <v>1.1619203453558</v>
+      </c>
+    </row>
+    <row r="442">
+      <c r="A442" t="n">
+        <v>1.118003314607796</v>
+      </c>
+    </row>
+    <row r="443">
+      <c r="A443" t="n">
+        <v>1.208621541501976</v>
+      </c>
+    </row>
+    <row r="444">
+      <c r="A444" t="n">
+        <v>1.056998556998558</v>
+      </c>
+    </row>
+    <row r="445">
+      <c r="A445" t="n">
+        <v>0.9552316725312512</v>
+      </c>
+    </row>
+    <row r="446">
+      <c r="A446" t="n">
+        <v>1.036300505050505</v>
+      </c>
+    </row>
+    <row r="447">
+      <c r="A447" t="n">
+        <v>1.106355915619741</v>
+      </c>
+    </row>
+    <row r="448">
+      <c r="A448" t="n">
+        <v>1.185138416707139</v>
+      </c>
+    </row>
+    <row r="449">
+      <c r="A449" t="n">
+        <v>1.137221284644484</v>
+      </c>
+    </row>
+    <row r="450">
+      <c r="A450" t="n">
+        <v>1.024892585160029</v>
+      </c>
+    </row>
+    <row r="451">
+      <c r="A451" t="n">
+        <v>1.016525718803029</v>
+      </c>
+    </row>
+    <row r="452">
+      <c r="A452" t="n">
+        <v>0.9719594594594601</v>
+      </c>
+    </row>
+    <row r="453">
+      <c r="A453" t="n">
+        <v>1.186974789915966</v>
+      </c>
+    </row>
+    <row r="454">
+      <c r="A454" t="n">
+        <v>1.034710529724129</v>
+      </c>
+    </row>
+    <row r="455">
+      <c r="A455" t="n">
+        <v>0.9824364977041913</v>
+      </c>
+    </row>
+    <row r="456">
+      <c r="A456" t="n">
+        <v>0.9815745052978382</v>
+      </c>
+    </row>
+    <row r="457">
+      <c r="A457" t="n">
+        <v>1.144150670047084</v>
+      </c>
+    </row>
+    <row r="458">
+      <c r="A458" t="n">
+        <v>0.7155844462825693</v>
+      </c>
+    </row>
+    <row r="459">
+      <c r="A459" t="n">
+        <v>1.134867568548177</v>
+      </c>
+    </row>
+    <row r="460">
+      <c r="A460" t="n">
+        <v>0.6</v>
+      </c>
+    </row>
+    <row r="461">
+      <c r="A461" t="n">
+        <v>1.031654228855721</v>
+      </c>
+    </row>
+    <row r="462">
+      <c r="A462" t="n">
+        <v>1.006427337915575</v>
+      </c>
+    </row>
+    <row r="463">
+      <c r="A463" t="n">
+        <v>1.000616199895246</v>
+      </c>
+    </row>
+    <row r="464">
+      <c r="A464" t="n">
+        <v>1.163142485361093</v>
+      </c>
+    </row>
+    <row r="465">
+      <c r="A465" t="n">
+        <v>0.540866034119128</v>
+      </c>
+    </row>
+    <row r="466">
+      <c r="A466" t="n">
+        <v>1.001390572938703</v>
+      </c>
+    </row>
+    <row r="467">
+      <c r="A467" t="n">
+        <v>1.048407414072341</v>
+      </c>
+    </row>
+    <row r="468">
+      <c r="A468" t="n">
+        <v>1.037063489486955</v>
+      </c>
+    </row>
+    <row r="469">
+      <c r="A469" t="n">
+        <v>1.055203610751295</v>
+      </c>
+    </row>
+    <row r="470">
+      <c r="A470" t="n">
+        <v>1.150840122199593</v>
+      </c>
+    </row>
+    <row r="471">
+      <c r="A471" t="n">
+        <v>0.9736370882936671</v>
+      </c>
+    </row>
+    <row r="472">
+      <c r="A472" t="n">
+        <v>0.9599977199362209</v>
+      </c>
+    </row>
+    <row r="473">
+      <c r="A473" t="n">
+        <v>1.003634003927944</v>
+      </c>
+    </row>
+    <row r="474">
+      <c r="A474" t="n">
+        <v>1.148488633438699</v>
+      </c>
+    </row>
+    <row r="475">
+      <c r="A475" t="n">
+        <v>1.162780659367179</v>
       </c>
     </row>
   </sheetData>
@@ -6152,7 +7078,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A574"/>
+  <dimension ref="A1:A642"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9023,6 +9949,346 @@
     <row r="574">
       <c r="A574" t="n">
         <v>1.018849989238826</v>
+      </c>
+    </row>
+    <row r="575">
+      <c r="A575" t="n">
+        <v>1.045454545454545</v>
+      </c>
+    </row>
+    <row r="576">
+      <c r="A576" t="n">
+        <v>0.9487179487179487</v>
+      </c>
+    </row>
+    <row r="577">
+      <c r="A577" t="n">
+        <v>1.245614035087719</v>
+      </c>
+    </row>
+    <row r="578">
+      <c r="A578" t="n">
+        <v>0.9693877551020408</v>
+      </c>
+    </row>
+    <row r="579">
+      <c r="A579" t="n">
+        <v>0.8571428571428571</v>
+      </c>
+    </row>
+    <row r="580">
+      <c r="A580" t="n">
+        <v>0.8271604938271605</v>
+      </c>
+    </row>
+    <row r="581">
+      <c r="A581" t="n">
+        <v>0.7846153846153846</v>
+      </c>
+    </row>
+    <row r="582">
+      <c r="A582" t="n">
+        <v>0.7368421052631579</v>
+      </c>
+    </row>
+    <row r="583">
+      <c r="A583" t="n">
+        <v>0.8780487804878049</v>
+      </c>
+    </row>
+    <row r="584">
+      <c r="A584" t="n">
+        <v>0.9795918367346939</v>
+      </c>
+    </row>
+    <row r="585">
+      <c r="A585" t="n">
+        <v>0.9578947368421052</v>
+      </c>
+    </row>
+    <row r="586">
+      <c r="A586" t="n">
+        <v>0.987012987012987</v>
+      </c>
+    </row>
+    <row r="587">
+      <c r="A587" t="n">
+        <v>0.9890109890109891</v>
+      </c>
+    </row>
+    <row r="588">
+      <c r="A588" t="n">
+        <v>0.9333333333333333</v>
+      </c>
+    </row>
+    <row r="589">
+      <c r="A589" t="n">
+        <v>0.9574468085106383</v>
+      </c>
+    </row>
+    <row r="590">
+      <c r="A590" t="n">
+        <v>0.75</v>
+      </c>
+    </row>
+    <row r="591">
+      <c r="A591" t="n">
+        <v>0.95</v>
+      </c>
+    </row>
+    <row r="592">
+      <c r="A592" t="n">
+        <v>0.9690721649484536</v>
+      </c>
+    </row>
+    <row r="593">
+      <c r="A593" t="n">
+        <v>0.9666666666666667</v>
+      </c>
+    </row>
+    <row r="594">
+      <c r="A594" t="n">
+        <v>0.9444444444444444</v>
+      </c>
+    </row>
+    <row r="595">
+      <c r="A595" t="n">
+        <v>1.022988505747126</v>
+      </c>
+    </row>
+    <row r="596">
+      <c r="A596" t="n">
+        <v>1.079775765416128</v>
+      </c>
+    </row>
+    <row r="597">
+      <c r="A597" t="n">
+        <v>1.005952380952381</v>
+      </c>
+    </row>
+    <row r="598">
+      <c r="A598" t="n">
+        <v>0.85</v>
+      </c>
+    </row>
+    <row r="599">
+      <c r="A599" t="n">
+        <v>1.064396328218065</v>
+      </c>
+    </row>
+    <row r="600">
+      <c r="A600" t="n">
+        <v>1.010509258715639</v>
+      </c>
+    </row>
+    <row r="601">
+      <c r="A601" t="n">
+        <v>1.015232710240938</v>
+      </c>
+    </row>
+    <row r="602">
+      <c r="A602" t="n">
+        <v>0.3333333333333333</v>
+      </c>
+    </row>
+    <row r="603">
+      <c r="A603" t="n">
+        <v>1.1619203453558</v>
+      </c>
+    </row>
+    <row r="604">
+      <c r="A604" t="n">
+        <v>1.118003314607796</v>
+      </c>
+    </row>
+    <row r="605">
+      <c r="A605" t="n">
+        <v>1.208621541501976</v>
+      </c>
+    </row>
+    <row r="606">
+      <c r="A606" t="n">
+        <v>1.056998556998558</v>
+      </c>
+    </row>
+    <row r="607">
+      <c r="A607" t="n">
+        <v>0.9552316725312512</v>
+      </c>
+    </row>
+    <row r="608">
+      <c r="A608" t="n">
+        <v>1.036300505050505</v>
+      </c>
+    </row>
+    <row r="609">
+      <c r="A609" t="n">
+        <v>1.106355915619741</v>
+      </c>
+    </row>
+    <row r="610">
+      <c r="A610" t="n">
+        <v>1.185138416707139</v>
+      </c>
+    </row>
+    <row r="611">
+      <c r="A611" t="n">
+        <v>1.137221284644484</v>
+      </c>
+    </row>
+    <row r="612">
+      <c r="A612" t="n">
+        <v>1.024892585160029</v>
+      </c>
+    </row>
+    <row r="613">
+      <c r="A613" t="n">
+        <v>1.016525718803029</v>
+      </c>
+    </row>
+    <row r="614">
+      <c r="A614" t="n">
+        <v>0.9719594594594601</v>
+      </c>
+    </row>
+    <row r="615">
+      <c r="A615" t="n">
+        <v>1.186974789915966</v>
+      </c>
+    </row>
+    <row r="616">
+      <c r="A616" t="n">
+        <v>1.034710529724129</v>
+      </c>
+    </row>
+    <row r="617">
+      <c r="A617" t="n">
+        <v>0.9824364977041913</v>
+      </c>
+    </row>
+    <row r="618">
+      <c r="A618" t="n">
+        <v>0.9815745052978382</v>
+      </c>
+    </row>
+    <row r="619">
+      <c r="A619" t="n">
+        <v>1.144150670047084</v>
+      </c>
+    </row>
+    <row r="620">
+      <c r="A620" t="n">
+        <v>2.783907492977497</v>
+      </c>
+    </row>
+    <row r="621">
+      <c r="A621" t="n">
+        <v>1.393450174618678</v>
+      </c>
+    </row>
+    <row r="622">
+      <c r="A622" t="n">
+        <v>0.7155844462825693</v>
+      </c>
+    </row>
+    <row r="623">
+      <c r="A623" t="n">
+        <v>1.134867568548177</v>
+      </c>
+    </row>
+    <row r="624">
+      <c r="A624" t="n">
+        <v>0.6</v>
+      </c>
+    </row>
+    <row r="625">
+      <c r="A625" t="n">
+        <v>1.031654228855721</v>
+      </c>
+    </row>
+    <row r="626">
+      <c r="A626" t="n">
+        <v>1.006427337915575</v>
+      </c>
+    </row>
+    <row r="627">
+      <c r="A627" t="n">
+        <v>1.000616199895246</v>
+      </c>
+    </row>
+    <row r="628">
+      <c r="A628" t="n">
+        <v>1.163142485361093</v>
+      </c>
+    </row>
+    <row r="629">
+      <c r="A629" t="n">
+        <v>1.370890412540252</v>
+      </c>
+    </row>
+    <row r="630">
+      <c r="A630" t="n">
+        <v>0.540866034119128</v>
+      </c>
+    </row>
+    <row r="631">
+      <c r="A631" t="n">
+        <v>1.001390572938703</v>
+      </c>
+    </row>
+    <row r="632">
+      <c r="A632" t="n">
+        <v>1.048407414072341</v>
+      </c>
+    </row>
+    <row r="633">
+      <c r="A633" t="n">
+        <v>1.037063489486955</v>
+      </c>
+    </row>
+    <row r="634">
+      <c r="A634" t="n">
+        <v>1.055203610751295</v>
+      </c>
+    </row>
+    <row r="635">
+      <c r="A635" t="n">
+        <v>1.150840122199593</v>
+      </c>
+    </row>
+    <row r="636">
+      <c r="A636" t="n">
+        <v>1.621996915631426</v>
+      </c>
+    </row>
+    <row r="637">
+      <c r="A637" t="n">
+        <v>0.9736370882936671</v>
+      </c>
+    </row>
+    <row r="638">
+      <c r="A638" t="n">
+        <v>0.9599977199362209</v>
+      </c>
+    </row>
+    <row r="639">
+      <c r="A639" t="n">
+        <v>1.003634003927944</v>
+      </c>
+    </row>
+    <row r="640">
+      <c r="A640" t="n">
+        <v>1.148488633438699</v>
+      </c>
+    </row>
+    <row r="641">
+      <c r="A641" t="n">
+        <v>1.162780659367179</v>
+      </c>
+    </row>
+    <row r="642">
+      <c r="A642" t="n">
+        <v>2.415458937198068</v>
       </c>
     </row>
   </sheetData>
@@ -9036,7 +10302,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A16"/>
+  <dimension ref="A1:A17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9144,6 +10410,13 @@
     </row>
     <row r="16">
       <c r="A16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Stand by</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artifacts/consolidado_valores_unicos_mapeo.xlsx
+++ b/artifacts/consolidado_valores_unicos_mapeo.xlsx
@@ -418,7 +418,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A415"/>
+  <dimension ref="A1:A465"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3323,6 +3323,356 @@
       <c r="A415" t="inlineStr">
         <is>
           <t>Cumplimiento Plan de formación Institucional</t>
+        </is>
+      </c>
+    </row>
+    <row r="416">
+      <c r="A416" t="inlineStr">
+        <is>
+          <t>Acreditación Institucional Sede Bogotá - Fase I</t>
+        </is>
+      </c>
+    </row>
+    <row r="417">
+      <c r="A417" t="inlineStr">
+        <is>
+          <t>Plan Talento</t>
+        </is>
+      </c>
+    </row>
+    <row r="418">
+      <c r="A418" t="inlineStr">
+        <is>
+          <t>Certificación SGA sede los Colores</t>
+        </is>
+      </c>
+    </row>
+    <row r="419">
+      <c r="A419" t="inlineStr">
+        <is>
+          <t>Diseño del Modelo de Experiencia Institucional - Fase 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="420">
+      <c r="A420" t="inlineStr">
+        <is>
+          <t>Innovación curricular - Fase I</t>
+        </is>
+      </c>
+    </row>
+    <row r="421">
+      <c r="A421" t="inlineStr">
+        <is>
+          <t>Nuevo POLISIGS</t>
+        </is>
+      </c>
+    </row>
+    <row r="422">
+      <c r="A422" t="inlineStr">
+        <is>
+          <t>Equidad de Genero</t>
+        </is>
+      </c>
+    </row>
+    <row r="423">
+      <c r="A423" t="inlineStr">
+        <is>
+          <t>Portal Universitario</t>
+        </is>
+      </c>
+    </row>
+    <row r="424">
+      <c r="A424" t="inlineStr">
+        <is>
+          <t>Data Lake Institucional</t>
+        </is>
+      </c>
+    </row>
+    <row r="425">
+      <c r="A425" t="inlineStr">
+        <is>
+          <t>Catalogo de recursos virtuales</t>
+        </is>
+      </c>
+    </row>
+    <row r="426">
+      <c r="A426" t="inlineStr">
+        <is>
+          <t>Monarca - Ecosistema Banner</t>
+        </is>
+      </c>
+    </row>
+    <row r="427">
+      <c r="A427" t="inlineStr">
+        <is>
+          <t>Acreditación Institucional Sede Bogotá - Fase II - Condiciones iniciales</t>
+        </is>
+      </c>
+    </row>
+    <row r="428">
+      <c r="A428" t="inlineStr">
+        <is>
+          <t>Creación del Instituto de Educación para el trabajo y el desarrollo humano - Stand By</t>
+        </is>
+      </c>
+    </row>
+    <row r="429">
+      <c r="A429" t="inlineStr">
+        <is>
+          <t>Creación del colegio de educación media virtual  - Stand By</t>
+        </is>
+      </c>
+    </row>
+    <row r="430">
+      <c r="A430" t="inlineStr">
+        <is>
+          <t>Diseño del Modelo de Experiencia Institucional - Fase 2</t>
+        </is>
+      </c>
+    </row>
+    <row r="431">
+      <c r="A431" t="inlineStr">
+        <is>
+          <t>Prime</t>
+        </is>
+      </c>
+    </row>
+    <row r="432">
+      <c r="A432" t="inlineStr">
+        <is>
+          <t>Pricing</t>
+        </is>
+      </c>
+    </row>
+    <row r="433">
+      <c r="A433" t="inlineStr">
+        <is>
+          <t>Experiencia Institucional - Fase 3- Hub de experiencia</t>
+        </is>
+      </c>
+    </row>
+    <row r="434">
+      <c r="A434" t="inlineStr">
+        <is>
+          <t>Centro de Idiomas Fase I</t>
+        </is>
+      </c>
+    </row>
+    <row r="435">
+      <c r="A435" t="inlineStr">
+        <is>
+          <t>CREA Centro de Recursos y Experiencias para el aprendizaje - Fase de Adecuación</t>
+        </is>
+      </c>
+    </row>
+    <row r="436">
+      <c r="A436" t="inlineStr">
+        <is>
+          <t>Migración modelo de transporte rotativo</t>
+        </is>
+      </c>
+    </row>
+    <row r="437">
+      <c r="A437" t="inlineStr">
+        <is>
+          <t>Ecosistema E3</t>
+        </is>
+      </c>
+    </row>
+    <row r="438">
+      <c r="A438" t="inlineStr">
+        <is>
+          <t>Habilidades Poderosas</t>
+        </is>
+      </c>
+    </row>
+    <row r="439">
+      <c r="A439" t="inlineStr">
+        <is>
+          <t>Ser PRO</t>
+        </is>
+      </c>
+    </row>
+    <row r="440">
+      <c r="A440" t="inlineStr">
+        <is>
+          <t>Cultura de una buena docencia</t>
+        </is>
+      </c>
+    </row>
+    <row r="441">
+      <c r="A441" t="inlineStr">
+        <is>
+          <t>Proyecto Silver</t>
+        </is>
+      </c>
+    </row>
+    <row r="442">
+      <c r="A442" t="inlineStr">
+        <is>
+          <t>Hubspot CRM</t>
+        </is>
+      </c>
+    </row>
+    <row r="443">
+      <c r="A443" t="inlineStr">
+        <is>
+          <t>Centro de Idiomas Fase I - Stand By</t>
+        </is>
+      </c>
+    </row>
+    <row r="444">
+      <c r="A444" t="inlineStr">
+        <is>
+          <t>Acreditación Institucional  Fase III - Etapa de evaluación externa</t>
+        </is>
+      </c>
+    </row>
+    <row r="445">
+      <c r="A445" t="inlineStr">
+        <is>
+          <t>Fortalecimiento de la investigacion, la innovación y la creación</t>
+        </is>
+      </c>
+    </row>
+    <row r="446">
+      <c r="A446" t="inlineStr">
+        <is>
+          <t>Fortalecimiento de planta docente</t>
+        </is>
+      </c>
+    </row>
+    <row r="447">
+      <c r="A447" t="inlineStr">
+        <is>
+          <t>Plataforma de gestión de la información curricular Fase I</t>
+        </is>
+      </c>
+    </row>
+    <row r="448">
+      <c r="A448" t="inlineStr">
+        <is>
+          <t>Actualización de TRD y creación del Plan de gestión documental</t>
+        </is>
+      </c>
+    </row>
+    <row r="449">
+      <c r="A449" t="inlineStr">
+        <is>
+          <t>ADN Poli</t>
+        </is>
+      </c>
+    </row>
+    <row r="450">
+      <c r="A450" t="inlineStr">
+        <is>
+          <t>Gobierno de datos</t>
+        </is>
+      </c>
+    </row>
+    <row r="451">
+      <c r="A451" t="inlineStr">
+        <is>
+          <t>Herramientas de Gestión para el mejoramiento continuo</t>
+        </is>
+      </c>
+    </row>
+    <row r="452">
+      <c r="A452" t="inlineStr">
+        <is>
+          <t>Proyectos Ilumno Self Service S&amp;P</t>
+        </is>
+      </c>
+    </row>
+    <row r="453">
+      <c r="A453" t="inlineStr">
+        <is>
+          <t>Reingenia de aplicaciones</t>
+        </is>
+      </c>
+    </row>
+    <row r="454">
+      <c r="A454" t="inlineStr">
+        <is>
+          <t>SOPHIA Sistema de optimización y programación horaria institucional</t>
+        </is>
+      </c>
+    </row>
+    <row r="455">
+      <c r="A455" t="inlineStr">
+        <is>
+          <t>Proyecto de permanencia institucional</t>
+        </is>
+      </c>
+    </row>
+    <row r="456">
+      <c r="A456" t="inlineStr">
+        <is>
+          <t>Centro Gastronómico</t>
+        </is>
+      </c>
+    </row>
+    <row r="457">
+      <c r="A457" t="inlineStr">
+        <is>
+          <t>Modelo de seguimiento al graduado</t>
+        </is>
+      </c>
+    </row>
+    <row r="458">
+      <c r="A458" t="inlineStr">
+        <is>
+          <t>Experiencia Institucional - Fase 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="459">
+      <c r="A459" t="inlineStr">
+        <is>
+          <t>Creación del colegio de educación media virtual</t>
+        </is>
+      </c>
+    </row>
+    <row r="460">
+      <c r="A460" t="inlineStr">
+        <is>
+          <t>Reingenieria de aplicaciones</t>
+        </is>
+      </c>
+    </row>
+    <row r="461">
+      <c r="A461" t="inlineStr">
+        <is>
+          <t>Redefinición de Modelo de seguimiento y acompañamiento al Graduado</t>
+        </is>
+      </c>
+    </row>
+    <row r="462">
+      <c r="A462" t="inlineStr">
+        <is>
+          <t>Titulación Autogestionada</t>
+        </is>
+      </c>
+    </row>
+    <row r="463">
+      <c r="A463" t="inlineStr">
+        <is>
+          <t>Ecosistema Banner</t>
+        </is>
+      </c>
+    </row>
+    <row r="464">
+      <c r="A464" t="inlineStr">
+        <is>
+          <t>Fortalecimiento del proceso de visibilidad nacional e internacional</t>
+        </is>
+      </c>
+    </row>
+    <row r="465">
+      <c r="A465" t="inlineStr">
+        <is>
+          <t>Sistema de medición de resultados de aprendizaje</t>
         </is>
       </c>
     </row>
@@ -3337,7 +3687,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A133"/>
+  <dimension ref="A1:A143"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4003,6 +4353,56 @@
     <row r="133">
       <c r="A133" t="n">
         <v>65</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="n">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="n">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="n">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="n">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="n">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="n">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="n">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="n">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="n">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="n">
+        <v>77</v>
       </c>
     </row>
   </sheetData>
@@ -4016,7 +4416,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:A431"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4027,7 +4427,2152 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr"/>
+      <c r="A2" t="n">
+        <v>1.1375</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>1.103125</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>1.084375</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>1.005294117647059</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>1.049338364617541</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>1.018387371149503</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>1.013388888888889</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>1.008861111111111</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>1.061852933368728</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>1.111111111111111</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>1.081081081081081</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>1.025641025641026</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>1.068092105263156</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>1.136371794871794</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>1.168625</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>1.1363125</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>1.009278350515464</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>1.006529209621993</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>1.004458762886598</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>0.9867697594501716</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>0.9783505154639176</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>1.22</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>1.125</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>1.163088235294118</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>1.2375</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>1.25</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>0.9934426229508201</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>1.020408163265306</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>1.110019646365422</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>0.983</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>0.99</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>1.3</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>1.092409596295854</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>1.0625</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>1.175</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>0.9175239389233949</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>0.975</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>0.875</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>1.14375</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>1.1584375</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>1.174166666666667</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>1.1</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>1.025</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>1.075</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>1.0125</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>0.925</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>1.1125</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>1.1625</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>1.176732209737827</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>1.225</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>1.021345268941676</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>0.9164420485175202</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>1.018268942797245</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>0.9721692718261532</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>0.8958967926894821</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>1.09653540903541</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>1.1373125</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>1.178979166666667</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>0.914</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>0.4375</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="n">
+        <v>1.274151011252328</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="n">
+        <v>1.180555670739568</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="n">
+        <v>1.102941176470588</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="n">
+        <v>1.226993865030675</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="n">
+        <v>1.159863945578231</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="n">
+        <v>1.2</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="n">
+        <v>1.002237136465324</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="n">
+        <v>1.018353514109951</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="n">
+        <v>1.101965279442938</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="n">
+        <v>1.235</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="n">
+        <v>1.183333333333333</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="n">
+        <v>0.4875</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="n">
+        <v>0.4829782608695652</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="n">
+        <v>0.5860217391304348</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="n">
+        <v>0.3916326530612245</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="n">
+        <v>0.6111111111111112</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="n">
+        <v>0.9230769230769231</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="n">
+        <v>1.164315151769025</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="n">
+        <v>1.06</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="n">
+        <v>1.206666666666667</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="n">
+        <v>1.054293758851389</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="n">
+        <v>1.0375</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="n">
+        <v>1.129625</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="n">
+        <v>1.1875</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="n">
+        <v>1.205</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="n">
+        <v>1.2136875</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="n">
+        <v>1.2115625</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="n">
+        <v>1.139176470588235</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="n">
+        <v>1.042388888888889</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="n">
+        <v>1.087547798740395</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="n">
+        <v>0.9948992481203011</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="n">
+        <v>0.9705679943988564</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="n">
+        <v>0.9567543859649122</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="n">
+        <v>0.9569473684210525</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="n">
+        <v>1.052631578947368</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="n">
+        <v>1.017125</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="n">
+        <v>1.048</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="n">
+        <v>1.215789473684211</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="n">
+        <v>0.9956504338545761</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="n">
+        <v>1.028890170900142</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="n">
+        <v>1.022513368983957</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="n">
+        <v>1.138493150684931</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="n">
+        <v>1.023875</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="n">
+        <v>1.098765432098765</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="n">
+        <v>1.032036082474227</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="n">
+        <v>0.9228245614035104</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="n">
+        <v>1.1561875</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="n">
+        <v>1.285714285714286</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="n">
+        <v>1.0925</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="n">
+        <v>1.044252873563218</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="n">
+        <v>0.9803030303030303</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="n">
+        <v>1.179039301310044</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="n">
+        <v>1.076929246123686</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="n">
+        <v>1.088077934787474</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="n">
+        <v>1.082526315789474</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="n">
+        <v>1.171894736842105</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="n">
+        <v>0.2215527733259426</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="n">
+        <v>1.295263157894737</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="n">
+        <v>0.9652509652509653</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="n">
+        <v>0.9784735812133072</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="n">
+        <v>0.9039956608208281</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="n">
+        <v>1.266261460462019</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="n">
+        <v>0.07499999999999929</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="n">
+        <v>1.049203896717607</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="n">
+        <v>0.3333</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="n">
+        <v>0.275</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="n">
+        <v>1.041666666666667</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="n">
+        <v>0.7638888888888888</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="n">
+        <v>0.9412</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="n">
+        <v>0.9167000000000001</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="n">
+        <v>0.7142857142857143</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="n">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="n">
+        <v>8.495912050318455e-05</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="n">
+        <v>1.001070326764465</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="n">
+        <v>1.074944444444444</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="n">
+        <v>1.062777777777778</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="n">
+        <v>1.085833333333333</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="n">
+        <v>0.9253333333333333</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="n">
+        <v>1.11575</v>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="n">
+        <v>1.075465277777778</v>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="n">
+        <v>0.8165289256198299</v>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="n">
+        <v>0.92012779552716</v>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="n">
+        <v>0.9724542838577928</v>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="n">
+        <v>0.8847944514062934</v>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="n">
+        <v>0.9392592592592593</v>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="n">
+        <v>0.65</v>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="n">
+        <v>0.9791666666666665</v>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="n">
+        <v>1.156866161616162</v>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="n">
+        <v>1.111740111740112</v>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="n">
+        <v>1.241322916666667</v>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="n">
+        <v>1.067555555555556</v>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="n">
+        <v>1.128045977011494</v>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="n">
+        <v>1.0022</v>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="n">
+        <v>1.0012</v>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="n">
+        <v>0.7223529411764705</v>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="n">
+        <v>1.03</v>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="n">
+        <v>0.9622641509433965</v>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="n">
+        <v>1.0431</v>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="n">
+        <v>0.18</v>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="n">
+        <v>0.15</v>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="n">
+        <v>1.23529705882355</v>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="n">
+        <v>0.9285714285714286</v>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="n">
+        <v>0.7</v>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="n">
+        <v>0.8714444444444445</v>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="n">
+        <v>1.03448275862069</v>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="n">
+        <v>1.105263157894737</v>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="n">
+        <v>0.8856499999999999</v>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="n">
+        <v>0.9840896763821895</v>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="n">
+        <v>0.9313157894736841</v>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="n">
+        <v>0.8047368421052632</v>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="n">
+        <v>0.976802605821255</v>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="n">
+        <v>1.019740259234822</v>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="n">
+        <v>1.03915</v>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="n">
+        <v>1.1354375</v>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="n">
+        <v>1.005917159763314</v>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="n">
+        <v>0.9071117561683598</v>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="n">
+        <v>0.9781427363844946</v>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="n">
+        <v>1.159776231409469</v>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="n">
+        <v>1.024705221785514</v>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="n">
+        <v>1.038011695906433</v>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="n">
+        <v>1.012291666666667</v>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="n">
+        <v>0.999278350515464</v>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="n">
+        <v>1.005</v>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="n">
+        <v>1.011111111111111</v>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="n">
+        <v>1.031111111111111</v>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="n">
+        <v>1.015217391304348</v>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="n">
+        <v>0.3058823529411765</v>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="n">
+        <v>0.9210526315789473</v>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="n">
+        <v>0.9928888888888889</v>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="n">
+        <v>1.037</v>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="n">
+        <v>0.873</v>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="n">
+        <v>0.8545</v>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="n">
+        <v>0.7765151515151526</v>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="n">
+        <v>1.02974828375286</v>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="n">
+        <v>1.001684210526316</v>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="n">
+        <v>0.9184</v>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="n">
+        <v>1.0728</v>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="n">
+        <v>1.073733333333333</v>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="n">
+        <v>0.7913</v>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="n">
+        <v>1.243445692883895</v>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="n">
+        <v>0.6776000000000001</v>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="n">
+        <v>1.099547511312217</v>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="n">
+        <v>0.8928571428571429</v>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" t="n">
+        <v>1.260869565217391</v>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" t="n">
+        <v>1.047619047619048</v>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" t="n">
+        <v>1.136363636363636</v>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" t="n">
+        <v>1.1285</v>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" t="n">
+        <v>1.013647058823529</v>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" t="n">
+        <v>0.7073170731707317</v>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" t="n">
+        <v>1.15</v>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" t="n">
+        <v>1.297222222222222</v>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" t="n">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" t="n">
+        <v>1.29375</v>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" t="n">
+        <v>1.105</v>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" t="n">
+        <v>1.0663</v>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" t="n">
+        <v>1.254355400696864</v>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" t="n">
+        <v>1.004431818181818</v>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" t="n">
+        <v>1.009545454545455</v>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" t="n">
+        <v>1.012359550561798</v>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" t="n">
+        <v>1.173125</v>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" t="n">
+        <v>0.9871951219512195</v>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" t="n">
+        <v>1.147975</v>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" t="n">
+        <v>0.9523809523809523</v>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" t="n">
+        <v>1.01</v>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" t="n">
+        <v>1.176333333333333</v>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" t="n">
+        <v>1.27219833333335</v>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" t="n">
+        <v>1.1372</v>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" t="n">
+        <v>1.0245</v>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" t="n">
+        <v>1.086135338345867</v>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" t="n">
+        <v>1.056612903225806</v>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" t="n">
+        <v>1.072204301075269</v>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" t="n">
+        <v>1.080941176470588</v>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" t="n">
+        <v>1.144470588235294</v>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" t="n">
+        <v>1.009180280706798</v>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" t="n">
+        <v>1.009722222222222</v>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" t="n">
+        <v>1.01010101010101</v>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" t="n">
+        <v>1.153846153846154</v>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" t="n">
+        <v>0.9941176470588236</v>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" t="n">
+        <v>1.114285714285714</v>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" t="n">
+        <v>1.083482689692428</v>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" t="n">
+        <v>1.003092869681518</v>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" t="n">
+        <v>1.053463260468791</v>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" t="n">
+        <v>1.045888138405023</v>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" t="n">
+        <v>1.137873563218391</v>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" t="n">
+        <v>1.057647058823529</v>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" t="n">
+        <v>1.013333333333333</v>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" t="n">
+        <v>1.039130434782609</v>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" t="n">
+        <v>0.99156641448592</v>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" t="n">
+        <v>1.015685321634592</v>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" t="n">
+        <v>1.016989795918367</v>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" t="n">
+        <v>1.1541</v>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" t="n">
+        <v>1.162790697674419</v>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" t="n">
+        <v>1.249951341040912</v>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" t="n">
+        <v>0.992</v>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" t="n">
+        <v>0.764</v>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" t="n">
+        <v>1.05</v>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" t="n">
+        <v>1.047222222222222</v>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" t="n">
+        <v>1.021505376344086</v>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" t="n">
+        <v>0.73775</v>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264" t="n">
+        <v>0.98575</v>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265" t="n">
+        <v>1.23355</v>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266" t="n">
+        <v>0.7855500000000001</v>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267" t="n">
+        <v>1.097701149425287</v>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268" t="n">
+        <v>1.054597701149425</v>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269" t="n">
+        <v>1.061111111111111</v>
+      </c>
+    </row>
+    <row r="270">
+      <c r="A270" t="n">
+        <v>0.739616666666675</v>
+      </c>
+    </row>
+    <row r="271">
+      <c r="A271" t="n">
+        <v>0.9852500000000001</v>
+      </c>
+    </row>
+    <row r="272">
+      <c r="A272" t="n">
+        <v>1.01215</v>
+      </c>
+    </row>
+    <row r="273">
+      <c r="A273" t="n">
+        <v>1.065894736842105</v>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274" t="n">
+        <v>1.148421052631579</v>
+      </c>
+    </row>
+    <row r="275">
+      <c r="A275" t="n">
+        <v>1.236947368421053</v>
+      </c>
+    </row>
+    <row r="276">
+      <c r="A276" t="n">
+        <v>0.7999360051195904</v>
+      </c>
+    </row>
+    <row r="277">
+      <c r="A277" t="n">
+        <v>1.0711</v>
+      </c>
+    </row>
+    <row r="278">
+      <c r="A278" t="n">
+        <v>1.038913043478261</v>
+      </c>
+    </row>
+    <row r="279">
+      <c r="A279" t="n">
+        <v>1.0568938582028</v>
+      </c>
+    </row>
+    <row r="280">
+      <c r="A280" t="n">
+        <v>0.97615</v>
+      </c>
+    </row>
+    <row r="281">
+      <c r="A281" t="n">
+        <v>1.0326</v>
+      </c>
+    </row>
+    <row r="282">
+      <c r="A282" t="n">
+        <v>1.034636945020853</v>
+      </c>
+    </row>
+    <row r="283">
+      <c r="A283" t="n">
+        <v>0.7892</v>
+      </c>
+    </row>
+    <row r="284">
+      <c r="A284" t="n">
+        <v>1.08985854341735</v>
+      </c>
+    </row>
+    <row r="285">
+      <c r="A285" t="n">
+        <v>0.9722499999999999</v>
+      </c>
+    </row>
+    <row r="286">
+      <c r="A286" t="n">
+        <v>1.0594</v>
+      </c>
+    </row>
+    <row r="287">
+      <c r="A287" t="n">
+        <v>1.02130205659755</v>
+      </c>
+    </row>
+    <row r="288">
+      <c r="A288" t="n">
+        <v>0.9591500000000001</v>
+      </c>
+    </row>
+    <row r="289">
+      <c r="A289" t="n">
+        <v>0.9853000000000001</v>
+      </c>
+    </row>
+    <row r="290">
+      <c r="A290" t="n">
+        <v>1.29021164972635</v>
+      </c>
+    </row>
+    <row r="291">
+      <c r="A291" t="n">
+        <v>1.10455</v>
+      </c>
+    </row>
+    <row r="292">
+      <c r="A292" t="n">
+        <v>1.13572352941175</v>
+      </c>
+    </row>
+    <row r="293">
+      <c r="A293" t="n">
+        <v>0.9505</v>
+      </c>
+    </row>
+    <row r="294">
+      <c r="A294" t="n">
+        <v>1.0208</v>
+      </c>
+    </row>
+    <row r="295">
+      <c r="A295" t="n">
+        <v>1.2493</v>
+      </c>
+    </row>
+    <row r="296">
+      <c r="A296" t="n">
+        <v>0.8856000000000001</v>
+      </c>
+    </row>
+    <row r="297">
+      <c r="A297" t="n">
+        <v>1.0889</v>
+      </c>
+    </row>
+    <row r="298">
+      <c r="A298" t="n">
+        <v>1.2060243283327</v>
+      </c>
+    </row>
+    <row r="299">
+      <c r="A299" t="n">
+        <v>0.9431999999999999</v>
+      </c>
+    </row>
+    <row r="300">
+      <c r="A300" t="n">
+        <v>1.1273</v>
+      </c>
+    </row>
+    <row r="301">
+      <c r="A301" t="n">
+        <v>0.4966666666666666</v>
+      </c>
+    </row>
+    <row r="302">
+      <c r="A302" t="n">
+        <v>0.99249166666667</v>
+      </c>
+    </row>
+    <row r="303">
+      <c r="A303" t="n">
+        <v>0.9992</v>
+      </c>
+    </row>
+    <row r="304">
+      <c r="A304" t="n">
+        <v>0.9978</v>
+      </c>
+    </row>
+    <row r="305">
+      <c r="A305" t="n">
+        <v>1.075268817204301</v>
+      </c>
+    </row>
+    <row r="306">
+      <c r="A306" t="n">
+        <v>1.008</v>
+      </c>
+    </row>
+    <row r="307">
+      <c r="A307" t="n">
+        <v>1.153846153846154</v>
+      </c>
+    </row>
+    <row r="308">
+      <c r="A308" t="n">
+        <v>1.29445</v>
+      </c>
+    </row>
+    <row r="309">
+      <c r="A309" t="n">
+        <v>1.111125</v>
+      </c>
+    </row>
+    <row r="310">
+      <c r="A310" t="n">
+        <v>1.10125</v>
+      </c>
+    </row>
+    <row r="311">
+      <c r="A311" t="n">
+        <v>1.150196428571431</v>
+      </c>
+    </row>
+    <row r="312">
+      <c r="A312" t="n">
+        <v>1.1435</v>
+      </c>
+    </row>
+    <row r="313">
+      <c r="A313" t="n">
+        <v>1.063333333333333</v>
+      </c>
+    </row>
+    <row r="314">
+      <c r="A314" t="n">
+        <v>1.1136</v>
+      </c>
+    </row>
+    <row r="315">
+      <c r="A315" t="n">
+        <v>1.0453</v>
+      </c>
+    </row>
+    <row r="316">
+      <c r="A316" t="n">
+        <v>1.2507</v>
+      </c>
+    </row>
+    <row r="317">
+      <c r="A317" t="n">
+        <v>1.180555555555556</v>
+      </c>
+    </row>
+    <row r="318">
+      <c r="A318" t="n">
+        <v>1.24</v>
+      </c>
+    </row>
+    <row r="319">
+      <c r="A319" t="n">
+        <v>0.98</v>
+      </c>
+    </row>
+    <row r="320">
+      <c r="A320" t="n">
+        <v>1.273242841204909</v>
+      </c>
+    </row>
+    <row r="321">
+      <c r="A321" t="n">
+        <v>1.026574917163008</v>
+      </c>
+    </row>
+    <row r="322">
+      <c r="A322" t="n">
+        <v>0.9628</v>
+      </c>
+    </row>
+    <row r="323">
+      <c r="A323" t="n">
+        <v>0.9878</v>
+      </c>
+    </row>
+    <row r="324">
+      <c r="A324" t="n">
+        <v>0.9887</v>
+      </c>
+    </row>
+    <row r="325">
+      <c r="A325" t="n">
+        <v>0.96</v>
+      </c>
+    </row>
+    <row r="326">
+      <c r="A326" t="n">
+        <v>0.9836</v>
+      </c>
+    </row>
+    <row r="327">
+      <c r="A327" t="n">
+        <v>0.993</v>
+      </c>
+    </row>
+    <row r="328">
+      <c r="A328" t="n">
+        <v>0.9439</v>
+      </c>
+    </row>
+    <row r="329">
+      <c r="A329" t="n">
+        <v>0.9883</v>
+      </c>
+    </row>
+    <row r="330">
+      <c r="A330" t="n">
+        <v>0.9799</v>
+      </c>
+    </row>
+    <row r="331">
+      <c r="A331" t="n">
+        <v>0.95802222222222</v>
+      </c>
+    </row>
+    <row r="332">
+      <c r="A332" t="n">
+        <v>0.9778</v>
+      </c>
+    </row>
+    <row r="333">
+      <c r="A333" t="n">
+        <v>0.9961</v>
+      </c>
+    </row>
+    <row r="334">
+      <c r="A334" t="n">
+        <v>0.9356</v>
+      </c>
+    </row>
+    <row r="335">
+      <c r="A335" t="n">
+        <v>0.9667</v>
+      </c>
+    </row>
+    <row r="336">
+      <c r="A336" t="n">
+        <v>1.2144</v>
+      </c>
+    </row>
+    <row r="337">
+      <c r="A337" t="n">
+        <v>1.051428571428571</v>
+      </c>
+    </row>
+    <row r="338">
+      <c r="A338" t="n">
+        <v>0.9875156054931337</v>
+      </c>
+    </row>
+    <row r="339">
+      <c r="A339" t="n">
+        <v>1.024739583333333</v>
+      </c>
+    </row>
+    <row r="340">
+      <c r="A340" t="n">
+        <v>0.9404761904761905</v>
+      </c>
+    </row>
+    <row r="341">
+      <c r="A341" t="n">
+        <v>1.227642276422764</v>
+      </c>
+    </row>
+    <row r="342">
+      <c r="A342" t="n">
+        <v>0.06521739130434782</v>
+      </c>
+    </row>
+    <row r="343">
+      <c r="A343" t="n">
+        <v>1.222222222222222</v>
+      </c>
+    </row>
+    <row r="344">
+      <c r="A344" t="n">
+        <v>1.051818181818182</v>
+      </c>
+    </row>
+    <row r="345">
+      <c r="A345" t="n">
+        <v>0.9186875000000001</v>
+      </c>
+    </row>
+    <row r="346">
+      <c r="A346" t="n">
+        <v>1.188118811881177</v>
+      </c>
+    </row>
+    <row r="347">
+      <c r="A347" t="n">
+        <v>1.176470588235294</v>
+      </c>
+    </row>
+    <row r="348">
+      <c r="A348" t="n">
+        <v>0.05521811154058531</v>
+      </c>
+    </row>
+    <row r="349">
+      <c r="A349" t="n">
+        <v>0.05696382796923953</v>
+      </c>
+    </row>
+    <row r="350">
+      <c r="A350" t="n">
+        <v>0.06060606060606061</v>
+      </c>
+    </row>
+    <row r="351">
+      <c r="A351" t="n">
+        <v>1.142857142857143</v>
+      </c>
+    </row>
+    <row r="352">
+      <c r="A352" t="n">
+        <v>1.067318562735053</v>
+      </c>
+    </row>
+    <row r="353">
+      <c r="A353" t="n">
+        <v>1.083552547063557</v>
+      </c>
+    </row>
+    <row r="354">
+      <c r="A354" t="n">
+        <v>1.176421052631579</v>
+      </c>
+    </row>
+    <row r="355">
+      <c r="A355" t="n">
+        <v>1.104253086419756</v>
+      </c>
+    </row>
+    <row r="356">
+      <c r="A356" t="n">
+        <v>0.8333333333333334</v>
+      </c>
+    </row>
+    <row r="357">
+      <c r="A357" t="n">
+        <v>0.4761904761904762</v>
+      </c>
+    </row>
+    <row r="358">
+      <c r="A358" t="n">
+        <v>0.5263157894736842</v>
+      </c>
+    </row>
+    <row r="359">
+      <c r="A359" t="n">
+        <v>1.046148213048083</v>
+      </c>
+    </row>
+    <row r="360">
+      <c r="A360" t="n">
+        <v>0.4422137218917903</v>
+      </c>
+    </row>
+    <row r="361">
+      <c r="A361" t="n">
+        <v>0.3083421981715308</v>
+      </c>
+    </row>
+    <row r="362">
+      <c r="A362" t="n">
+        <v>0.2521</v>
+      </c>
+    </row>
+    <row r="363">
+      <c r="A363" t="n">
+        <v>1.265346087218498</v>
+      </c>
+    </row>
+    <row r="364">
+      <c r="A364" t="n">
+        <v>0.9974088014033367</v>
+      </c>
+    </row>
+    <row r="365">
+      <c r="A365" t="n">
+        <v>1.01515306122449</v>
+      </c>
+    </row>
+    <row r="366">
+      <c r="A366" t="n">
+        <v>1.017908163265306</v>
+      </c>
+    </row>
+    <row r="367">
+      <c r="A367" t="n">
+        <v>1.110221510541767</v>
+      </c>
+    </row>
+    <row r="368">
+      <c r="A368" t="n">
+        <v>1.049629629629629</v>
+      </c>
+    </row>
+    <row r="369">
+      <c r="A369" t="n">
+        <v>1.077333333333333</v>
+      </c>
+    </row>
+    <row r="370">
+      <c r="A370" t="n">
+        <v>1.000666666666667</v>
+      </c>
+    </row>
+    <row r="371">
+      <c r="A371" t="n">
+        <v>1.035555555555556</v>
+      </c>
+    </row>
+    <row r="372">
+      <c r="A372" t="n">
+        <v>1.2515</v>
+      </c>
+    </row>
+    <row r="373">
+      <c r="A373" t="n">
+        <v>0.87</v>
+      </c>
+    </row>
+    <row r="374">
+      <c r="A374" t="n">
+        <v>0.97345</v>
+      </c>
+    </row>
+    <row r="375">
+      <c r="A375" t="n">
+        <v>1.115925</v>
+      </c>
+    </row>
+    <row r="376">
+      <c r="A376" t="n">
+        <v>0.8</v>
+      </c>
+    </row>
+    <row r="377">
+      <c r="A377" t="n">
+        <v>1.130925</v>
+      </c>
+    </row>
+    <row r="378">
+      <c r="A378" t="n">
+        <v>1.142996108949417</v>
+      </c>
+    </row>
+    <row r="379">
+      <c r="A379" t="n">
+        <v>1.05225</v>
+      </c>
+    </row>
+    <row r="380">
+      <c r="A380" t="n">
+        <v>0.5683</v>
+      </c>
+    </row>
+    <row r="381">
+      <c r="A381" t="n">
+        <v>1.134</v>
+      </c>
+    </row>
+    <row r="382">
+      <c r="A382" t="n">
+        <v>1.0655</v>
+      </c>
+    </row>
+    <row r="383">
+      <c r="A383" t="n">
+        <v>1.2154</v>
+      </c>
+    </row>
+    <row r="384">
+      <c r="A384" t="n">
+        <v>1.0875</v>
+      </c>
+    </row>
+    <row r="385">
+      <c r="A385" t="n">
+        <v>1.100917431192661</v>
+      </c>
+    </row>
+    <row r="386">
+      <c r="A386" t="n">
+        <v>0.997</v>
+      </c>
+    </row>
+    <row r="387">
+      <c r="A387" t="n">
+        <v>0.9913</v>
+      </c>
+    </row>
+    <row r="388">
+      <c r="A388" t="n">
+        <v>0.9986</v>
+      </c>
+    </row>
+    <row r="389">
+      <c r="A389" t="n">
+        <v>1.145833333333333</v>
+      </c>
+    </row>
+    <row r="390">
+      <c r="A390" t="n">
+        <v>1.001761363636364</v>
+      </c>
+    </row>
+    <row r="391">
+      <c r="A391" t="n">
+        <v>0.303</v>
+      </c>
+    </row>
+    <row r="392">
+      <c r="A392" t="n">
+        <v>1.093662217185824</v>
+      </c>
+    </row>
+    <row r="393">
+      <c r="A393" t="n">
+        <v>0.9082402811130974</v>
+      </c>
+    </row>
+    <row r="394">
+      <c r="A394" t="n">
+        <v>0.9625</v>
+      </c>
+    </row>
+    <row r="395">
+      <c r="A395" t="n">
+        <v>0.7875</v>
+      </c>
+    </row>
+    <row r="396">
+      <c r="A396" t="n">
+        <v>1.2125</v>
+      </c>
+    </row>
+    <row r="397">
+      <c r="A397" t="n">
+        <v>0.8375</v>
+      </c>
+    </row>
+    <row r="398">
+      <c r="A398" t="n">
+        <v>1.15625</v>
+      </c>
+    </row>
+    <row r="399">
+      <c r="A399" t="n">
+        <v>1.081444444444444</v>
+      </c>
+    </row>
+    <row r="400">
+      <c r="A400" t="n">
+        <v>0.9841428571428571</v>
+      </c>
+    </row>
+    <row r="401">
+      <c r="A401" t="n">
+        <v>1.02725</v>
+      </c>
+    </row>
+    <row r="402">
+      <c r="A402" t="n">
+        <v>1.016842105263158</v>
+      </c>
+    </row>
+    <row r="403">
+      <c r="A403" t="n">
+        <v>0.8820618556701031</v>
+      </c>
+    </row>
+    <row r="404">
+      <c r="A404" t="n">
+        <v>1.043777777777778</v>
+      </c>
+    </row>
+    <row r="405">
+      <c r="A405" t="n">
+        <v>0.9892307692307691</v>
+      </c>
+    </row>
+    <row r="406">
+      <c r="A406" t="n">
+        <v>1.006340206185567</v>
+      </c>
+    </row>
+    <row r="407">
+      <c r="A407" t="n">
+        <v>1.1338</v>
+      </c>
+    </row>
+    <row r="408">
+      <c r="A408" t="n">
+        <v>1.19375</v>
+      </c>
+    </row>
+    <row r="409">
+      <c r="A409" t="n">
+        <v>1.022988505747126</v>
+      </c>
+    </row>
+    <row r="410">
+      <c r="A410" t="n">
+        <v>0.9487179487179487</v>
+      </c>
+    </row>
+    <row r="411">
+      <c r="A411" t="n">
+        <v>1.245614035087719</v>
+      </c>
+    </row>
+    <row r="412">
+      <c r="A412" t="n">
+        <v>0.9693877551020408</v>
+      </c>
+    </row>
+    <row r="413">
+      <c r="A413" t="n">
+        <v>0.8571428571428571</v>
+      </c>
+    </row>
+    <row r="414">
+      <c r="A414" t="n">
+        <v>0.8271604938271605</v>
+      </c>
+    </row>
+    <row r="415">
+      <c r="A415" t="n">
+        <v>0.7846153846153846</v>
+      </c>
+    </row>
+    <row r="416">
+      <c r="A416" t="n">
+        <v>0.7368421052631579</v>
+      </c>
+    </row>
+    <row r="417">
+      <c r="A417" t="n">
+        <v>0.8780487804878049</v>
+      </c>
+    </row>
+    <row r="418">
+      <c r="A418" t="n">
+        <v>0.9795918367346939</v>
+      </c>
+    </row>
+    <row r="419">
+      <c r="A419" t="n">
+        <v>0.9850746268656716</v>
+      </c>
+    </row>
+    <row r="420">
+      <c r="A420" t="n">
+        <v>0.9791666666666666</v>
+      </c>
+    </row>
+    <row r="421">
+      <c r="A421" t="n">
+        <v>0.9868421052631579</v>
+      </c>
+    </row>
+    <row r="422">
+      <c r="A422" t="n">
+        <v>1.08</v>
+      </c>
+    </row>
+    <row r="423">
+      <c r="A423" t="n">
+        <v>0.9512195121951219</v>
+      </c>
+    </row>
+    <row r="424">
+      <c r="A424" t="n">
+        <v>1.051948051948052</v>
+      </c>
+    </row>
+    <row r="425">
+      <c r="A425" t="n">
+        <v>0.968421052631579</v>
+      </c>
+    </row>
+    <row r="426">
+      <c r="A426" t="n">
+        <v>0.9560439560439561</v>
+      </c>
+    </row>
+    <row r="427">
+      <c r="A427" t="n">
+        <v>1.013157894736842</v>
+      </c>
+    </row>
+    <row r="428">
+      <c r="A428" t="n">
+        <v>0.9333333333333333</v>
+      </c>
+    </row>
+    <row r="429">
+      <c r="A429" t="n">
+        <v>0.95</v>
+      </c>
+    </row>
+    <row r="430">
+      <c r="A430" t="n">
+        <v>0.9666666666666667</v>
+      </c>
+    </row>
+    <row r="431">
+      <c r="A431" t="n">
+        <v>0.9444444444444444</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -4040,7 +6585,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:A593"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4051,7 +6596,2962 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr"/>
+      <c r="A2" t="n">
+        <v>1.1375</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>1.103125</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>1.084375</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>1.005294117647059</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>1.049338364617541</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>1.018387371149503</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>1.013388888888889</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>1.008861111111111</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>1.061852933368728</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>1.111111111111111</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>1.081081081081081</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>1.025641025641026</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>1.068092105263156</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>1.136371794871794</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>1.168625</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>1.1363125</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>1.009278350515464</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>1.006529209621993</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>1.004458762886598</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>0.9867697594501716</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>0.9783505154639176</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>1.22</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>1.125</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>1.163088235294118</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>1.2375</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>1.25</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>0.9934426229508201</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>1.020408163265306</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>1.110019646365422</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>0.983</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>0.99</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>5.756600000000013</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>4.553191489361702</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>10.90909090909091</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>10.19047619047619</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>1.092409596295854</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>1.0625</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>1.175</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>0.9175239389233949</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>0.975</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>0.875</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>1.14375</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>1.1584375</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>1.174166666666667</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>1.1</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>1.025</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>1.075</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>1.0125</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>0.925</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>1.1125</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>1.1625</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>1.176732209737827</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>1.225</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>1.021345268941676</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>0.9164420485175202</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>1.018268942797245</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>0.9721692718261532</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>0.8958967926894821</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>1.09653540903541</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>1.1373125</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="n">
+        <v>1.178979166666667</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="n">
+        <v>0.914</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="n">
+        <v>0.4375</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="n">
+        <v>52.60305720909686</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="n">
+        <v>56.32131658729979</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="n">
+        <v>15.38671074380166</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="n">
+        <v>8.24295554164058</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="n">
+        <v>2.666666666666667</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="n">
+        <v>59.18396903047894</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="n">
+        <v>26.76728254883809</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="n">
+        <v>20.3143460949464</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="n">
+        <v>18.78904430655509</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="n">
+        <v>20.88888888888889</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="n">
+        <v>16.1399999999996</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="n">
+        <v>16.66666666666667</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="n">
+        <v>12.5</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="n">
+        <v>1.274151011252328</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="n">
+        <v>1.180555670739568</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="n">
+        <v>1.468479758156837</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="n">
+        <v>1.102941176470588</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="n">
+        <v>1.226993865030675</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="n">
+        <v>1.159863945578231</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="n">
+        <v>1.2</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="n">
+        <v>1.002237136465324</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="n">
+        <v>1.018353514109951</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="n">
+        <v>1.101965279442938</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="n">
+        <v>1.46</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="n">
+        <v>1.235</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="n">
+        <v>1.183333333333333</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="n">
+        <v>1.61</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="n">
+        <v>1.533333333333333</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="n">
+        <v>0.4875</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="n">
+        <v>2.1186440677966</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="n">
+        <v>1.955</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="n">
+        <v>1.68</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="n">
+        <v>0.4829782608695652</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="n">
+        <v>0.5860217391304348</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="n">
+        <v>0.3916326530612245</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="n">
+        <v>0.6111111111111112</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="n">
+        <v>0.9230769230769231</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="n">
+        <v>1.164315151769025</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="n">
+        <v>1.309333333333333</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="n">
+        <v>1.06</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="n">
+        <v>1.206666666666667</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="n">
+        <v>1.054293758851389</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="n">
+        <v>1.0375</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="n">
+        <v>1.129625</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="n">
+        <v>1.1875</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="n">
+        <v>2.333333333333333</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="n">
+        <v>1.205</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="n">
+        <v>1.2136875</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="n">
+        <v>1.2115625</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="n">
+        <v>1.139176470588235</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="n">
+        <v>1.042388888888889</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="n">
+        <v>1.087547798740395</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="n">
+        <v>0.9948992481203011</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="n">
+        <v>0.9705679943988564</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="n">
+        <v>0.9567543859649122</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="n">
+        <v>0.9569473684210525</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="n">
+        <v>1.052631578947368</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="n">
+        <v>1.017125</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="n">
+        <v>1.048</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="n">
+        <v>1.215789473684211</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="n">
+        <v>0.9956504338545761</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="n">
+        <v>1.028890170900142</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="n">
+        <v>1.022513368983957</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="n">
+        <v>1.138493150684931</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="n">
+        <v>1.023875</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="n">
+        <v>1.098765432098765</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="n">
+        <v>1.389932381667919</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="n">
+        <v>1.032036082474227</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="n">
+        <v>0.9228245614035104</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="n">
+        <v>1.321428571428571</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="n">
+        <v>1.1561875</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="n">
+        <v>1.285714285714286</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="n">
+        <v>1.0925</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="n">
+        <v>1.044252873563218</v>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="n">
+        <v>0.9803030303030303</v>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="n">
+        <v>1.179039301310044</v>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="n">
+        <v>1.076929246123686</v>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="n">
+        <v>1.088077934787474</v>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="n">
+        <v>1.082526315789474</v>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="n">
+        <v>1.171894736842105</v>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="n">
+        <v>0.2215527733259426</v>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="n">
+        <v>1.709157894736842</v>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="n">
+        <v>1.521368421052631</v>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="n">
+        <v>1.602526315789474</v>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="n">
+        <v>4.489578947368421</v>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="n">
+        <v>1.944421052631579</v>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="n">
+        <v>1.295263157894737</v>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="n">
+        <v>4.606790289121734</v>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="n">
+        <v>1.37</v>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="n">
+        <v>2.14</v>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="n">
+        <v>0.9652509652509653</v>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="n">
+        <v>0.9784735812133072</v>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="n">
+        <v>0.9039956608208281</v>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="n">
+        <v>1.38401731378522</v>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="n">
+        <v>1.301476921113911</v>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="n">
+        <v>1.411325192846518</v>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="n">
+        <v>1.929625425652667</v>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="n">
+        <v>2.015393124822253</v>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="n">
+        <v>2.742822870632321</v>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="n">
+        <v>1.753614442924429</v>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="n">
+        <v>6.5832786490285</v>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="n">
+        <v>1.887620844696939</v>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="n">
+        <v>1.266261460462019</v>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="n">
+        <v>3.654458333333333</v>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="n">
+        <v>1.286222340868201</v>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="n">
+        <v>1.197005523658542</v>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="n">
+        <v>1.241893202166627</v>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="n">
+        <v>1.934083969102072</v>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="n">
+        <v>7.628518413137146</v>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="n">
+        <v>0.07499999999999929</v>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="n">
+        <v>1.049203896717607</v>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="n">
+        <v>8.315000000000001</v>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="n">
+        <v>11.9</v>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="n">
+        <v>0.3333</v>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="n">
+        <v>0.275</v>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="n">
+        <v>1.041666666666667</v>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="n">
+        <v>0.7638888888888888</v>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="n">
+        <v>0.9412</v>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="n">
+        <v>0.9167000000000001</v>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="n">
+        <v>0.7142857142857143</v>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="n">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="n">
+        <v>20.41666666666667</v>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="n">
+        <v>20.5</v>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="n">
+        <v>19.41666666666667</v>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="n">
+        <v>238.2449979782104</v>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="n">
+        <v>311.345</v>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="n">
+        <v>1765.555</v>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="n">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="n">
+        <v>8.495912050318455e-05</v>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="n">
+        <v>1.001070326764465</v>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="n">
+        <v>35.3111</v>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="n">
+        <v>1.074944444444444</v>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="n">
+        <v>1.957428571428572</v>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="n">
+        <v>2.870571428571429</v>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="n">
+        <v>112.1267142857143</v>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="n">
+        <v>1.062777777777778</v>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="n">
+        <v>1.085833333333333</v>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="n">
+        <v>0.9253333333333333</v>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" t="n">
+        <v>1.612653791509528</v>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" t="n">
+        <v>1.645641134450872</v>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" t="n">
+        <v>1.11575</v>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" t="n">
+        <v>1.6964375</v>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" t="n">
+        <v>1.075465277777778</v>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" t="n">
+        <v>2.6443125</v>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" t="n">
+        <v>0.8165289256198299</v>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" t="n">
+        <v>0.92012779552716</v>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" t="n">
+        <v>0.9724542838577928</v>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" t="n">
+        <v>0.8847944514062934</v>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" t="n">
+        <v>0.9392592592592593</v>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" t="n">
+        <v>0.65</v>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" t="n">
+        <v>0.9791666666666665</v>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" t="n">
+        <v>1.156866161616162</v>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" t="n">
+        <v>1.111740111740112</v>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" t="n">
+        <v>1.241322916666667</v>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" t="n">
+        <v>1.067555555555556</v>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" t="n">
+        <v>1.923076923076923</v>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" t="n">
+        <v>1.128045977011494</v>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" t="n">
+        <v>1.0022</v>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" t="n">
+        <v>1.0012</v>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" t="n">
+        <v>0.7223529411764705</v>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" t="n">
+        <v>1.398518518518518</v>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" t="n">
+        <v>1.03</v>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" t="n">
+        <v>0.9622641509433965</v>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" t="n">
+        <v>1.616323529411765</v>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" t="n">
+        <v>1.36474622770919</v>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" t="n">
+        <v>1.0431</v>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" t="n">
+        <v>1.43884892086331</v>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" t="n">
+        <v>0.18</v>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" t="n">
+        <v>0.15</v>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" t="n">
+        <v>1.23529705882355</v>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" t="n">
+        <v>1.35295</v>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" t="n">
+        <v>0.9285714285714286</v>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" t="n">
+        <v>0.7</v>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" t="n">
+        <v>0.8714444444444445</v>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" t="n">
+        <v>1.03448275862069</v>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" t="n">
+        <v>1.333333333333333</v>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" t="n">
+        <v>1.105263157894737</v>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" t="n">
+        <v>1.456310679611651</v>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" t="n">
+        <v>1.363636363636364</v>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" t="n">
+        <v>1.428571428571429</v>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" t="n">
+        <v>1.8001800180018</v>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" t="n">
+        <v>0.8856499999999999</v>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" t="n">
+        <v>0.9840896763821895</v>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" t="n">
+        <v>0.9313157894736841</v>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" t="n">
+        <v>0.8047368421052632</v>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" t="n">
+        <v>0.976802605821255</v>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" t="n">
+        <v>1.019740259234822</v>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" t="n">
+        <v>1.03915</v>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" t="n">
+        <v>1.3333125</v>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" t="n">
+        <v>1.1354375</v>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" t="n">
+        <v>1.005917159763314</v>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" t="n">
+        <v>0.9071117561683598</v>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" t="n">
+        <v>0.9781427363844946</v>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" t="n">
+        <v>1.159776231409469</v>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264" t="n">
+        <v>1.024705221785514</v>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265" t="n">
+        <v>1.038011695906433</v>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266" t="n">
+        <v>1.012291666666667</v>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267" t="n">
+        <v>0.999278350515464</v>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268" t="n">
+        <v>1.005</v>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269" t="n">
+        <v>1.011111111111111</v>
+      </c>
+    </row>
+    <row r="270">
+      <c r="A270" t="n">
+        <v>1.031111111111111</v>
+      </c>
+    </row>
+    <row r="271">
+      <c r="A271" t="n">
+        <v>1.015217391304348</v>
+      </c>
+    </row>
+    <row r="272">
+      <c r="A272" t="n">
+        <v>1.323529411764706</v>
+      </c>
+    </row>
+    <row r="273">
+      <c r="A273" t="n">
+        <v>0.3058823529411765</v>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274" t="n">
+        <v>0.9210526315789473</v>
+      </c>
+    </row>
+    <row r="275">
+      <c r="A275" t="n">
+        <v>0.9928888888888889</v>
+      </c>
+    </row>
+    <row r="276">
+      <c r="A276" t="n">
+        <v>1.037</v>
+      </c>
+    </row>
+    <row r="277">
+      <c r="A277" t="n">
+        <v>6.441612246331</v>
+      </c>
+    </row>
+    <row r="278">
+      <c r="A278" t="n">
+        <v>6.262961235299454</v>
+      </c>
+    </row>
+    <row r="279">
+      <c r="A279" t="n">
+        <v>1.3125</v>
+      </c>
+    </row>
+    <row r="280">
+      <c r="A280" t="n">
+        <v>12.02424752093617</v>
+      </c>
+    </row>
+    <row r="281">
+      <c r="A281" t="n">
+        <v>5.296115753636645</v>
+      </c>
+    </row>
+    <row r="282">
+      <c r="A282" t="n">
+        <v>2.801875000000001</v>
+      </c>
+    </row>
+    <row r="283">
+      <c r="A283" t="n">
+        <v>0.873</v>
+      </c>
+    </row>
+    <row r="284">
+      <c r="A284" t="n">
+        <v>0.8545</v>
+      </c>
+    </row>
+    <row r="285">
+      <c r="A285" t="n">
+        <v>21.50537634408602</v>
+      </c>
+    </row>
+    <row r="286">
+      <c r="A286" t="n">
+        <v>0.7765151515151526</v>
+      </c>
+    </row>
+    <row r="287">
+      <c r="A287" t="n">
+        <v>1.02974828375286</v>
+      </c>
+    </row>
+    <row r="288">
+      <c r="A288" t="n">
+        <v>1.001684210526316</v>
+      </c>
+    </row>
+    <row r="289">
+      <c r="A289" t="n">
+        <v>1.830950000000001</v>
+      </c>
+    </row>
+    <row r="290">
+      <c r="A290" t="n">
+        <v>0.9184</v>
+      </c>
+    </row>
+    <row r="291">
+      <c r="A291" t="n">
+        <v>1.0728</v>
+      </c>
+    </row>
+    <row r="292">
+      <c r="A292" t="n">
+        <v>1.565</v>
+      </c>
+    </row>
+    <row r="293">
+      <c r="A293" t="n">
+        <v>1.755</v>
+      </c>
+    </row>
+    <row r="294">
+      <c r="A294" t="n">
+        <v>1.073733333333333</v>
+      </c>
+    </row>
+    <row r="295">
+      <c r="A295" t="n">
+        <v>2.326086956521739</v>
+      </c>
+    </row>
+    <row r="296">
+      <c r="A296" t="n">
+        <v>4.1333</v>
+      </c>
+    </row>
+    <row r="297">
+      <c r="A297" t="n">
+        <v>2.53125</v>
+      </c>
+    </row>
+    <row r="298">
+      <c r="A298" t="n">
+        <v>1.609375</v>
+      </c>
+    </row>
+    <row r="299">
+      <c r="A299" t="n">
+        <v>1.5467</v>
+      </c>
+    </row>
+    <row r="300">
+      <c r="A300" t="n">
+        <v>1.976190476190476</v>
+      </c>
+    </row>
+    <row r="301">
+      <c r="A301" t="n">
+        <v>0.7913</v>
+      </c>
+    </row>
+    <row r="302">
+      <c r="A302" t="n">
+        <v>1.243445692883895</v>
+      </c>
+    </row>
+    <row r="303">
+      <c r="A303" t="n">
+        <v>0.6776000000000001</v>
+      </c>
+    </row>
+    <row r="304">
+      <c r="A304" t="n">
+        <v>1.099547511312217</v>
+      </c>
+    </row>
+    <row r="305">
+      <c r="A305" t="n">
+        <v>0.8928571428571429</v>
+      </c>
+    </row>
+    <row r="306">
+      <c r="A306" t="n">
+        <v>1.260869565217391</v>
+      </c>
+    </row>
+    <row r="307">
+      <c r="A307" t="n">
+        <v>1.45</v>
+      </c>
+    </row>
+    <row r="308">
+      <c r="A308" t="n">
+        <v>1.4</v>
+      </c>
+    </row>
+    <row r="309">
+      <c r="A309" t="n">
+        <v>1.047619047619048</v>
+      </c>
+    </row>
+    <row r="310">
+      <c r="A310" t="n">
+        <v>1.136363636363636</v>
+      </c>
+    </row>
+    <row r="311">
+      <c r="A311" t="n">
+        <v>1.1285</v>
+      </c>
+    </row>
+    <row r="312">
+      <c r="A312" t="n">
+        <v>1.013647058823529</v>
+      </c>
+    </row>
+    <row r="313">
+      <c r="A313" t="n">
+        <v>0.7073170731707317</v>
+      </c>
+    </row>
+    <row r="314">
+      <c r="A314" t="n">
+        <v>1.15</v>
+      </c>
+    </row>
+    <row r="315">
+      <c r="A315" t="n">
+        <v>1.297222222222222</v>
+      </c>
+    </row>
+    <row r="316">
+      <c r="A316" t="n">
+        <v>5.0217</v>
+      </c>
+    </row>
+    <row r="317">
+      <c r="A317" t="n">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="318">
+      <c r="A318" t="n">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="319">
+      <c r="A319" t="n">
+        <v>1.29375</v>
+      </c>
+    </row>
+    <row r="320">
+      <c r="A320" t="n">
+        <v>1.57</v>
+      </c>
+    </row>
+    <row r="321">
+      <c r="A321" t="n">
+        <v>1.105</v>
+      </c>
+    </row>
+    <row r="322">
+      <c r="A322" t="n">
+        <v>1.0663</v>
+      </c>
+    </row>
+    <row r="323">
+      <c r="A323" t="n">
+        <v>1.254355400696864</v>
+      </c>
+    </row>
+    <row r="324">
+      <c r="A324" t="n">
+        <v>1.434782608695652</v>
+      </c>
+    </row>
+    <row r="325">
+      <c r="A325" t="n">
+        <v>1.325842696629213</v>
+      </c>
+    </row>
+    <row r="326">
+      <c r="A326" t="n">
+        <v>1.004431818181818</v>
+      </c>
+    </row>
+    <row r="327">
+      <c r="A327" t="n">
+        <v>1.009545454545455</v>
+      </c>
+    </row>
+    <row r="328">
+      <c r="A328" t="n">
+        <v>1.012359550561798</v>
+      </c>
+    </row>
+    <row r="329">
+      <c r="A329" t="n">
+        <v>1.173125</v>
+      </c>
+    </row>
+    <row r="330">
+      <c r="A330" t="n">
+        <v>0.9871951219512195</v>
+      </c>
+    </row>
+    <row r="331">
+      <c r="A331" t="n">
+        <v>1.147975</v>
+      </c>
+    </row>
+    <row r="332">
+      <c r="A332" t="n">
+        <v>2.531645569620253</v>
+      </c>
+    </row>
+    <row r="333">
+      <c r="A333" t="n">
+        <v>5.555555555555555</v>
+      </c>
+    </row>
+    <row r="334">
+      <c r="A334" t="n">
+        <v>0.9523809523809523</v>
+      </c>
+    </row>
+    <row r="335">
+      <c r="A335" t="n">
+        <v>1.01</v>
+      </c>
+    </row>
+    <row r="336">
+      <c r="A336" t="n">
+        <v>1.176333333333333</v>
+      </c>
+    </row>
+    <row r="337">
+      <c r="A337" t="n">
+        <v>1.27219833333335</v>
+      </c>
+    </row>
+    <row r="338">
+      <c r="A338" t="n">
+        <v>1.1372</v>
+      </c>
+    </row>
+    <row r="339">
+      <c r="A339" t="n">
+        <v>1.0245</v>
+      </c>
+    </row>
+    <row r="340">
+      <c r="A340" t="n">
+        <v>1.086135338345867</v>
+      </c>
+    </row>
+    <row r="341">
+      <c r="A341" t="n">
+        <v>1.056612903225806</v>
+      </c>
+    </row>
+    <row r="342">
+      <c r="A342" t="n">
+        <v>1.072204301075269</v>
+      </c>
+    </row>
+    <row r="343">
+      <c r="A343" t="n">
+        <v>1.080941176470588</v>
+      </c>
+    </row>
+    <row r="344">
+      <c r="A344" t="n">
+        <v>1.144470588235294</v>
+      </c>
+    </row>
+    <row r="345">
+      <c r="A345" t="n">
+        <v>6.666666666666667</v>
+      </c>
+    </row>
+    <row r="346">
+      <c r="A346" t="n">
+        <v>2.222222222222222</v>
+      </c>
+    </row>
+    <row r="347">
+      <c r="A347" t="n">
+        <v>1.009180280706798</v>
+      </c>
+    </row>
+    <row r="348">
+      <c r="A348" t="n">
+        <v>1.009722222222222</v>
+      </c>
+    </row>
+    <row r="349">
+      <c r="A349" t="n">
+        <v>1.01010101010101</v>
+      </c>
+    </row>
+    <row r="350">
+      <c r="A350" t="n">
+        <v>1.153846153846154</v>
+      </c>
+    </row>
+    <row r="351">
+      <c r="A351" t="n">
+        <v>3.177</v>
+      </c>
+    </row>
+    <row r="352">
+      <c r="A352" t="n">
+        <v>1.64916004403234</v>
+      </c>
+    </row>
+    <row r="353">
+      <c r="A353" t="n">
+        <v>0.9941176470588236</v>
+      </c>
+    </row>
+    <row r="354">
+      <c r="A354" t="n">
+        <v>1.114285714285714</v>
+      </c>
+    </row>
+    <row r="355">
+      <c r="A355" t="n">
+        <v>1.083482689692428</v>
+      </c>
+    </row>
+    <row r="356">
+      <c r="A356" t="n">
+        <v>1.003092869681518</v>
+      </c>
+    </row>
+    <row r="357">
+      <c r="A357" t="n">
+        <v>1.053463260468791</v>
+      </c>
+    </row>
+    <row r="358">
+      <c r="A358" t="n">
+        <v>1.045888138405023</v>
+      </c>
+    </row>
+    <row r="359">
+      <c r="A359" t="n">
+        <v>1.137873563218391</v>
+      </c>
+    </row>
+    <row r="360">
+      <c r="A360" t="n">
+        <v>1.057647058823529</v>
+      </c>
+    </row>
+    <row r="361">
+      <c r="A361" t="n">
+        <v>1.013333333333333</v>
+      </c>
+    </row>
+    <row r="362">
+      <c r="A362" t="n">
+        <v>1.039130434782609</v>
+      </c>
+    </row>
+    <row r="363">
+      <c r="A363" t="n">
+        <v>0.99156641448592</v>
+      </c>
+    </row>
+    <row r="364">
+      <c r="A364" t="n">
+        <v>1.015685321634592</v>
+      </c>
+    </row>
+    <row r="365">
+      <c r="A365" t="n">
+        <v>1.016989795918367</v>
+      </c>
+    </row>
+    <row r="366">
+      <c r="A366" t="n">
+        <v>1.1541</v>
+      </c>
+    </row>
+    <row r="367">
+      <c r="A367" t="n">
+        <v>1.162790697674419</v>
+      </c>
+    </row>
+    <row r="368">
+      <c r="A368" t="n">
+        <v>1.249951341040912</v>
+      </c>
+    </row>
+    <row r="369">
+      <c r="A369" t="n">
+        <v>0.992</v>
+      </c>
+    </row>
+    <row r="370">
+      <c r="A370" t="n">
+        <v>0.764</v>
+      </c>
+    </row>
+    <row r="371">
+      <c r="A371" t="n">
+        <v>1.05</v>
+      </c>
+    </row>
+    <row r="372">
+      <c r="A372" t="n">
+        <v>1.047222222222222</v>
+      </c>
+    </row>
+    <row r="373">
+      <c r="A373" t="n">
+        <v>1.021505376344086</v>
+      </c>
+    </row>
+    <row r="374">
+      <c r="A374" t="n">
+        <v>0.73775</v>
+      </c>
+    </row>
+    <row r="375">
+      <c r="A375" t="n">
+        <v>0.98575</v>
+      </c>
+    </row>
+    <row r="376">
+      <c r="A376" t="n">
+        <v>1.6528637121818</v>
+      </c>
+    </row>
+    <row r="377">
+      <c r="A377" t="n">
+        <v>1.23355</v>
+      </c>
+    </row>
+    <row r="378">
+      <c r="A378" t="n">
+        <v>0.7855500000000001</v>
+      </c>
+    </row>
+    <row r="379">
+      <c r="A379" t="n">
+        <v>1.097701149425287</v>
+      </c>
+    </row>
+    <row r="380">
+      <c r="A380" t="n">
+        <v>1.054597701149425</v>
+      </c>
+    </row>
+    <row r="381">
+      <c r="A381" t="n">
+        <v>1.061111111111111</v>
+      </c>
+    </row>
+    <row r="382">
+      <c r="A382" t="n">
+        <v>0.739616666666675</v>
+      </c>
+    </row>
+    <row r="383">
+      <c r="A383" t="n">
+        <v>0.9852500000000001</v>
+      </c>
+    </row>
+    <row r="384">
+      <c r="A384" t="n">
+        <v>1.01215</v>
+      </c>
+    </row>
+    <row r="385">
+      <c r="A385" t="n">
+        <v>1.065894736842105</v>
+      </c>
+    </row>
+    <row r="386">
+      <c r="A386" t="n">
+        <v>1.148421052631579</v>
+      </c>
+    </row>
+    <row r="387">
+      <c r="A387" t="n">
+        <v>1.236947368421053</v>
+      </c>
+    </row>
+    <row r="388">
+      <c r="A388" t="n">
+        <v>1.645548790521639</v>
+      </c>
+    </row>
+    <row r="389">
+      <c r="A389" t="n">
+        <v>0.7999360051195904</v>
+      </c>
+    </row>
+    <row r="390">
+      <c r="A390" t="n">
+        <v>1.0711</v>
+      </c>
+    </row>
+    <row r="391">
+      <c r="A391" t="n">
+        <v>1.038913043478261</v>
+      </c>
+    </row>
+    <row r="392">
+      <c r="A392" t="n">
+        <v>1.0568938582028</v>
+      </c>
+    </row>
+    <row r="393">
+      <c r="A393" t="n">
+        <v>0.97615</v>
+      </c>
+    </row>
+    <row r="394">
+      <c r="A394" t="n">
+        <v>1.0326</v>
+      </c>
+    </row>
+    <row r="395">
+      <c r="A395" t="n">
+        <v>1.034636945020853</v>
+      </c>
+    </row>
+    <row r="396">
+      <c r="A396" t="n">
+        <v>0.7892</v>
+      </c>
+    </row>
+    <row r="397">
+      <c r="A397" t="n">
+        <v>1.08985854341735</v>
+      </c>
+    </row>
+    <row r="398">
+      <c r="A398" t="n">
+        <v>0.9722499999999999</v>
+      </c>
+    </row>
+    <row r="399">
+      <c r="A399" t="n">
+        <v>1.0594</v>
+      </c>
+    </row>
+    <row r="400">
+      <c r="A400" t="n">
+        <v>1.02130205659755</v>
+      </c>
+    </row>
+    <row r="401">
+      <c r="A401" t="n">
+        <v>0.9591500000000001</v>
+      </c>
+    </row>
+    <row r="402">
+      <c r="A402" t="n">
+        <v>0.9853000000000001</v>
+      </c>
+    </row>
+    <row r="403">
+      <c r="A403" t="n">
+        <v>1.29021164972635</v>
+      </c>
+    </row>
+    <row r="404">
+      <c r="A404" t="n">
+        <v>1.10455</v>
+      </c>
+    </row>
+    <row r="405">
+      <c r="A405" t="n">
+        <v>1.32415</v>
+      </c>
+    </row>
+    <row r="406">
+      <c r="A406" t="n">
+        <v>1.13572352941175</v>
+      </c>
+    </row>
+    <row r="407">
+      <c r="A407" t="n">
+        <v>0.9505</v>
+      </c>
+    </row>
+    <row r="408">
+      <c r="A408" t="n">
+        <v>1.0208</v>
+      </c>
+    </row>
+    <row r="409">
+      <c r="A409" t="n">
+        <v>1.2493</v>
+      </c>
+    </row>
+    <row r="410">
+      <c r="A410" t="n">
+        <v>0.8856000000000001</v>
+      </c>
+    </row>
+    <row r="411">
+      <c r="A411" t="n">
+        <v>1.0889</v>
+      </c>
+    </row>
+    <row r="412">
+      <c r="A412" t="n">
+        <v>1.2060243283327</v>
+      </c>
+    </row>
+    <row r="413">
+      <c r="A413" t="n">
+        <v>0.9431999999999999</v>
+      </c>
+    </row>
+    <row r="414">
+      <c r="A414" t="n">
+        <v>1.1273</v>
+      </c>
+    </row>
+    <row r="415">
+      <c r="A415" t="n">
+        <v>0.4966666666666666</v>
+      </c>
+    </row>
+    <row r="416">
+      <c r="A416" t="n">
+        <v>0.99249166666667</v>
+      </c>
+    </row>
+    <row r="417">
+      <c r="A417" t="n">
+        <v>0.9992</v>
+      </c>
+    </row>
+    <row r="418">
+      <c r="A418" t="n">
+        <v>0.9978</v>
+      </c>
+    </row>
+    <row r="419">
+      <c r="A419" t="n">
+        <v>1.075268817204301</v>
+      </c>
+    </row>
+    <row r="420">
+      <c r="A420" t="n">
+        <v>1.4738</v>
+      </c>
+    </row>
+    <row r="421">
+      <c r="A421" t="n">
+        <v>1.4521</v>
+      </c>
+    </row>
+    <row r="422">
+      <c r="A422" t="n">
+        <v>1.008</v>
+      </c>
+    </row>
+    <row r="423">
+      <c r="A423" t="n">
+        <v>1.153846153846154</v>
+      </c>
+    </row>
+    <row r="424">
+      <c r="A424" t="n">
+        <v>3.12569285714285</v>
+      </c>
+    </row>
+    <row r="425">
+      <c r="A425" t="n">
+        <v>1.553</v>
+      </c>
+    </row>
+    <row r="426">
+      <c r="A426" t="n">
+        <v>1.383925</v>
+      </c>
+    </row>
+    <row r="427">
+      <c r="A427" t="n">
+        <v>2.8039382352941</v>
+      </c>
+    </row>
+    <row r="428">
+      <c r="A428" t="n">
+        <v>1.29445</v>
+      </c>
+    </row>
+    <row r="429">
+      <c r="A429" t="n">
+        <v>2.04415</v>
+      </c>
+    </row>
+    <row r="430">
+      <c r="A430" t="n">
+        <v>1.111125</v>
+      </c>
+    </row>
+    <row r="431">
+      <c r="A431" t="n">
+        <v>1.10125</v>
+      </c>
+    </row>
+    <row r="432">
+      <c r="A432" t="n">
+        <v>1.150196428571431</v>
+      </c>
+    </row>
+    <row r="433">
+      <c r="A433" t="n">
+        <v>1.1435</v>
+      </c>
+    </row>
+    <row r="434">
+      <c r="A434" t="n">
+        <v>1.063333333333333</v>
+      </c>
+    </row>
+    <row r="435">
+      <c r="A435" t="n">
+        <v>2.456</v>
+      </c>
+    </row>
+    <row r="436">
+      <c r="A436" t="n">
+        <v>2.2196</v>
+      </c>
+    </row>
+    <row r="437">
+      <c r="A437" t="n">
+        <v>1.64105</v>
+      </c>
+    </row>
+    <row r="438">
+      <c r="A438" t="n">
+        <v>1.334</v>
+      </c>
+    </row>
+    <row r="439">
+      <c r="A439" t="n">
+        <v>1.1136</v>
+      </c>
+    </row>
+    <row r="440">
+      <c r="A440" t="n">
+        <v>1.0453</v>
+      </c>
+    </row>
+    <row r="441">
+      <c r="A441" t="n">
+        <v>2.5143</v>
+      </c>
+    </row>
+    <row r="442">
+      <c r="A442" t="n">
+        <v>3.3409</v>
+      </c>
+    </row>
+    <row r="443">
+      <c r="A443" t="n">
+        <v>1.2507</v>
+      </c>
+    </row>
+    <row r="444">
+      <c r="A444" t="n">
+        <v>1.180555555555556</v>
+      </c>
+    </row>
+    <row r="445">
+      <c r="A445" t="n">
+        <v>1.586666666666667</v>
+      </c>
+    </row>
+    <row r="446">
+      <c r="A446" t="n">
+        <v>11.76470588235294</v>
+      </c>
+    </row>
+    <row r="447">
+      <c r="A447" t="n">
+        <v>1.661129568106313</v>
+      </c>
+    </row>
+    <row r="448">
+      <c r="A448" t="n">
+        <v>1.24</v>
+      </c>
+    </row>
+    <row r="449">
+      <c r="A449" t="n">
+        <v>0.98</v>
+      </c>
+    </row>
+    <row r="450">
+      <c r="A450" t="n">
+        <v>1.273242841204909</v>
+      </c>
+    </row>
+    <row r="451">
+      <c r="A451" t="n">
+        <v>1.026574917163008</v>
+      </c>
+    </row>
+    <row r="452">
+      <c r="A452" t="n">
+        <v>0.9628</v>
+      </c>
+    </row>
+    <row r="453">
+      <c r="A453" t="n">
+        <v>0.9878</v>
+      </c>
+    </row>
+    <row r="454">
+      <c r="A454" t="n">
+        <v>0.9887</v>
+      </c>
+    </row>
+    <row r="455">
+      <c r="A455" t="n">
+        <v>0.96</v>
+      </c>
+    </row>
+    <row r="456">
+      <c r="A456" t="n">
+        <v>0.9836</v>
+      </c>
+    </row>
+    <row r="457">
+      <c r="A457" t="n">
+        <v>0.993</v>
+      </c>
+    </row>
+    <row r="458">
+      <c r="A458" t="n">
+        <v>0.9439</v>
+      </c>
+    </row>
+    <row r="459">
+      <c r="A459" t="n">
+        <v>0.9883</v>
+      </c>
+    </row>
+    <row r="460">
+      <c r="A460" t="n">
+        <v>0.9799</v>
+      </c>
+    </row>
+    <row r="461">
+      <c r="A461" t="n">
+        <v>0.95802222222222</v>
+      </c>
+    </row>
+    <row r="462">
+      <c r="A462" t="n">
+        <v>0.9778</v>
+      </c>
+    </row>
+    <row r="463">
+      <c r="A463" t="n">
+        <v>0.9961</v>
+      </c>
+    </row>
+    <row r="464">
+      <c r="A464" t="n">
+        <v>0.9356</v>
+      </c>
+    </row>
+    <row r="465">
+      <c r="A465" t="n">
+        <v>0.9667</v>
+      </c>
+    </row>
+    <row r="466">
+      <c r="A466" t="n">
+        <v>1.372277316268532</v>
+      </c>
+    </row>
+    <row r="467">
+      <c r="A467" t="n">
+        <v>1.2144</v>
+      </c>
+    </row>
+    <row r="468">
+      <c r="A468" t="n">
+        <v>1.051428571428571</v>
+      </c>
+    </row>
+    <row r="469">
+      <c r="A469" t="n">
+        <v>0.9875156054931337</v>
+      </c>
+    </row>
+    <row r="470">
+      <c r="A470" t="n">
+        <v>1.024739583333333</v>
+      </c>
+    </row>
+    <row r="471">
+      <c r="A471" t="n">
+        <v>0.9404761904761905</v>
+      </c>
+    </row>
+    <row r="472">
+      <c r="A472" t="n">
+        <v>1.481927710843373</v>
+      </c>
+    </row>
+    <row r="473">
+      <c r="A473" t="n">
+        <v>1.227642276422764</v>
+      </c>
+    </row>
+    <row r="474">
+      <c r="A474" t="n">
+        <v>0.06521739130434782</v>
+      </c>
+    </row>
+    <row r="475">
+      <c r="A475" t="n">
+        <v>1.222222222222222</v>
+      </c>
+    </row>
+    <row r="476">
+      <c r="A476" t="n">
+        <v>1.051818181818182</v>
+      </c>
+    </row>
+    <row r="477">
+      <c r="A477" t="n">
+        <v>1.6469</v>
+      </c>
+    </row>
+    <row r="478">
+      <c r="A478" t="n">
+        <v>0.9186875000000001</v>
+      </c>
+    </row>
+    <row r="479">
+      <c r="A479" t="n">
+        <v>1.188118811881177</v>
+      </c>
+    </row>
+    <row r="480">
+      <c r="A480" t="n">
+        <v>1.176470588235294</v>
+      </c>
+    </row>
+    <row r="481">
+      <c r="A481" t="n">
+        <v>1.379310344827586</v>
+      </c>
+    </row>
+    <row r="482">
+      <c r="A482" t="n">
+        <v>0.05521811154058531</v>
+      </c>
+    </row>
+    <row r="483">
+      <c r="A483" t="n">
+        <v>0.05696382796923953</v>
+      </c>
+    </row>
+    <row r="484">
+      <c r="A484" t="n">
+        <v>0.06060606060606061</v>
+      </c>
+    </row>
+    <row r="485">
+      <c r="A485" t="n">
+        <v>1.433962264150943</v>
+      </c>
+    </row>
+    <row r="486">
+      <c r="A486" t="n">
+        <v>1.142857142857143</v>
+      </c>
+    </row>
+    <row r="487">
+      <c r="A487" t="n">
+        <v>1.36936936936937</v>
+      </c>
+    </row>
+    <row r="488">
+      <c r="A488" t="n">
+        <v>1.067318562735053</v>
+      </c>
+    </row>
+    <row r="489">
+      <c r="A489" t="n">
+        <v>1.083552547063557</v>
+      </c>
+    </row>
+    <row r="490">
+      <c r="A490" t="n">
+        <v>1.176421052631579</v>
+      </c>
+    </row>
+    <row r="491">
+      <c r="A491" t="n">
+        <v>1.104253086419756</v>
+      </c>
+    </row>
+    <row r="492">
+      <c r="A492" t="n">
+        <v>0.8333333333333334</v>
+      </c>
+    </row>
+    <row r="493">
+      <c r="A493" t="n">
+        <v>0.4761904761904762</v>
+      </c>
+    </row>
+    <row r="494">
+      <c r="A494" t="n">
+        <v>0.5263157894736842</v>
+      </c>
+    </row>
+    <row r="495">
+      <c r="A495" t="n">
+        <v>1.046148213048083</v>
+      </c>
+    </row>
+    <row r="496">
+      <c r="A496" t="n">
+        <v>0.4422137218917903</v>
+      </c>
+    </row>
+    <row r="497">
+      <c r="A497" t="n">
+        <v>0.3083421981715308</v>
+      </c>
+    </row>
+    <row r="498">
+      <c r="A498" t="n">
+        <v>0.2521</v>
+      </c>
+    </row>
+    <row r="499">
+      <c r="A499" t="n">
+        <v>1.897304622797772</v>
+      </c>
+    </row>
+    <row r="500">
+      <c r="A500" t="n">
+        <v>1.265346087218498</v>
+      </c>
+    </row>
+    <row r="501">
+      <c r="A501" t="n">
+        <v>1.380670611439842</v>
+      </c>
+    </row>
+    <row r="502">
+      <c r="A502" t="n">
+        <v>1.462904911180773</v>
+      </c>
+    </row>
+    <row r="503">
+      <c r="A503" t="n">
+        <v>0.9974088014033367</v>
+      </c>
+    </row>
+    <row r="504">
+      <c r="A504" t="n">
+        <v>1.01515306122449</v>
+      </c>
+    </row>
+    <row r="505">
+      <c r="A505" t="n">
+        <v>1.017908163265306</v>
+      </c>
+    </row>
+    <row r="506">
+      <c r="A506" t="n">
+        <v>1.110221510541767</v>
+      </c>
+    </row>
+    <row r="507">
+      <c r="A507" t="n">
+        <v>2.09</v>
+      </c>
+    </row>
+    <row r="508">
+      <c r="A508" t="n">
+        <v>1.818181818181818</v>
+      </c>
+    </row>
+    <row r="509">
+      <c r="A509" t="n">
+        <v>1.049629629629629</v>
+      </c>
+    </row>
+    <row r="510">
+      <c r="A510" t="n">
+        <v>1.077333333333333</v>
+      </c>
+    </row>
+    <row r="511">
+      <c r="A511" t="n">
+        <v>1.000666666666667</v>
+      </c>
+    </row>
+    <row r="512">
+      <c r="A512" t="n">
+        <v>1.035555555555556</v>
+      </c>
+    </row>
+    <row r="513">
+      <c r="A513" t="n">
+        <v>3.491764705882353</v>
+      </c>
+    </row>
+    <row r="514">
+      <c r="A514" t="n">
+        <v>1.2515</v>
+      </c>
+    </row>
+    <row r="515">
+      <c r="A515" t="n">
+        <v>1.3</v>
+      </c>
+    </row>
+    <row r="516">
+      <c r="A516" t="n">
+        <v>1.51135</v>
+      </c>
+    </row>
+    <row r="517">
+      <c r="A517" t="n">
+        <v>2.133333333333333</v>
+      </c>
+    </row>
+    <row r="518">
+      <c r="A518" t="n">
+        <v>0.87</v>
+      </c>
+    </row>
+    <row r="519">
+      <c r="A519" t="n">
+        <v>0.97345</v>
+      </c>
+    </row>
+    <row r="520">
+      <c r="A520" t="n">
+        <v>1.115925</v>
+      </c>
+    </row>
+    <row r="521">
+      <c r="A521" t="n">
+        <v>0.8</v>
+      </c>
+    </row>
+    <row r="522">
+      <c r="A522" t="n">
+        <v>1.130925</v>
+      </c>
+    </row>
+    <row r="523">
+      <c r="A523" t="n">
+        <v>1.142996108949417</v>
+      </c>
+    </row>
+    <row r="524">
+      <c r="A524" t="n">
+        <v>1.05225</v>
+      </c>
+    </row>
+    <row r="525">
+      <c r="A525" t="n">
+        <v>0.5683</v>
+      </c>
+    </row>
+    <row r="526">
+      <c r="A526" t="n">
+        <v>1.134</v>
+      </c>
+    </row>
+    <row r="527">
+      <c r="A527" t="n">
+        <v>1.0655</v>
+      </c>
+    </row>
+    <row r="528">
+      <c r="A528" t="n">
+        <v>1.2154</v>
+      </c>
+    </row>
+    <row r="529">
+      <c r="A529" t="n">
+        <v>1.0875</v>
+      </c>
+    </row>
+    <row r="530">
+      <c r="A530" t="n">
+        <v>1.100917431192661</v>
+      </c>
+    </row>
+    <row r="531">
+      <c r="A531" t="n">
+        <v>0.997</v>
+      </c>
+    </row>
+    <row r="532">
+      <c r="A532" t="n">
+        <v>0.9913</v>
+      </c>
+    </row>
+    <row r="533">
+      <c r="A533" t="n">
+        <v>0.9986</v>
+      </c>
+    </row>
+    <row r="534">
+      <c r="A534" t="n">
+        <v>9.165000000000001</v>
+      </c>
+    </row>
+    <row r="535">
+      <c r="A535" t="n">
+        <v>1.145833333333333</v>
+      </c>
+    </row>
+    <row r="536">
+      <c r="A536" t="n">
+        <v>1.001761363636364</v>
+      </c>
+    </row>
+    <row r="537">
+      <c r="A537" t="n">
+        <v>0.303</v>
+      </c>
+    </row>
+    <row r="538">
+      <c r="A538" t="n">
+        <v>2.943</v>
+      </c>
+    </row>
+    <row r="539">
+      <c r="A539" t="n">
+        <v>1.093662217185824</v>
+      </c>
+    </row>
+    <row r="540">
+      <c r="A540" t="n">
+        <v>0.9082402811130974</v>
+      </c>
+    </row>
+    <row r="541">
+      <c r="A541" t="n">
+        <v>0.9625</v>
+      </c>
+    </row>
+    <row r="542">
+      <c r="A542" t="n">
+        <v>0.7875</v>
+      </c>
+    </row>
+    <row r="543">
+      <c r="A543" t="n">
+        <v>1.2125</v>
+      </c>
+    </row>
+    <row r="544">
+      <c r="A544" t="n">
+        <v>0.8375</v>
+      </c>
+    </row>
+    <row r="545">
+      <c r="A545" t="n">
+        <v>1.15625</v>
+      </c>
+    </row>
+    <row r="546">
+      <c r="A546" t="n">
+        <v>1.081444444444444</v>
+      </c>
+    </row>
+    <row r="547">
+      <c r="A547" t="n">
+        <v>0.9841428571428571</v>
+      </c>
+    </row>
+    <row r="548">
+      <c r="A548" t="n">
+        <v>1.375</v>
+      </c>
+    </row>
+    <row r="549">
+      <c r="A549" t="n">
+        <v>2.8129</v>
+      </c>
+    </row>
+    <row r="550">
+      <c r="A550" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="551">
+      <c r="A551" t="n">
+        <v>1.02725</v>
+      </c>
+    </row>
+    <row r="552">
+      <c r="A552" t="n">
+        <v>1.016842105263158</v>
+      </c>
+    </row>
+    <row r="553">
+      <c r="A553" t="n">
+        <v>1.97940379403794</v>
+      </c>
+    </row>
+    <row r="554">
+      <c r="A554" t="n">
+        <v>20.14</v>
+      </c>
+    </row>
+    <row r="555">
+      <c r="A555" t="n">
+        <v>1.634222222222222</v>
+      </c>
+    </row>
+    <row r="556">
+      <c r="A556" t="n">
+        <v>0.8820618556701031</v>
+      </c>
+    </row>
+    <row r="557">
+      <c r="A557" t="n">
+        <v>1.043777777777778</v>
+      </c>
+    </row>
+    <row r="558">
+      <c r="A558" t="n">
+        <v>1.33965</v>
+      </c>
+    </row>
+    <row r="559">
+      <c r="A559" t="n">
+        <v>1.5142</v>
+      </c>
+    </row>
+    <row r="560">
+      <c r="A560" t="n">
+        <v>1.3431</v>
+      </c>
+    </row>
+    <row r="561">
+      <c r="A561" t="n">
+        <v>1.7115</v>
+      </c>
+    </row>
+    <row r="562">
+      <c r="A562" t="n">
+        <v>1.8504</v>
+      </c>
+    </row>
+    <row r="563">
+      <c r="A563" t="n">
+        <v>0.9892307692307691</v>
+      </c>
+    </row>
+    <row r="564">
+      <c r="A564" t="n">
+        <v>1.006340206185567</v>
+      </c>
+    </row>
+    <row r="565">
+      <c r="A565" t="n">
+        <v>1.7475</v>
+      </c>
+    </row>
+    <row r="566">
+      <c r="A566" t="n">
+        <v>2.0625</v>
+      </c>
+    </row>
+    <row r="567">
+      <c r="A567" t="n">
+        <v>1.1338</v>
+      </c>
+    </row>
+    <row r="568">
+      <c r="A568" t="n">
+        <v>1.19375</v>
+      </c>
+    </row>
+    <row r="569">
+      <c r="A569" t="n">
+        <v>1.625</v>
+      </c>
+    </row>
+    <row r="570">
+      <c r="A570" t="n">
+        <v>1.022988505747126</v>
+      </c>
+    </row>
+    <row r="571">
+      <c r="A571" t="n">
+        <v>0.9487179487179487</v>
+      </c>
+    </row>
+    <row r="572">
+      <c r="A572" t="n">
+        <v>1.245614035087719</v>
+      </c>
+    </row>
+    <row r="573">
+      <c r="A573" t="n">
+        <v>0.9693877551020408</v>
+      </c>
+    </row>
+    <row r="574">
+      <c r="A574" t="n">
+        <v>0.8571428571428571</v>
+      </c>
+    </row>
+    <row r="575">
+      <c r="A575" t="n">
+        <v>0.8271604938271605</v>
+      </c>
+    </row>
+    <row r="576">
+      <c r="A576" t="n">
+        <v>0.7846153846153846</v>
+      </c>
+    </row>
+    <row r="577">
+      <c r="A577" t="n">
+        <v>0.7368421052631579</v>
+      </c>
+    </row>
+    <row r="578">
+      <c r="A578" t="n">
+        <v>0.8780487804878049</v>
+      </c>
+    </row>
+    <row r="579">
+      <c r="A579" t="n">
+        <v>0.9795918367346939</v>
+      </c>
+    </row>
+    <row r="580">
+      <c r="A580" t="n">
+        <v>0.9850746268656716</v>
+      </c>
+    </row>
+    <row r="581">
+      <c r="A581" t="n">
+        <v>0.9791666666666666</v>
+      </c>
+    </row>
+    <row r="582">
+      <c r="A582" t="n">
+        <v>0.9868421052631579</v>
+      </c>
+    </row>
+    <row r="583">
+      <c r="A583" t="n">
+        <v>1.08</v>
+      </c>
+    </row>
+    <row r="584">
+      <c r="A584" t="n">
+        <v>0.9512195121951219</v>
+      </c>
+    </row>
+    <row r="585">
+      <c r="A585" t="n">
+        <v>4.666666666666667</v>
+      </c>
+    </row>
+    <row r="586">
+      <c r="A586" t="n">
+        <v>1.051948051948052</v>
+      </c>
+    </row>
+    <row r="587">
+      <c r="A587" t="n">
+        <v>0.968421052631579</v>
+      </c>
+    </row>
+    <row r="588">
+      <c r="A588" t="n">
+        <v>0.9560439560439561</v>
+      </c>
+    </row>
+    <row r="589">
+      <c r="A589" t="n">
+        <v>1.013157894736842</v>
+      </c>
+    </row>
+    <row r="590">
+      <c r="A590" t="n">
+        <v>0.9333333333333333</v>
+      </c>
+    </row>
+    <row r="591">
+      <c r="A591" t="n">
+        <v>0.95</v>
+      </c>
+    </row>
+    <row r="592">
+      <c r="A592" t="n">
+        <v>0.9666666666666667</v>
+      </c>
+    </row>
+    <row r="593">
+      <c r="A593" t="n">
+        <v>0.9444444444444444</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -4064,7 +9564,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A16"/>
+  <dimension ref="A1:A17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4171,6 +9671,13 @@
     <row r="16">
       <c r="A16" t="n">
         <v>0</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Stand by</t>
+        </is>
       </c>
     </row>
   </sheetData>

--- a/artifacts/consolidado_valores_unicos_mapeo.xlsx
+++ b/artifacts/consolidado_valores_unicos_mapeo.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="434" uniqueCount="434">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="572" uniqueCount="572">
   <si>
     <t>Indicador</t>
   </si>
@@ -96,9 +96,6 @@
     <t>Nivel de Satisfacción -Comunicaciones internas</t>
   </si>
   <si>
-    <t>Nivel de Satisfacción Servicios Prestados - Comunicaciones Internas</t>
-  </si>
-  <si>
     <t>Nivel de Satisfacción del sistema de gestión de calidad</t>
   </si>
   <si>
@@ -108,6 +105,9 @@
     <t>Eficacia en la solicitud documental- por periodo</t>
   </si>
   <si>
+    <t>Eficacia del Plan documental Institucional</t>
+  </si>
+  <si>
     <t>Indice de Frecuencia de accidentalidad</t>
   </si>
   <si>
@@ -153,12 +153,18 @@
     <t>Nivel de Satisfacción Servicios Prestados- Investigación, desarrollo tecnológico, innovación y creación</t>
   </si>
   <si>
+    <t>Nivel de Satisfacción Servicios Prestados - Recursos digitales</t>
+  </si>
+  <si>
     <t>Indexación de bases de datos o SIRES</t>
   </si>
   <si>
     <t>Satisfacción actividades plan de bienestar</t>
   </si>
   <si>
+    <t>ANS documentos operativos Inactivo</t>
+  </si>
+  <si>
     <t>Cumplimiento plan operativo del SGC</t>
   </si>
   <si>
@@ -171,9 +177,15 @@
     <t>Porcentaje de cumplimiento del Acuerdo de Nivel de Servicio (ANS)</t>
   </si>
   <si>
+    <t>Porcentaje de Cumplimiento del Acuerdo de Nivel de Servicio (ANS)</t>
+  </si>
+  <si>
     <t>Índice de satisfacción del estudiante (SSI)</t>
   </si>
   <si>
+    <t>NPS- Net Promotor Score</t>
+  </si>
+  <si>
     <t>(% de solicitudes procesos Pareto)</t>
   </si>
   <si>
@@ -198,9 +210,6 @@
     <t>Utilidad Neta</t>
   </si>
   <si>
-    <t>Inversión en CAPEX de la utilidad anterior (veces)</t>
-  </si>
-  <si>
     <t>Inversión en CAPEX de la utilidad anterior</t>
   </si>
   <si>
@@ -288,9 +297,6 @@
     <t>Portafolio de Proyectos - Metrica</t>
   </si>
   <si>
-    <t>Portafolio de Proyectos</t>
-  </si>
-  <si>
     <t>Cumplimiento de Gestión De Proyectos Cerrados</t>
   </si>
   <si>
@@ -306,10 +312,7 @@
     <t>GreenMetric - Nacional</t>
   </si>
   <si>
-    <t>Permanencia Intersemestral</t>
-  </si>
-  <si>
-    <t>Satisfacción del proceso de grados</t>
+    <t>Tasa de Permanencia Intersemestral</t>
   </si>
   <si>
     <t>Satisfacción del proceso de grados presencial</t>
@@ -324,15 +327,9 @@
     <t>Programas con matriz de resultado de aprendizaje</t>
   </si>
   <si>
-    <t>Subprocesos Con CMI Estructurado</t>
-  </si>
-  <si>
     <t>Subprocesos Con indicadores definidos</t>
   </si>
   <si>
-    <t>Permanencia intersemestral ingresantes</t>
-  </si>
-  <si>
     <t>Tasa de Permanencia Intersemestral de Estudiantes Ingresantes</t>
   </si>
   <si>
@@ -342,9 +339,6 @@
     <t>Áreas con reportes de plan de retos</t>
   </si>
   <si>
-    <t>Informe anual de variación de índice H</t>
-  </si>
-  <si>
     <t>Informe anual de índice H</t>
   </si>
   <si>
@@ -375,39 +369,30 @@
     <t>Eficiencia Emisión De Conceptos Jurídicos (Educación)</t>
   </si>
   <si>
-    <t>Emisión De Conceptos Jurídicos (Jurídicos)</t>
-  </si>
-  <si>
     <t>Eficiencia Emisión De Conceptos Jurídicos (Jurídicos)</t>
   </si>
   <si>
+    <t>Eficiencia Emisión De Conceptos Jurídicos y normativos aplicables</t>
+  </si>
+  <si>
     <t>Oportunidad en la elaboración de contratos</t>
   </si>
   <si>
+    <t>Tasa de oportunidad en la elaboración y firma de contratos</t>
+  </si>
+  <si>
     <t>Satisfacción procesos de Homologaciones</t>
   </si>
   <si>
-    <t>Cantidad de usuarios</t>
-  </si>
-  <si>
     <t>Cantidad de usuarios - (Metrica)</t>
   </si>
   <si>
-    <t>N de personas promedio por evento</t>
-  </si>
-  <si>
     <t>N de personas promedio por evento - (Metrica)</t>
   </si>
   <si>
-    <t>N de horas promedio por evento</t>
-  </si>
-  <si>
     <t>N de horas promedio por evento - (Metrica)</t>
   </si>
   <si>
-    <t>N de horas por solicitud</t>
-  </si>
-  <si>
     <t>N de horas por solicitud - (Metrica)</t>
   </si>
   <si>
@@ -423,13 +408,13 @@
     <t>Satisfacción Institucional por grupo de interes</t>
   </si>
   <si>
+    <t>Satisfacción Institucional por grupos de interés principales (CSAT)</t>
+  </si>
+  <si>
     <t>Relación Estudiante-Docente Tiempo completo</t>
   </si>
   <si>
-    <t>Relación estudiante docente Tiempo Completo Equivalente</t>
-  </si>
-  <si>
-    <t>Docentes contratados</t>
+    <t>Relación estudiante docente TCE (Tiempo Completo Equivalente)</t>
   </si>
   <si>
     <t>Docentes contratados - Metrica</t>
@@ -456,9 +441,6 @@
     <t>Docentes con plan de trabajo asignado</t>
   </si>
   <si>
-    <t>Total docentes por nivel de estudios</t>
-  </si>
-  <si>
     <t>Total docentes por nivel de estudios - Metrica</t>
   </si>
   <si>
@@ -474,18 +456,12 @@
     <t>Cumplimiento del cronograma de actividades deportivas</t>
   </si>
   <si>
-    <t>Participación en Actividades deportivas presenciales</t>
-  </si>
-  <si>
     <t>Participación en Actividades deportivas</t>
   </si>
   <si>
     <t>Cumplimiento del cronograma de actividades culturales</t>
   </si>
   <si>
-    <t>Participación en actividades culturales presenciales</t>
-  </si>
-  <si>
     <t>Participación en actividades culturales</t>
   </si>
   <si>
@@ -507,7 +483,7 @@
     <t>Cumplimiento plan de trabajo</t>
   </si>
   <si>
-    <t>N de solicitudes radicadas</t>
+    <t>Cumplimiento plan de trabajo - Bogotá</t>
   </si>
   <si>
     <t>N de solicitudes radicadas - (Metrica)</t>
@@ -564,9 +540,6 @@
     <t>Plan De Internacionalización A 7 Años</t>
   </si>
   <si>
-    <t>Convenios, alianzas activas con actividades desde 2018</t>
-  </si>
-  <si>
     <t>Convenios, alianzas activas con actividades en los últimos 5 años</t>
   </si>
   <si>
@@ -591,21 +564,18 @@
     <t>Número de programas nuevos radicados en el Ministerio de Educación</t>
   </si>
   <si>
-    <t>Número de programas nuevos con registro calificado aprobado</t>
-  </si>
-  <si>
-    <t>Número de informes de autoevaluación con fines de acreditación en alta calidad radicados</t>
+    <t>Número de programas nuevos con registro calificado aprobado - Metrica</t>
   </si>
   <si>
     <t>Número de informes de autoevaluación con fines de acreditación en alta calidad radicados- Metrica</t>
   </si>
   <si>
+    <t>Número de programas con obtención de acreditación por primera vez- Metrica</t>
+  </si>
+  <si>
     <t>Número de programas con obtención de acreditación por primera vez</t>
   </si>
   <si>
-    <t>Número de programas con obtención de acreditación por primera vez- Metrica</t>
-  </si>
-  <si>
     <t>Nivel de encuestas obtenidas en el encuentro institucional de graduados</t>
   </si>
   <si>
@@ -627,30 +597,18 @@
     <t>Materiales bibliográficos en formato físico con estado de perdida</t>
   </si>
   <si>
-    <t>Número de programas con renovación de acreditación en alta calidad</t>
-  </si>
-  <si>
     <t>Número de programas con renovación de acreditación en alta calidad - Metrica</t>
   </si>
   <si>
-    <t>Número de programas con condiciones iniciales aprobadas</t>
-  </si>
-  <si>
     <t>Número de programas con condiciones iniciales aprobadas (indicador externo)- Metrica</t>
   </si>
   <si>
-    <t>% Programas acreditables acreditados Sede Bogotá</t>
+    <t>Programas acreditables acreditados Sede Bogotá</t>
   </si>
   <si>
     <t>Cumplimiento cronograma revisiones locativas</t>
   </si>
   <si>
-    <t>Monto total de ahorro en gestión de abastecimiento</t>
-  </si>
-  <si>
-    <t>Reducción de costos en gestión de abastecimiento</t>
-  </si>
-  <si>
     <t>Eficiencia en la reducción de costos en la gestión del abastecimiento</t>
   </si>
   <si>
@@ -666,9 +624,15 @@
     <t>Legalizaciones y anticipos</t>
   </si>
   <si>
+    <t>Número de anticipos y legalizaciones pendientes de legalización  45 días</t>
+  </si>
+  <si>
     <t>Cuentas por pagar</t>
   </si>
   <si>
+    <t>Indice de cuentas por pagar</t>
+  </si>
+  <si>
     <t>Número de redes de investigación</t>
   </si>
   <si>
@@ -678,9 +642,15 @@
     <t>Partidas conciliatorias de bancos</t>
   </si>
   <si>
+    <t>Nivel de partidas conciliatorias bancarias pendientes</t>
+  </si>
+  <si>
     <t>Nivel de facturas generadas con error</t>
   </si>
   <si>
+    <t>Índice de facturas generadas con inconsistencias</t>
+  </si>
+  <si>
     <t>Cobertura de tableros BI en procesos</t>
   </si>
   <si>
@@ -693,21 +663,12 @@
     <t>Indice de Endeudamiento</t>
   </si>
   <si>
-    <t>Cartera</t>
-  </si>
-  <si>
     <t>Cartera - Metrica</t>
   </si>
   <si>
-    <t>Acompañamiento a estudiantes en practicas</t>
-  </si>
-  <si>
     <t>Nivel de acompañamiento a estudiantes en práctica</t>
   </si>
   <si>
-    <t>Satisfacción Institucional</t>
-  </si>
-  <si>
     <t>Satisfacción Institucional CSAT</t>
   </si>
   <si>
@@ -729,7 +690,7 @@
     <t>Normalización de cobros pecuniarios</t>
   </si>
   <si>
-    <t>% Estudiantes con Becas</t>
+    <t>Estudiantes con Becas</t>
   </si>
   <si>
     <t>Satisfacción de los estudiantes de Educación para toda la vida</t>
@@ -813,18 +774,12 @@
     <t>Publicaciones en medios de comunicación Tier 1 y Tier 2</t>
   </si>
   <si>
-    <t>Publicaciones en medios de comunicación Tier 1 y Tier 2 de la región Antioquia</t>
-  </si>
-  <si>
     <t>Publicaciones en medios de comunicación de la región Antioquia</t>
   </si>
   <si>
     <t>Publicaciones en el Campus Virtual</t>
   </si>
   <si>
-    <t>Gestión de casos del Estudio de Emisión</t>
-  </si>
-  <si>
     <t>Gestión de casos del Estudio de Grabación Virtual</t>
   </si>
   <si>
@@ -843,9 +798,6 @@
     <t>Informe anual de consulta de MI-Books</t>
   </si>
   <si>
-    <t>Número de estudiantes que ha realizado la simulación</t>
-  </si>
-  <si>
     <t>Número de estudiantes que ha realizado la simulación (Metrica)</t>
   </si>
   <si>
@@ -879,9 +831,6 @@
     <t>Participación en eventos externos de impacto</t>
   </si>
   <si>
-    <t>Participaciones del Poli como sede o patrocinador</t>
-  </si>
-  <si>
     <t>Participación del Poli como sede o patrocinador</t>
   </si>
   <si>
@@ -915,7 +864,7 @@
     <t>Brand equity</t>
   </si>
   <si>
-    <t>Conocimiento espontaneo</t>
+    <t>Conocimiento espontáneo</t>
   </si>
   <si>
     <t>Cumplimiento Leads Educación para la vida</t>
@@ -945,9 +894,6 @@
     <t>Generación de Residuos Peligrosos per Cápita Semestral</t>
   </si>
   <si>
-    <t>Generación de Residuos Peligroso Mensual</t>
-  </si>
-  <si>
     <t>Generación de Residuos Peligrosos Mensual</t>
   </si>
   <si>
@@ -990,9 +936,6 @@
     <t>Cumplimiento en la supervisión y monitoreo a los planes de tratamiento de los riesgos institucionales en nivel alto y extremo</t>
   </si>
   <si>
-    <t>% Participación de publicaciones positiva</t>
-  </si>
-  <si>
     <t>% de publicaciones con sentimiento positivo</t>
   </si>
   <si>
@@ -1020,9 +963,6 @@
     <t>% de profesores (Contrato Indefinido- Fijo) impactados plan de desarrollo docente</t>
   </si>
   <si>
-    <t>% de profesores (Contrato Indefinido- Fijo) impactados plan de desarrollo docente *</t>
-  </si>
-  <si>
     <t>Nivel Esfuerzo Editorial</t>
   </si>
   <si>
@@ -1089,7 +1029,7 @@
     <t>Número de visitas a la página web</t>
   </si>
   <si>
-    <t>Impactados Talleres de formación</t>
+    <t>Número Impactados Talleres de formación</t>
   </si>
   <si>
     <t>Oportunidad en el cierre de actividades de los planes de mejora</t>
@@ -1188,9 +1128,6 @@
     <t>Participación de Grupos de Interés en la construcción del nuevo plan de desarrollo (PDI)</t>
   </si>
   <si>
-    <t>Participación de la comunidad en la Rendición de Cuentas</t>
-  </si>
-  <si>
     <t>Oportunidad en la solución de solicitudes de infraestructura</t>
   </si>
   <si>
@@ -1266,9 +1203,483 @@
     <t>Cumplimiento Plan de formación Institucional</t>
   </si>
   <si>
+    <t>Nivel de Satisfacción de servicios prestados - Estudios Internos</t>
+  </si>
+  <si>
     <t>Tasa de Ejecución Presupuestal del Proceso</t>
   </si>
   <si>
+    <t>Tasa de crecimiento de estudiantes beneficiarios de becas</t>
+  </si>
+  <si>
+    <t>Tasa de Permanencia de Beneficiarios del Programa de Becas</t>
+  </si>
+  <si>
+    <t>Nivel Satisfacción con la Oficina de inclusión</t>
+  </si>
+  <si>
+    <t>Satisfacción con la estrategia de acompañamiento del proceso de inclusión</t>
+  </si>
+  <si>
+    <t>Relación Estudiante-Docente Tiempo completo  Equivalente (Población AAC/Institucional - Bogotá Virtual)</t>
+  </si>
+  <si>
+    <t>Nivel de satisfacción Gestión docente</t>
+  </si>
+  <si>
+    <t>Nivel de Cumplimiento en la actualización de información normativa de programas académicos</t>
+  </si>
+  <si>
+    <t>Nivel de Cumplimiento de Tamaños Muestrales por Grupo de Interés</t>
+  </si>
+  <si>
+    <t>Cumplimiento Meta de estudiantes de Reintegros</t>
+  </si>
+  <si>
+    <t>Nivel de satisfacción Biblioteca Presencial</t>
+  </si>
+  <si>
+    <t>CES Recursos digitales</t>
+  </si>
+  <si>
+    <t>Satisfacción Front de servicios de Talento Humano</t>
+  </si>
+  <si>
+    <t>Nivel de Satisfacción Servicios Prestados - Gerencia de tecnología e innovación</t>
+  </si>
+  <si>
+    <t>Cumplimiento total estudiantes antiguos — Posgrado Presencial</t>
+  </si>
+  <si>
+    <t>Cumplimiento total estudiantes antiguos — Pregrado Presencial</t>
+  </si>
+  <si>
+    <t>Cumplimiento total estudiantes antiguos — Pregrado Virtual</t>
+  </si>
+  <si>
+    <t>Cumplimiento total estudiantes antiguos — Posgrado Virtual</t>
+  </si>
+  <si>
+    <t>Cumplimiento de planes anuales por líneas — Expansión</t>
+  </si>
+  <si>
+    <t>Cumplimiento de planes anuales por líneas — Educación para toda la vida</t>
+  </si>
+  <si>
+    <t>Cumplimiento de planes anuales por líneas — Trasformación Organizacional</t>
+  </si>
+  <si>
+    <t>Cumplimiento de planes anuales por líneas — Experiencia</t>
+  </si>
+  <si>
+    <t>Cumplimiento de planes anuales por líneas — Sostenibilidad</t>
+  </si>
+  <si>
+    <t>Cumplimiento de planes anuales por líneas — Calidad</t>
+  </si>
+  <si>
+    <t>Cumplimiento Plan Anual por escuela — ESCUELA DE CIENCIAS BÁSICAS</t>
+  </si>
+  <si>
+    <t>Cumplimiento Plan Anual por escuela — ESCUELA DE MARKETING Y BRANDING</t>
+  </si>
+  <si>
+    <t>Cumplimiento Plan Anual por escuela — ESCUELA DE PSIC, TALENTO HUM Y SOC</t>
+  </si>
+  <si>
+    <t>Cumplimiento Plan Anual por escuela — ESCUELA DE EDUCACIÓN E INNOVACIÓN</t>
+  </si>
+  <si>
+    <t>Cumplimiento Plan Anual por escuela — ESCUELA DE  DISEÑO</t>
+  </si>
+  <si>
+    <t>Cumplimiento Plan Anual por escuela — ESCUELA DE OPTIMIZACIÓN, INFRA Y AUTO</t>
+  </si>
+  <si>
+    <t>Cumplimiento Plan Anual por escuela — ESCUELA TIC</t>
+  </si>
+  <si>
+    <t>Cumplimiento Plan Anual por escuela — ESCUELA DE ADMINISTRACIÓN Y COMPETITIVIDAD</t>
+  </si>
+  <si>
+    <t>Cumplimiento Plan Anual por escuela — ESCUELA DE CONTABILIDAD INTERNACIONAL</t>
+  </si>
+  <si>
+    <t>Cumplimiento Plan Anual por escuela — ESCUELA DE NEGOCIOS Y DESARROLLO INTERNACIONAL</t>
+  </si>
+  <si>
+    <t>Cumplimiento Plan Anual por escuela — ESCUELA DE COMUNICACIÓN ARTES VISUALES Y DIGITALES</t>
+  </si>
+  <si>
+    <t>Cumplimiento Plan Anual por escuela — ESCUELA DE DERECHO Y GOBIERNO</t>
+  </si>
+  <si>
+    <t>Cumplimiento Plan Anual Rectoría — Vicerrectoría de crecimiento</t>
+  </si>
+  <si>
+    <t>Cumplimiento Plan Anual Rectoría — Vicerrectoría del estudiante</t>
+  </si>
+  <si>
+    <t>Cumplimiento Plan Anual Rectoría — Vicerrectoría financiera</t>
+  </si>
+  <si>
+    <t>Cumplimiento Plan Anual Rectoría — Gerencia de estrategia</t>
+  </si>
+  <si>
+    <t>Cumplimiento Plan Anual Rectoría — Gerencia de  talento humano y desarrollo</t>
+  </si>
+  <si>
+    <t>Cumplimiento Plan Anual Rectoría — Gerencia sede Medellín</t>
+  </si>
+  <si>
+    <t>Cumplimiento Plan Anual Rectoría — Secretaria general</t>
+  </si>
+  <si>
+    <t>Plan anual Secretaría General</t>
+  </si>
+  <si>
+    <t>Cumplimiento Plan Anual Rectoría — Gerencia de educación virtual</t>
+  </si>
+  <si>
+    <t>Cumplimiento Plan Anual Rectoría — Vicerrectoría académica</t>
+  </si>
+  <si>
+    <t>Cumplimiento Plan Anual Vicerrectoría del estudiante — Gerencia de operaciones</t>
+  </si>
+  <si>
+    <t>Plan anual Gerencia de tecnologÍa e innovación digital</t>
+  </si>
+  <si>
+    <t>Cumplimiento Plan Anual Vicerrectoría del estudiante — Director de operaciones IT</t>
+  </si>
+  <si>
+    <t>Cumplimiento Plan Anual Vicerrectoría del estudiante — Director de operaciones integrales</t>
+  </si>
+  <si>
+    <t>Cumplimiento Plan Anual Vicerrectoría del estudiante — Director de permanencia</t>
+  </si>
+  <si>
+    <t>Cumplimiento Plan Anual Vicerrectoría del estudiante — Director de servicio</t>
+  </si>
+  <si>
+    <t>Cumplimiento Plan Anual Vicerrectoría del estudiante — Direccion bienestar universitario y huella grancolombiana</t>
+  </si>
+  <si>
+    <t>Cumplimiento Plan Anual Vicerrectoría del estudiante — Gerencia de servicio y permanencia</t>
+  </si>
+  <si>
+    <t>Cumplimiento Plan Anual Vicerrectoría del estudiante — Gerencia de tecnología e innovación digital</t>
+  </si>
+  <si>
+    <t>Cumplimiento Plan Anual Vicerrectoría del estudiante — BI y analítica</t>
+  </si>
+  <si>
+    <t>Cumplimiento Plan Anual Vicerrectoría del estudiante — Dirección nacional de registro y control</t>
+  </si>
+  <si>
+    <t>Cumplimiento Plan Anual Vicerrectoría del estudiante — Dirección de Experiencia E Inclusion</t>
+  </si>
+  <si>
+    <t>Cumplimiento Plan Anual Vicerrectoría del estudiante — Director de gobierno digital</t>
+  </si>
+  <si>
+    <t>Cumplimiento Plan Anual Vicerrectoría del estudiante — Gerente de innovación y producto</t>
+  </si>
+  <si>
+    <t>Cumplimiento Plan Anual Vicerrectoría del estudiante — Dirección de desarrollo e innovación</t>
+  </si>
+  <si>
+    <t>Cumplimiento Plan Anual Vicerrectoría de crecimiento — Gerencia de matriculas</t>
+  </si>
+  <si>
+    <t>Cumplimiento Plan Anual Vicerrectoría de crecimiento — Gerencia de mercadeo</t>
+  </si>
+  <si>
+    <t>Cumplimiento Plan Anual Vicerrectoría de crecimiento — Gerencia de servicios corporativos</t>
+  </si>
+  <si>
+    <t>Cumplimiento Plan Anual Vicerrectoría de crecimiento — Director B2B y B2C</t>
+  </si>
+  <si>
+    <t>Cumplimiento Plan Anual Vicerrectoría de crecimiento — Director de producto</t>
+  </si>
+  <si>
+    <t>Cumplimiento Plan Anual Vicerrectoría de crecimiento — Director de estrategia marca</t>
+  </si>
+  <si>
+    <t>Cumplimiento Plan Anual Vicerrectoría Financiera — Dirección de contabilidad</t>
+  </si>
+  <si>
+    <t>Cumplimiento Plan Anual Vicerrectoría Financiera — Dirección de infraestructura</t>
+  </si>
+  <si>
+    <t>Cumplimiento Plan Anual Vicerrectoría Financiera — Dirección planeación financiera y tesorería</t>
+  </si>
+  <si>
+    <t>Cumplimiento Plan Anual Vicerrectoría Financiera — Dirección de servicios administrativos</t>
+  </si>
+  <si>
+    <t>Cumplimiento Plan Anual Vicerrectoría Financiera — Dirección de compras y abastecimiento</t>
+  </si>
+  <si>
+    <t>Cumplimiento Plan Anual Vicerrectoría Financiera — Dirección de relacionamiento de CSU</t>
+  </si>
+  <si>
+    <t>Cumplimiento Plan Anual Vicerrectoría Académica — Dirección aseguramiento de la calidad</t>
+  </si>
+  <si>
+    <t>Cumplimiento Plan Anual Vicerrectoría Académica — Dirección relaciones nacionales e internacionales</t>
+  </si>
+  <si>
+    <t>Cumplimiento Plan Anual Vicerrectoría Académica — Secretaria académica y de extensión</t>
+  </si>
+  <si>
+    <t>Cumplimiento Plan Anual Vicerrectoría Académica — Dirección de docencia</t>
+  </si>
+  <si>
+    <t>Cumplimiento Plan Anual Vicerrectoría Académica — Dirección de currículo presencial y virtual</t>
+  </si>
+  <si>
+    <t>Cumplimiento Plan Anual Vicerrectoría Académica — Facultad ingeniería diseño e innovación</t>
+  </si>
+  <si>
+    <t>Cumplimiento Plan Anual Vicerrectoría Académica — Facultad negocios gestión y sostenibilidad</t>
+  </si>
+  <si>
+    <t>Cumplimiento Plan Anual Vicerrectoría Académica — Facultad sociedad cultura y creatividad</t>
+  </si>
+  <si>
+    <t>Cumplimiento Plan Anual Vicerrectoría Académica — Dirección investigación innovación y creación</t>
+  </si>
+  <si>
+    <t>Cumplimiento Plan Anual Gerencia de estrategia — SGC</t>
+  </si>
+  <si>
+    <t>Cumplimiento Plan Anual Gerencia de estrategia — SGA</t>
+  </si>
+  <si>
+    <t>Cumplimiento Plan Anual Gerencia de estrategia — Riesgos</t>
+  </si>
+  <si>
+    <t>Cumplimiento Plan Anual Gerencia de estrategia — Auditoría</t>
+  </si>
+  <si>
+    <t>Cumplimiento Plan Anual Gerencia de estrategia — Planeación estratégica</t>
+  </si>
+  <si>
+    <t>Cumplimiento Plan Anual Gerencia de estrategia — Estudios Internos</t>
+  </si>
+  <si>
+    <t>Cumplimiento Plan Anual Áreas sede Medellín — FSCC- DERECHO Y GOBIERNO-DERECHO</t>
+  </si>
+  <si>
+    <t>Cumplimiento Plan Anual Áreas sede Medellín — FIDI-TIC -INGENIERIA DE SISTEMAS</t>
+  </si>
+  <si>
+    <t>Cumplimiento Plan Anual Áreas sede Medellín — FIDI-OPINA-INGENIERIA INDUSTRIAL</t>
+  </si>
+  <si>
+    <t>Cumplimiento Plan Anual Áreas sede Medellín — FNGS-NEG Y DLLO INTER-NEGOCIOS INTERNACIONALES</t>
+  </si>
+  <si>
+    <t>Cumplimiento Plan Anual Áreas sede Medellín — FSCC- EST.PSIC,TH Y SOC- PSICOLOGIA</t>
+  </si>
+  <si>
+    <t>Cumplimiento Plan Anual Áreas sede Medellín — FIDI-CIENCIAS BÁSICAS MED</t>
+  </si>
+  <si>
+    <t>Cumplimiento Plan Anual Áreas sede Medellín — ADMON DE EMPRESAS</t>
+  </si>
+  <si>
+    <t>Cumplimiento Plan Anual Áreas sede Medellín — FSCC - MARKETING MED</t>
+  </si>
+  <si>
+    <t>Cumplimiento Plan Anual Áreas sede Medellín — FIDI-DISEÑO-DISEÑO GRAFICO</t>
+  </si>
+  <si>
+    <t>Cumplimiento plan anual Secretaria académica y de extensión — DIRECTOR EDITORIAL</t>
+  </si>
+  <si>
+    <t>Cumplimiento plan anual Secretaria académica y de extensión — DIRECTOR CENTRO MEDIOS AUDIOVISUALES</t>
+  </si>
+  <si>
+    <t>Cumplimiento plan anual Secretaria académica y de extensión — DIRECTOR AGENCIA TROMPO</t>
+  </si>
+  <si>
+    <t>Cumplimiento plan anual Secretaria académica y de extensión — DIRECTOR DE GRADUADOS Y PROYECCION EMP.</t>
+  </si>
+  <si>
+    <t>Cumplimiento plan anual Secretaria académica y de extensión — DIRECTOR SISTEMA NACIONAL DE BIBLIOTECAS</t>
+  </si>
+  <si>
+    <t>Cumplimiento plan anual Gerencia de Talento Humano — DIRECTOR DE BIENESTAR Y RELAC. LABORALES</t>
+  </si>
+  <si>
+    <t>Cumplimiento plan anual Gerencia de Talento Humano — DIRECTOR DE FORMACION Y DESARROLLO</t>
+  </si>
+  <si>
+    <t>Cumplimiento plan anual Gerencia de Talento Humano — DIRECTOR DE RELACIONES PUBLICAS Y PROTOC</t>
+  </si>
+  <si>
+    <t>Cumplimiento plan anual Gerencia de Talento Humano — DIRECTOR DE COMUNICACIONES</t>
+  </si>
+  <si>
+    <t>Cumplimiento plan anual Gerencia de Talento Humano — DIRECTOR DE ADMON LABORAL Y COMPENSACION</t>
+  </si>
+  <si>
+    <t>Cumplimiento plan anual Gerencia de Talento Humano — DIRECTOR DE GESTION DE TALENTO</t>
+  </si>
+  <si>
+    <t>Cumplimiento plan anual Gerencia de Talento Humano — DIRECTOR DE COMUN. EXTERNAS SED MEDELLIN</t>
+  </si>
+  <si>
+    <t>Innovación curricular - Fase I</t>
+  </si>
+  <si>
+    <t>Acreditación Institucional Sede Bogotá - Fase II - Condiciones iniciales</t>
+  </si>
+  <si>
+    <t>Acreditación Institucional Sede Bogotá - Fase I</t>
+  </si>
+  <si>
+    <t>Creación del Instituto de Educación para el trabajo y el desarrollo humano - Stand By</t>
+  </si>
+  <si>
+    <t>Institución de educación para el trabajo y desarrollo humano IETDH</t>
+  </si>
+  <si>
+    <t>Creación del colegio de educación media virtual  - Stand By</t>
+  </si>
+  <si>
+    <t>Colegio Virtual</t>
+  </si>
+  <si>
+    <t>Diseño del Modelo de Experiencia Institucional - Fase 2</t>
+  </si>
+  <si>
+    <t>Diseño del Modelo de Experiencia Institucional - Fase 1</t>
+  </si>
+  <si>
+    <t>Experiencia Institucional - Fase 3- Hub de experiencia</t>
+  </si>
+  <si>
+    <t>Centro de Idiomas Fase I</t>
+  </si>
+  <si>
+    <t>Centro de Idiomas POLI</t>
+  </si>
+  <si>
+    <t>CREA Centro de Recursos y Experiencias para el aprendizaje - Fase de Adecuación</t>
+  </si>
+  <si>
+    <t>Migración modelo de transporte rotativo</t>
+  </si>
+  <si>
+    <t>Plan Talento</t>
+  </si>
+  <si>
+    <t>Ecosistema E3</t>
+  </si>
+  <si>
+    <t>Habilidades Poderosas</t>
+  </si>
+  <si>
+    <t>Ser PRO</t>
+  </si>
+  <si>
+    <t>SER PRO Fase II</t>
+  </si>
+  <si>
+    <t>Cultura de una buena docencia</t>
+  </si>
+  <si>
+    <t>Proyecto Silver</t>
+  </si>
+  <si>
+    <t>Acreditación Institucional fase III Etapa de evaluación externa o evaluación por pares</t>
+  </si>
+  <si>
+    <t>Fortalecimiento de la investigación, la innovación y la creación</t>
+  </si>
+  <si>
+    <t>Fortalecimiento de planta docente</t>
+  </si>
+  <si>
+    <t>Plataforma Tecnologica de Gestión de información Curricular</t>
+  </si>
+  <si>
+    <t>Actualización de TRD y creación del Plan de Gestión documental</t>
+  </si>
+  <si>
+    <t>Nuevo POLISIGS</t>
+  </si>
+  <si>
+    <t>ADN POLI</t>
+  </si>
+  <si>
+    <t>Gobierno de datos</t>
+  </si>
+  <si>
+    <t>Herramientas de Gestión para el mejoramiento continuo</t>
+  </si>
+  <si>
+    <t>Proyectos Ilumno Self Service S&amp;P</t>
+  </si>
+  <si>
+    <t>Reingenieria de aplicaciones</t>
+  </si>
+  <si>
+    <t>SOPHIA Sistema de Optimización y Programación Horaria Institucional  Académica  I Fase</t>
+  </si>
+  <si>
+    <t>Hubspot CRM</t>
+  </si>
+  <si>
+    <t>Prime</t>
+  </si>
+  <si>
+    <t>Proyecto de Permanencia institucional</t>
+  </si>
+  <si>
+    <t>Centro Gastronómico</t>
+  </si>
+  <si>
+    <t>Certificación SGA sede los Colores</t>
+  </si>
+  <si>
+    <t>Modelo de seguimiento al graduado</t>
+  </si>
+  <si>
+    <t>Pricing</t>
+  </si>
+  <si>
+    <t>Titulación Autogestionada</t>
+  </si>
+  <si>
+    <t>Sistema de medición de resultados de aprendizaje</t>
+  </si>
+  <si>
+    <t>Fortalecimiento de la investigacion, la innovación y la creación</t>
+  </si>
+  <si>
+    <t>Equidad de Genero</t>
+  </si>
+  <si>
+    <t>Portal Universitario</t>
+  </si>
+  <si>
+    <t>Data Lake Institucional</t>
+  </si>
+  <si>
+    <t>Catalogo de recursos virtuales</t>
+  </si>
+  <si>
+    <t>Monarca - Ecosistema Banner</t>
+  </si>
+  <si>
+    <t>Ecosistema Banner</t>
+  </si>
+  <si>
     <t>Meta</t>
   </si>
   <si>
@@ -1299,25 +1710,28 @@
     <t>Metrica</t>
   </si>
   <si>
+    <t>m3</t>
+  </si>
+  <si>
+    <t>Sin Reporte</t>
+  </si>
+  <si>
+    <t>Kg</t>
+  </si>
+  <si>
+    <t>kWh</t>
+  </si>
+  <si>
+    <t>tCO2e</t>
+  </si>
+  <si>
+    <t>Linea Base</t>
+  </si>
+  <si>
     <t>No Aplica</t>
   </si>
   <si>
-    <t>Linea Base</t>
-  </si>
-  <si>
-    <t>m3</t>
-  </si>
-  <si>
-    <t>Sin Reporte</t>
-  </si>
-  <si>
-    <t>Kg</t>
-  </si>
-  <si>
-    <t>kWh</t>
-  </si>
-  <si>
-    <t>tCO2e</t>
+    <t>Stand by</t>
   </si>
   <si>
     <t>Decimales_Meta</t>
@@ -1652,7 +2066,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A416"/>
+  <dimension ref="A1:A553"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:1">
@@ -3733,6 +4147,691 @@
     <row r="416" spans="1:1">
       <c r="A416" t="s">
         <v>415</v>
+      </c>
+    </row>
+    <row r="417" spans="1:1">
+      <c r="A417" t="s">
+        <v>416</v>
+      </c>
+    </row>
+    <row r="418" spans="1:1">
+      <c r="A418" t="s">
+        <v>417</v>
+      </c>
+    </row>
+    <row r="419" spans="1:1">
+      <c r="A419" t="s">
+        <v>418</v>
+      </c>
+    </row>
+    <row r="420" spans="1:1">
+      <c r="A420" t="s">
+        <v>419</v>
+      </c>
+    </row>
+    <row r="421" spans="1:1">
+      <c r="A421" t="s">
+        <v>420</v>
+      </c>
+    </row>
+    <row r="422" spans="1:1">
+      <c r="A422" t="s">
+        <v>421</v>
+      </c>
+    </row>
+    <row r="423" spans="1:1">
+      <c r="A423" t="s">
+        <v>422</v>
+      </c>
+    </row>
+    <row r="424" spans="1:1">
+      <c r="A424" t="s">
+        <v>423</v>
+      </c>
+    </row>
+    <row r="425" spans="1:1">
+      <c r="A425" t="s">
+        <v>424</v>
+      </c>
+    </row>
+    <row r="426" spans="1:1">
+      <c r="A426" t="s">
+        <v>425</v>
+      </c>
+    </row>
+    <row r="427" spans="1:1">
+      <c r="A427" t="s">
+        <v>426</v>
+      </c>
+    </row>
+    <row r="428" spans="1:1">
+      <c r="A428" t="s">
+        <v>427</v>
+      </c>
+    </row>
+    <row r="429" spans="1:1">
+      <c r="A429" t="s">
+        <v>428</v>
+      </c>
+    </row>
+    <row r="430" spans="1:1">
+      <c r="A430" t="s">
+        <v>429</v>
+      </c>
+    </row>
+    <row r="431" spans="1:1">
+      <c r="A431" t="s">
+        <v>430</v>
+      </c>
+    </row>
+    <row r="432" spans="1:1">
+      <c r="A432" t="s">
+        <v>431</v>
+      </c>
+    </row>
+    <row r="433" spans="1:1">
+      <c r="A433" t="s">
+        <v>432</v>
+      </c>
+    </row>
+    <row r="434" spans="1:1">
+      <c r="A434" t="s">
+        <v>433</v>
+      </c>
+    </row>
+    <row r="435" spans="1:1">
+      <c r="A435" t="s">
+        <v>434</v>
+      </c>
+    </row>
+    <row r="436" spans="1:1">
+      <c r="A436" t="s">
+        <v>435</v>
+      </c>
+    </row>
+    <row r="437" spans="1:1">
+      <c r="A437" t="s">
+        <v>436</v>
+      </c>
+    </row>
+    <row r="438" spans="1:1">
+      <c r="A438" t="s">
+        <v>437</v>
+      </c>
+    </row>
+    <row r="439" spans="1:1">
+      <c r="A439" t="s">
+        <v>438</v>
+      </c>
+    </row>
+    <row r="440" spans="1:1">
+      <c r="A440" t="s">
+        <v>439</v>
+      </c>
+    </row>
+    <row r="441" spans="1:1">
+      <c r="A441" t="s">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="442" spans="1:1">
+      <c r="A442" t="s">
+        <v>441</v>
+      </c>
+    </row>
+    <row r="443" spans="1:1">
+      <c r="A443" t="s">
+        <v>442</v>
+      </c>
+    </row>
+    <row r="444" spans="1:1">
+      <c r="A444" t="s">
+        <v>443</v>
+      </c>
+    </row>
+    <row r="445" spans="1:1">
+      <c r="A445" t="s">
+        <v>444</v>
+      </c>
+    </row>
+    <row r="446" spans="1:1">
+      <c r="A446" t="s">
+        <v>445</v>
+      </c>
+    </row>
+    <row r="447" spans="1:1">
+      <c r="A447" t="s">
+        <v>446</v>
+      </c>
+    </row>
+    <row r="448" spans="1:1">
+      <c r="A448" t="s">
+        <v>447</v>
+      </c>
+    </row>
+    <row r="449" spans="1:1">
+      <c r="A449" t="s">
+        <v>448</v>
+      </c>
+    </row>
+    <row r="450" spans="1:1">
+      <c r="A450" t="s">
+        <v>449</v>
+      </c>
+    </row>
+    <row r="451" spans="1:1">
+      <c r="A451" t="s">
+        <v>450</v>
+      </c>
+    </row>
+    <row r="452" spans="1:1">
+      <c r="A452" t="s">
+        <v>451</v>
+      </c>
+    </row>
+    <row r="453" spans="1:1">
+      <c r="A453" t="s">
+        <v>452</v>
+      </c>
+    </row>
+    <row r="454" spans="1:1">
+      <c r="A454" t="s">
+        <v>453</v>
+      </c>
+    </row>
+    <row r="455" spans="1:1">
+      <c r="A455" t="s">
+        <v>454</v>
+      </c>
+    </row>
+    <row r="456" spans="1:1">
+      <c r="A456" t="s">
+        <v>455</v>
+      </c>
+    </row>
+    <row r="457" spans="1:1">
+      <c r="A457" t="s">
+        <v>456</v>
+      </c>
+    </row>
+    <row r="458" spans="1:1">
+      <c r="A458" t="s">
+        <v>457</v>
+      </c>
+    </row>
+    <row r="459" spans="1:1">
+      <c r="A459" t="s">
+        <v>458</v>
+      </c>
+    </row>
+    <row r="460" spans="1:1">
+      <c r="A460" t="s">
+        <v>459</v>
+      </c>
+    </row>
+    <row r="461" spans="1:1">
+      <c r="A461" t="s">
+        <v>460</v>
+      </c>
+    </row>
+    <row r="462" spans="1:1">
+      <c r="A462" t="s">
+        <v>461</v>
+      </c>
+    </row>
+    <row r="463" spans="1:1">
+      <c r="A463" t="s">
+        <v>462</v>
+      </c>
+    </row>
+    <row r="464" spans="1:1">
+      <c r="A464" t="s">
+        <v>463</v>
+      </c>
+    </row>
+    <row r="465" spans="1:1">
+      <c r="A465" t="s">
+        <v>464</v>
+      </c>
+    </row>
+    <row r="466" spans="1:1">
+      <c r="A466" t="s">
+        <v>465</v>
+      </c>
+    </row>
+    <row r="467" spans="1:1">
+      <c r="A467" t="s">
+        <v>466</v>
+      </c>
+    </row>
+    <row r="468" spans="1:1">
+      <c r="A468" t="s">
+        <v>467</v>
+      </c>
+    </row>
+    <row r="469" spans="1:1">
+      <c r="A469" t="s">
+        <v>468</v>
+      </c>
+    </row>
+    <row r="470" spans="1:1">
+      <c r="A470" t="s">
+        <v>469</v>
+      </c>
+    </row>
+    <row r="471" spans="1:1">
+      <c r="A471" t="s">
+        <v>470</v>
+      </c>
+    </row>
+    <row r="472" spans="1:1">
+      <c r="A472" t="s">
+        <v>471</v>
+      </c>
+    </row>
+    <row r="473" spans="1:1">
+      <c r="A473" t="s">
+        <v>472</v>
+      </c>
+    </row>
+    <row r="474" spans="1:1">
+      <c r="A474" t="s">
+        <v>473</v>
+      </c>
+    </row>
+    <row r="475" spans="1:1">
+      <c r="A475" t="s">
+        <v>474</v>
+      </c>
+    </row>
+    <row r="476" spans="1:1">
+      <c r="A476" t="s">
+        <v>475</v>
+      </c>
+    </row>
+    <row r="477" spans="1:1">
+      <c r="A477" t="s">
+        <v>476</v>
+      </c>
+    </row>
+    <row r="478" spans="1:1">
+      <c r="A478" t="s">
+        <v>477</v>
+      </c>
+    </row>
+    <row r="479" spans="1:1">
+      <c r="A479" t="s">
+        <v>478</v>
+      </c>
+    </row>
+    <row r="480" spans="1:1">
+      <c r="A480" t="s">
+        <v>479</v>
+      </c>
+    </row>
+    <row r="481" spans="1:1">
+      <c r="A481" t="s">
+        <v>480</v>
+      </c>
+    </row>
+    <row r="482" spans="1:1">
+      <c r="A482" t="s">
+        <v>481</v>
+      </c>
+    </row>
+    <row r="483" spans="1:1">
+      <c r="A483" t="s">
+        <v>482</v>
+      </c>
+    </row>
+    <row r="484" spans="1:1">
+      <c r="A484" t="s">
+        <v>483</v>
+      </c>
+    </row>
+    <row r="485" spans="1:1">
+      <c r="A485" t="s">
+        <v>484</v>
+      </c>
+    </row>
+    <row r="486" spans="1:1">
+      <c r="A486" t="s">
+        <v>485</v>
+      </c>
+    </row>
+    <row r="487" spans="1:1">
+      <c r="A487" t="s">
+        <v>486</v>
+      </c>
+    </row>
+    <row r="488" spans="1:1">
+      <c r="A488" t="s">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="489" spans="1:1">
+      <c r="A489" t="s">
+        <v>488</v>
+      </c>
+    </row>
+    <row r="490" spans="1:1">
+      <c r="A490" t="s">
+        <v>489</v>
+      </c>
+    </row>
+    <row r="491" spans="1:1">
+      <c r="A491" t="s">
+        <v>490</v>
+      </c>
+    </row>
+    <row r="492" spans="1:1">
+      <c r="A492" t="s">
+        <v>491</v>
+      </c>
+    </row>
+    <row r="493" spans="1:1">
+      <c r="A493" t="s">
+        <v>492</v>
+      </c>
+    </row>
+    <row r="494" spans="1:1">
+      <c r="A494" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="495" spans="1:1">
+      <c r="A495" t="s">
+        <v>494</v>
+      </c>
+    </row>
+    <row r="496" spans="1:1">
+      <c r="A496" t="s">
+        <v>495</v>
+      </c>
+    </row>
+    <row r="497" spans="1:1">
+      <c r="A497" t="s">
+        <v>496</v>
+      </c>
+    </row>
+    <row r="498" spans="1:1">
+      <c r="A498" t="s">
+        <v>497</v>
+      </c>
+    </row>
+    <row r="499" spans="1:1">
+      <c r="A499" t="s">
+        <v>498</v>
+      </c>
+    </row>
+    <row r="500" spans="1:1">
+      <c r="A500" t="s">
+        <v>499</v>
+      </c>
+    </row>
+    <row r="501" spans="1:1">
+      <c r="A501" t="s">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="502" spans="1:1">
+      <c r="A502" t="s">
+        <v>501</v>
+      </c>
+    </row>
+    <row r="503" spans="1:1">
+      <c r="A503" t="s">
+        <v>502</v>
+      </c>
+    </row>
+    <row r="504" spans="1:1">
+      <c r="A504" t="s">
+        <v>503</v>
+      </c>
+    </row>
+    <row r="505" spans="1:1">
+      <c r="A505" t="s">
+        <v>504</v>
+      </c>
+    </row>
+    <row r="506" spans="1:1">
+      <c r="A506" t="s">
+        <v>505</v>
+      </c>
+    </row>
+    <row r="507" spans="1:1">
+      <c r="A507" t="s">
+        <v>506</v>
+      </c>
+    </row>
+    <row r="508" spans="1:1">
+      <c r="A508" t="s">
+        <v>507</v>
+      </c>
+    </row>
+    <row r="509" spans="1:1">
+      <c r="A509" t="s">
+        <v>508</v>
+      </c>
+    </row>
+    <row r="510" spans="1:1">
+      <c r="A510" t="s">
+        <v>509</v>
+      </c>
+    </row>
+    <row r="511" spans="1:1">
+      <c r="A511" t="s">
+        <v>510</v>
+      </c>
+    </row>
+    <row r="512" spans="1:1">
+      <c r="A512" t="s">
+        <v>511</v>
+      </c>
+    </row>
+    <row r="513" spans="1:1">
+      <c r="A513" t="s">
+        <v>512</v>
+      </c>
+    </row>
+    <row r="514" spans="1:1">
+      <c r="A514" t="s">
+        <v>513</v>
+      </c>
+    </row>
+    <row r="515" spans="1:1">
+      <c r="A515" t="s">
+        <v>514</v>
+      </c>
+    </row>
+    <row r="516" spans="1:1">
+      <c r="A516" t="s">
+        <v>515</v>
+      </c>
+    </row>
+    <row r="517" spans="1:1">
+      <c r="A517" t="s">
+        <v>516</v>
+      </c>
+    </row>
+    <row r="518" spans="1:1">
+      <c r="A518" t="s">
+        <v>517</v>
+      </c>
+    </row>
+    <row r="519" spans="1:1">
+      <c r="A519" t="s">
+        <v>518</v>
+      </c>
+    </row>
+    <row r="520" spans="1:1">
+      <c r="A520" t="s">
+        <v>519</v>
+      </c>
+    </row>
+    <row r="521" spans="1:1">
+      <c r="A521" t="s">
+        <v>520</v>
+      </c>
+    </row>
+    <row r="522" spans="1:1">
+      <c r="A522" t="s">
+        <v>521</v>
+      </c>
+    </row>
+    <row r="523" spans="1:1">
+      <c r="A523" t="s">
+        <v>522</v>
+      </c>
+    </row>
+    <row r="524" spans="1:1">
+      <c r="A524" t="s">
+        <v>523</v>
+      </c>
+    </row>
+    <row r="525" spans="1:1">
+      <c r="A525" t="s">
+        <v>524</v>
+      </c>
+    </row>
+    <row r="526" spans="1:1">
+      <c r="A526" t="s">
+        <v>525</v>
+      </c>
+    </row>
+    <row r="527" spans="1:1">
+      <c r="A527" t="s">
+        <v>526</v>
+      </c>
+    </row>
+    <row r="528" spans="1:1">
+      <c r="A528" t="s">
+        <v>527</v>
+      </c>
+    </row>
+    <row r="529" spans="1:1">
+      <c r="A529" t="s">
+        <v>528</v>
+      </c>
+    </row>
+    <row r="530" spans="1:1">
+      <c r="A530" t="s">
+        <v>529</v>
+      </c>
+    </row>
+    <row r="531" spans="1:1">
+      <c r="A531" t="s">
+        <v>530</v>
+      </c>
+    </row>
+    <row r="532" spans="1:1">
+      <c r="A532" t="s">
+        <v>531</v>
+      </c>
+    </row>
+    <row r="533" spans="1:1">
+      <c r="A533" t="s">
+        <v>532</v>
+      </c>
+    </row>
+    <row r="534" spans="1:1">
+      <c r="A534" t="s">
+        <v>533</v>
+      </c>
+    </row>
+    <row r="535" spans="1:1">
+      <c r="A535" t="s">
+        <v>534</v>
+      </c>
+    </row>
+    <row r="536" spans="1:1">
+      <c r="A536" t="s">
+        <v>535</v>
+      </c>
+    </row>
+    <row r="537" spans="1:1">
+      <c r="A537" t="s">
+        <v>536</v>
+      </c>
+    </row>
+    <row r="538" spans="1:1">
+      <c r="A538" t="s">
+        <v>537</v>
+      </c>
+    </row>
+    <row r="539" spans="1:1">
+      <c r="A539" t="s">
+        <v>538</v>
+      </c>
+    </row>
+    <row r="540" spans="1:1">
+      <c r="A540" t="s">
+        <v>539</v>
+      </c>
+    </row>
+    <row r="541" spans="1:1">
+      <c r="A541" t="s">
+        <v>540</v>
+      </c>
+    </row>
+    <row r="542" spans="1:1">
+      <c r="A542" t="s">
+        <v>541</v>
+      </c>
+    </row>
+    <row r="543" spans="1:1">
+      <c r="A543" t="s">
+        <v>542</v>
+      </c>
+    </row>
+    <row r="544" spans="1:1">
+      <c r="A544" t="s">
+        <v>543</v>
+      </c>
+    </row>
+    <row r="545" spans="1:1">
+      <c r="A545" t="s">
+        <v>544</v>
+      </c>
+    </row>
+    <row r="546" spans="1:1">
+      <c r="A546" t="s">
+        <v>545</v>
+      </c>
+    </row>
+    <row r="547" spans="1:1">
+      <c r="A547" t="s">
+        <v>546</v>
+      </c>
+    </row>
+    <row r="548" spans="1:1">
+      <c r="A548" t="s">
+        <v>547</v>
+      </c>
+    </row>
+    <row r="549" spans="1:1">
+      <c r="A549" t="s">
+        <v>548</v>
+      </c>
+    </row>
+    <row r="550" spans="1:1">
+      <c r="A550" t="s">
+        <v>549</v>
+      </c>
+    </row>
+    <row r="551" spans="1:1">
+      <c r="A551" t="s">
+        <v>550</v>
+      </c>
+    </row>
+    <row r="552" spans="1:1">
+      <c r="A552" t="s">
+        <v>551</v>
+      </c>
+    </row>
+    <row r="553" spans="1:1">
+      <c r="A553" t="s">
+        <v>552</v>
       </c>
     </row>
   </sheetData>
@@ -3742,12 +4841,12 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A133"/>
+  <dimension ref="A1:A141"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" t="s">
-        <v>416</v>
+        <v>553</v>
       </c>
     </row>
     <row r="2" spans="1:1">
@@ -3772,397 +4871,397 @@
     </row>
     <row r="6" spans="1:1">
       <c r="A6">
-        <v>97</v>
+        <v>23</v>
       </c>
     </row>
     <row r="7" spans="1:1">
       <c r="A7">
-        <v>100</v>
+        <v>87</v>
       </c>
     </row>
     <row r="8" spans="1:1">
       <c r="A8">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="9" spans="1:1">
       <c r="A9">
-        <v>509</v>
+        <v>100</v>
       </c>
     </row>
     <row r="10" spans="1:1">
       <c r="A10">
-        <v>2.14</v>
+        <v>98</v>
       </c>
     </row>
     <row r="11" spans="1:1">
       <c r="A11">
-        <v>1.2</v>
+        <v>509</v>
       </c>
     </row>
     <row r="12" spans="1:1">
       <c r="A12">
-        <v>0</v>
+        <v>2.14</v>
+      </c>
+    </row>
+    <row r="13" spans="1:1">
+      <c r="A13">
+        <v>1.2</v>
       </c>
     </row>
     <row r="14" spans="1:1">
       <c r="A14">
-        <v>102</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15" spans="1:1">
       <c r="A15">
-        <v>1.6</v>
+        <v>102</v>
       </c>
     </row>
     <row r="16" spans="1:1">
       <c r="A16">
-        <v>0.2</v>
+        <v>1.6</v>
       </c>
     </row>
     <row r="17" spans="1:1">
       <c r="A17">
-        <v>4.7</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="18" spans="1:1">
       <c r="A18">
-        <v>1.9</v>
+        <v>4.7</v>
       </c>
     </row>
     <row r="19" spans="1:1">
       <c r="A19">
-        <v>2</v>
+        <v>1.9</v>
       </c>
     </row>
     <row r="20" spans="1:1">
       <c r="A20">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="21" spans="1:1">
       <c r="A21">
-        <v>447</v>
+        <v>1</v>
       </c>
     </row>
     <row r="22" spans="1:1">
       <c r="A22">
-        <v>981.982</v>
+        <v>447</v>
       </c>
     </row>
     <row r="23" spans="1:1">
       <c r="A23">
-        <v>1338.614396</v>
+        <v>981.982</v>
       </c>
     </row>
     <row r="24" spans="1:1">
       <c r="A24">
-        <v>3</v>
+        <v>1338.614396</v>
       </c>
     </row>
     <row r="25" spans="1:1">
       <c r="A25">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="26" spans="1:1">
       <c r="A26">
-        <v>230</v>
+        <v>4</v>
       </c>
     </row>
     <row r="27" spans="1:1">
       <c r="A27">
-        <v>294</v>
+        <v>230</v>
       </c>
     </row>
     <row r="28" spans="1:1">
       <c r="A28">
-        <v>18</v>
+        <v>294</v>
       </c>
     </row>
     <row r="29" spans="1:1">
       <c r="A29">
-        <v>13</v>
+        <v>18</v>
       </c>
     </row>
     <row r="30" spans="1:1">
       <c r="A30">
-        <v>16</v>
+        <v>13</v>
       </c>
     </row>
     <row r="31" spans="1:1">
       <c r="A31">
-        <v>3.75</v>
+        <v>16</v>
       </c>
     </row>
     <row r="32" spans="1:1">
       <c r="A32">
-        <v>5</v>
+        <v>3.75</v>
       </c>
     </row>
     <row r="33" spans="1:1">
       <c r="A33">
-        <v>4.5</v>
+        <v>5</v>
       </c>
     </row>
     <row r="34" spans="1:1">
       <c r="A34">
-        <v>95</v>
+        <v>4.5</v>
       </c>
     </row>
     <row r="35" spans="1:1">
       <c r="A35">
-        <v>76</v>
+        <v>10</v>
       </c>
     </row>
     <row r="36" spans="1:1">
       <c r="A36">
-        <v>92</v>
+        <v>95</v>
       </c>
     </row>
     <row r="37" spans="1:1">
       <c r="A37">
-        <v>93.5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="38" spans="1:1">
       <c r="A38">
-        <v>73</v>
+        <v>76</v>
       </c>
     </row>
     <row r="39" spans="1:1">
       <c r="A39">
-        <v>81</v>
+        <v>92</v>
       </c>
     </row>
     <row r="40" spans="1:1">
       <c r="A40">
-        <v>37</v>
+        <v>93.5</v>
       </c>
     </row>
     <row r="41" spans="1:1">
       <c r="A41">
-        <v>70</v>
+        <v>73</v>
       </c>
     </row>
     <row r="42" spans="1:1">
       <c r="A42">
-        <v>87</v>
+        <v>81</v>
       </c>
     </row>
     <row r="43" spans="1:1">
       <c r="A43">
-        <v>66</v>
+        <v>25</v>
       </c>
     </row>
     <row r="44" spans="1:1">
       <c r="A44">
-        <v>68.7</v>
+        <v>42</v>
       </c>
     </row>
     <row r="45" spans="1:1">
       <c r="A45">
-        <v>224440</v>
+        <v>37</v>
       </c>
     </row>
     <row r="46" spans="1:1">
       <c r="A46">
-        <v>82987</v>
+        <v>70</v>
       </c>
     </row>
     <row r="47" spans="1:1">
       <c r="A47">
-        <v>2605</v>
+        <v>82</v>
       </c>
     </row>
     <row r="48" spans="1:1">
       <c r="A48">
-        <v>1700</v>
-      </c>
-    </row>
-    <row r="49" spans="1:1">
-      <c r="A49">
-        <v>90000</v>
+        <v>66</v>
       </c>
     </row>
     <row r="50" spans="1:1">
       <c r="A50">
-        <v>7500</v>
+        <v>68.7</v>
       </c>
     </row>
     <row r="51" spans="1:1">
       <c r="A51">
-        <v>240</v>
+        <v>224440</v>
       </c>
     </row>
     <row r="52" spans="1:1">
       <c r="A52">
-        <v>2064000</v>
+        <v>82987</v>
       </c>
     </row>
     <row r="53" spans="1:1">
       <c r="A53">
-        <v>172000</v>
+        <v>2605</v>
       </c>
     </row>
     <row r="54" spans="1:1">
       <c r="A54">
-        <v>0.3</v>
+        <v>1700</v>
       </c>
     </row>
     <row r="55" spans="1:1">
       <c r="A55">
-        <v>180</v>
+        <v>90000</v>
       </c>
     </row>
     <row r="56" spans="1:1">
       <c r="A56">
-        <v>4000</v>
+        <v>7500</v>
       </c>
     </row>
     <row r="57" spans="1:1">
       <c r="A57">
-        <v>25</v>
+        <v>240</v>
       </c>
     </row>
     <row r="58" spans="1:1">
       <c r="A58">
-        <v>67.5</v>
+        <v>2064000</v>
       </c>
     </row>
     <row r="59" spans="1:1">
       <c r="A59">
-        <v>44</v>
+        <v>172000</v>
       </c>
     </row>
     <row r="60" spans="1:1">
       <c r="A60">
-        <v>68</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="61" spans="1:1">
       <c r="A61">
-        <v>72.90000000000001</v>
+        <v>180</v>
       </c>
     </row>
     <row r="62" spans="1:1">
       <c r="A62">
-        <v>8</v>
+        <v>4000</v>
       </c>
     </row>
     <row r="63" spans="1:1">
       <c r="A63">
-        <v>200</v>
+        <v>67.5</v>
       </c>
     </row>
     <row r="64" spans="1:1">
       <c r="A64">
-        <v>42</v>
+        <v>44</v>
       </c>
     </row>
     <row r="65" spans="1:1">
       <c r="A65">
-        <v>2.8</v>
+        <v>68</v>
       </c>
     </row>
     <row r="66" spans="1:1">
       <c r="A66">
-        <v>2.1</v>
+        <v>72.90000000000001</v>
       </c>
     </row>
     <row r="67" spans="1:1">
       <c r="A67">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="68" spans="1:1">
       <c r="A68">
-        <v>545</v>
+        <v>200</v>
       </c>
     </row>
     <row r="69" spans="1:1">
       <c r="A69">
-        <v>30907</v>
+        <v>2.8</v>
       </c>
     </row>
     <row r="70" spans="1:1">
       <c r="A70">
-        <v>75</v>
+        <v>2.1</v>
       </c>
     </row>
     <row r="71" spans="1:1">
       <c r="A71">
-        <v>71</v>
+        <v>75</v>
       </c>
     </row>
     <row r="72" spans="1:1">
       <c r="A72">
-        <v>192</v>
+        <v>71</v>
       </c>
     </row>
     <row r="73" spans="1:1">
       <c r="A73">
-        <v>194</v>
+        <v>192</v>
       </c>
     </row>
     <row r="74" spans="1:1">
       <c r="A74">
-        <v>4.6</v>
+        <v>194</v>
       </c>
     </row>
     <row r="75" spans="1:1">
       <c r="A75">
-        <v>6</v>
+        <v>4.6</v>
       </c>
     </row>
     <row r="76" spans="1:1">
       <c r="A76">
-        <v>32</v>
+        <v>4.66</v>
       </c>
     </row>
     <row r="77" spans="1:1">
       <c r="A77">
-        <v>60</v>
+        <v>32</v>
       </c>
     </row>
     <row r="78" spans="1:1">
       <c r="A78">
-        <v>190</v>
+        <v>60</v>
       </c>
     </row>
     <row r="79" spans="1:1">
       <c r="A79">
-        <v>46</v>
+        <v>190</v>
       </c>
     </row>
     <row r="80" spans="1:1">
       <c r="A80">
-        <v>64</v>
+        <v>46</v>
       </c>
     </row>
     <row r="81" spans="1:1">
       <c r="A81">
-        <v>84</v>
+        <v>64</v>
       </c>
     </row>
     <row r="82" spans="1:1">
       <c r="A82">
-        <v>267</v>
+        <v>84</v>
       </c>
     </row>
     <row r="83" spans="1:1">
       <c r="A83">
-        <v>221</v>
+        <v>267</v>
       </c>
     </row>
     <row r="84" spans="1:1">
       <c r="A84">
-        <v>28</v>
+        <v>221</v>
       </c>
     </row>
     <row r="85" spans="1:1">
       <c r="A85">
-        <v>23</v>
+        <v>28</v>
       </c>
     </row>
     <row r="86" spans="1:1">
@@ -4212,17 +5311,17 @@
     </row>
     <row r="95" spans="1:1">
       <c r="A95">
-        <v>88</v>
+        <v>1.3</v>
       </c>
     </row>
     <row r="96" spans="1:1">
       <c r="A96">
-        <v>89</v>
+        <v>88</v>
       </c>
     </row>
     <row r="97" spans="1:1">
       <c r="A97">
-        <v>82</v>
+        <v>89</v>
       </c>
     </row>
     <row r="98" spans="1:1">
@@ -4257,122 +5356,122 @@
     </row>
     <row r="104" spans="1:1">
       <c r="A104">
-        <v>10049277970</v>
+        <v>196</v>
       </c>
     </row>
     <row r="105" spans="1:1">
       <c r="A105">
-        <v>196</v>
+        <v>49384.117103</v>
       </c>
     </row>
     <row r="106" spans="1:1">
       <c r="A106">
-        <v>49384.117103</v>
+        <v>38</v>
       </c>
     </row>
     <row r="107" spans="1:1">
       <c r="A107">
-        <v>38</v>
+        <v>91</v>
       </c>
     </row>
     <row r="108" spans="1:1">
       <c r="A108">
-        <v>91</v>
+        <v>96</v>
       </c>
     </row>
     <row r="109" spans="1:1">
       <c r="A109">
-        <v>96</v>
+        <v>15</v>
       </c>
     </row>
     <row r="110" spans="1:1">
       <c r="A110">
-        <v>15</v>
+        <v>50</v>
       </c>
     </row>
     <row r="111" spans="1:1">
       <c r="A111">
-        <v>50</v>
+        <v>160</v>
       </c>
     </row>
     <row r="112" spans="1:1">
       <c r="A112">
-        <v>160</v>
+        <v>380</v>
       </c>
     </row>
     <row r="113" spans="1:1">
       <c r="A113">
-        <v>380</v>
+        <v>201272</v>
       </c>
     </row>
     <row r="114" spans="1:1">
       <c r="A114">
-        <v>201272</v>
+        <v>10.5</v>
       </c>
     </row>
     <row r="115" spans="1:1">
       <c r="A115">
-        <v>10.5</v>
+        <v>8.01</v>
       </c>
     </row>
     <row r="116" spans="1:1">
       <c r="A116">
-        <v>8.01</v>
+        <v>7.68</v>
       </c>
     </row>
     <row r="117" spans="1:1">
       <c r="A117">
-        <v>7.68</v>
+        <v>8.4</v>
       </c>
     </row>
     <row r="118" spans="1:1">
       <c r="A118">
-        <v>8.4</v>
+        <v>8.300000000000001</v>
       </c>
     </row>
     <row r="119" spans="1:1">
       <c r="A119">
-        <v>8.300000000000001</v>
+        <v>12.3</v>
       </c>
     </row>
     <row r="120" spans="1:1">
       <c r="A120">
-        <v>12.3</v>
+        <v>7</v>
       </c>
     </row>
     <row r="121" spans="1:1">
       <c r="A121">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="122" spans="1:1">
       <c r="A122">
-        <v>9</v>
+        <v>5500</v>
       </c>
     </row>
     <row r="123" spans="1:1">
       <c r="A123">
-        <v>5500</v>
+        <v>0.76</v>
       </c>
     </row>
     <row r="124" spans="1:1">
       <c r="A124">
-        <v>0.76</v>
+        <v>0.05</v>
       </c>
     </row>
     <row r="125" spans="1:1">
       <c r="A125">
-        <v>0.05</v>
+        <v>2400</v>
       </c>
     </row>
     <row r="126" spans="1:1">
       <c r="A126">
-        <v>2400</v>
+        <v>14</v>
       </c>
     </row>
     <row r="127" spans="1:1">
       <c r="A127">
-        <v>14</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="128" spans="1:1">
@@ -4392,17 +5491,57 @@
     </row>
     <row r="131" spans="1:1">
       <c r="A131">
-        <v>2.5</v>
+        <v>2.3</v>
       </c>
     </row>
     <row r="132" spans="1:1">
       <c r="A132">
-        <v>3690</v>
+        <v>65</v>
       </c>
     </row>
     <row r="133" spans="1:1">
       <c r="A133">
-        <v>65</v>
+        <v>47</v>
+      </c>
+    </row>
+    <row r="134" spans="1:1">
+      <c r="A134">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="135" spans="1:1">
+      <c r="A135">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="136" spans="1:1">
+      <c r="A136">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="137" spans="1:1">
+      <c r="A137">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="138" spans="1:1">
+      <c r="A138">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="139" spans="1:1">
+      <c r="A139">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="140" spans="1:1">
+      <c r="A140">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="141" spans="1:1">
+      <c r="A141">
+        <v>78</v>
       </c>
     </row>
   </sheetData>
@@ -4412,12 +5551,2557 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1"/>
+  <dimension ref="A1:A511"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" t="s">
-        <v>417</v>
+        <v>554</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1">
+      <c r="A2">
+        <v>1.1375</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1">
+      <c r="A3">
+        <v>1.103125</v>
+      </c>
+    </row>
+    <row r="4" spans="1:1">
+      <c r="A4">
+        <v>1.084375</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1">
+      <c r="A5">
+        <v>1.005294117647059</v>
+      </c>
+    </row>
+    <row r="6" spans="1:1">
+      <c r="A6">
+        <v>1.049338364617541</v>
+      </c>
+    </row>
+    <row r="7" spans="1:1">
+      <c r="A7">
+        <v>1.018387371149503</v>
+      </c>
+    </row>
+    <row r="8" spans="1:1">
+      <c r="A8">
+        <v>1.013388888888889</v>
+      </c>
+    </row>
+    <row r="9" spans="1:1">
+      <c r="A9">
+        <v>1.008861111111111</v>
+      </c>
+    </row>
+    <row r="10" spans="1:1">
+      <c r="A10">
+        <v>1.008277777777778</v>
+      </c>
+    </row>
+    <row r="11" spans="1:1">
+      <c r="A11">
+        <v>1.061852933368728</v>
+      </c>
+    </row>
+    <row r="12" spans="1:1">
+      <c r="A12">
+        <v>1.111111111111111</v>
+      </c>
+    </row>
+    <row r="13" spans="1:1">
+      <c r="A13">
+        <v>1.081081081081081</v>
+      </c>
+    </row>
+    <row r="14" spans="1:1">
+      <c r="A14">
+        <v>1.025641025641026</v>
+      </c>
+    </row>
+    <row r="15" spans="1:1">
+      <c r="A15">
+        <v>0.8214285714285714</v>
+      </c>
+    </row>
+    <row r="16" spans="1:1">
+      <c r="A16">
+        <v>1.068092105263156</v>
+      </c>
+    </row>
+    <row r="17" spans="1:1">
+      <c r="A17">
+        <v>1.136371794871794</v>
+      </c>
+    </row>
+    <row r="18" spans="1:1">
+      <c r="A18">
+        <v>1.168625</v>
+      </c>
+    </row>
+    <row r="19" spans="1:1">
+      <c r="A19">
+        <v>1.1363125</v>
+      </c>
+    </row>
+    <row r="20" spans="1:1">
+      <c r="A20">
+        <v>0.9622988505747126</v>
+      </c>
+    </row>
+    <row r="21" spans="1:1">
+      <c r="A21">
+        <v>1.009278350515464</v>
+      </c>
+    </row>
+    <row r="22" spans="1:1">
+      <c r="A22">
+        <v>1.006529209621993</v>
+      </c>
+    </row>
+    <row r="23" spans="1:1">
+      <c r="A23">
+        <v>1.004458762886598</v>
+      </c>
+    </row>
+    <row r="24" spans="1:1">
+      <c r="A24">
+        <v>0.9867697594501716</v>
+      </c>
+    </row>
+    <row r="25" spans="1:1">
+      <c r="A25">
+        <v>0.9778350515463918</v>
+      </c>
+    </row>
+    <row r="26" spans="1:1">
+      <c r="A26">
+        <v>1.22</v>
+      </c>
+    </row>
+    <row r="27" spans="1:1">
+      <c r="A27">
+        <v>1.125</v>
+      </c>
+    </row>
+    <row r="28" spans="1:1">
+      <c r="A28">
+        <v>1.163088235294118</v>
+      </c>
+    </row>
+    <row r="29" spans="1:1">
+      <c r="A29">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="30" spans="1:1">
+      <c r="A30">
+        <v>1.2375</v>
+      </c>
+    </row>
+    <row r="31" spans="1:1">
+      <c r="A31">
+        <v>1.25</v>
+      </c>
+    </row>
+    <row r="32" spans="1:1">
+      <c r="A32">
+        <v>0.9934426229508201</v>
+      </c>
+    </row>
+    <row r="33" spans="1:1">
+      <c r="A33">
+        <v>1.020408163265306</v>
+      </c>
+    </row>
+    <row r="34" spans="1:1">
+      <c r="A34">
+        <v>1.110019646365422</v>
+      </c>
+    </row>
+    <row r="35" spans="1:1">
+      <c r="A35">
+        <v>0.983</v>
+      </c>
+    </row>
+    <row r="36" spans="1:1">
+      <c r="A36">
+        <v>0.99</v>
+      </c>
+    </row>
+    <row r="37" spans="1:1">
+      <c r="A37">
+        <v>1.3</v>
+      </c>
+    </row>
+    <row r="39" spans="1:1">
+      <c r="A39">
+        <v>1.00625</v>
+      </c>
+    </row>
+    <row r="40" spans="1:1">
+      <c r="A40">
+        <v>1.1875</v>
+      </c>
+    </row>
+    <row r="41" spans="1:1">
+      <c r="A41">
+        <v>1.075</v>
+      </c>
+    </row>
+    <row r="42" spans="1:1">
+      <c r="A42">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="1:1">
+      <c r="A43">
+        <v>1.092409596295854</v>
+      </c>
+    </row>
+    <row r="44" spans="1:1">
+      <c r="A44">
+        <v>1.0625</v>
+      </c>
+    </row>
+    <row r="45" spans="1:1">
+      <c r="A45">
+        <v>1.175</v>
+      </c>
+    </row>
+    <row r="46" spans="1:1">
+      <c r="A46">
+        <v>0.9175239389233949</v>
+      </c>
+    </row>
+    <row r="47" spans="1:1">
+      <c r="A47">
+        <v>0.975</v>
+      </c>
+    </row>
+    <row r="48" spans="1:1">
+      <c r="A48">
+        <v>0.875</v>
+      </c>
+    </row>
+    <row r="49" spans="1:1">
+      <c r="A49">
+        <v>1.14375</v>
+      </c>
+    </row>
+    <row r="50" spans="1:1">
+      <c r="A50">
+        <v>1.1584375</v>
+      </c>
+    </row>
+    <row r="51" spans="1:1">
+      <c r="A51">
+        <v>1.174166666666667</v>
+      </c>
+    </row>
+    <row r="52" spans="1:1">
+      <c r="A52">
+        <v>1.148235294117647</v>
+      </c>
+    </row>
+    <row r="53" spans="1:1">
+      <c r="A53">
+        <v>1.1</v>
+      </c>
+    </row>
+    <row r="54" spans="1:1">
+      <c r="A54">
+        <v>1.025</v>
+      </c>
+    </row>
+    <row r="55" spans="1:1">
+      <c r="A55">
+        <v>1.0125</v>
+      </c>
+    </row>
+    <row r="56" spans="1:1">
+      <c r="A56">
+        <v>0.925</v>
+      </c>
+    </row>
+    <row r="57" spans="1:1">
+      <c r="A57">
+        <v>1.1125</v>
+      </c>
+    </row>
+    <row r="58" spans="1:1">
+      <c r="A58">
+        <v>1.176470588235294</v>
+      </c>
+    </row>
+    <row r="59" spans="1:1">
+      <c r="A59">
+        <v>1.1625</v>
+      </c>
+    </row>
+    <row r="60" spans="1:1">
+      <c r="A60">
+        <v>1.225</v>
+      </c>
+    </row>
+    <row r="61" spans="1:1">
+      <c r="A61">
+        <v>1.021345268941676</v>
+      </c>
+    </row>
+    <row r="62" spans="1:1">
+      <c r="A62">
+        <v>0.9164420485175202</v>
+      </c>
+    </row>
+    <row r="63" spans="1:1">
+      <c r="A63">
+        <v>1.018268942797245</v>
+      </c>
+    </row>
+    <row r="64" spans="1:1">
+      <c r="A64">
+        <v>0.9721692718261532</v>
+      </c>
+    </row>
+    <row r="65" spans="1:1">
+      <c r="A65">
+        <v>0.9759831595062674</v>
+      </c>
+    </row>
+    <row r="66" spans="1:1">
+      <c r="A66">
+        <v>1.09653540903541</v>
+      </c>
+    </row>
+    <row r="67" spans="1:1">
+      <c r="A67">
+        <v>1.1373125</v>
+      </c>
+    </row>
+    <row r="68" spans="1:1">
+      <c r="A68">
+        <v>1.178979166666667</v>
+      </c>
+    </row>
+    <row r="69" spans="1:1">
+      <c r="A69">
+        <v>0.914</v>
+      </c>
+    </row>
+    <row r="70" spans="1:1">
+      <c r="A70">
+        <v>0.9900625</v>
+      </c>
+    </row>
+    <row r="71" spans="1:1">
+      <c r="A71">
+        <v>1.274151011252328</v>
+      </c>
+    </row>
+    <row r="72" spans="1:1">
+      <c r="A72">
+        <v>1.180555670739568</v>
+      </c>
+    </row>
+    <row r="73" spans="1:1">
+      <c r="A73">
+        <v>1.102941176470588</v>
+      </c>
+    </row>
+    <row r="74" spans="1:1">
+      <c r="A74">
+        <v>1.159863945578231</v>
+      </c>
+    </row>
+    <row r="75" spans="1:1">
+      <c r="A75">
+        <v>1.2</v>
+      </c>
+    </row>
+    <row r="76" spans="1:1">
+      <c r="A76">
+        <v>1.002237136465324</v>
+      </c>
+    </row>
+    <row r="77" spans="1:1">
+      <c r="A77">
+        <v>1.018353514109951</v>
+      </c>
+    </row>
+    <row r="78" spans="1:1">
+      <c r="A78">
+        <v>1.101965279442938</v>
+      </c>
+    </row>
+    <row r="79" spans="1:1">
+      <c r="A79">
+        <v>1.235</v>
+      </c>
+    </row>
+    <row r="80" spans="1:1">
+      <c r="A80">
+        <v>1.183333333333333</v>
+      </c>
+    </row>
+    <row r="81" spans="1:1">
+      <c r="A81">
+        <v>0.4875</v>
+      </c>
+    </row>
+    <row r="82" spans="1:1">
+      <c r="A82">
+        <v>0.4829782608695652</v>
+      </c>
+    </row>
+    <row r="83" spans="1:1">
+      <c r="A83">
+        <v>0.5860217391304348</v>
+      </c>
+    </row>
+    <row r="84" spans="1:1">
+      <c r="A84">
+        <v>0.3916326530612245</v>
+      </c>
+    </row>
+    <row r="85" spans="1:1">
+      <c r="A85">
+        <v>0.6111111111111112</v>
+      </c>
+    </row>
+    <row r="86" spans="1:1">
+      <c r="A86">
+        <v>0.9230769230769231</v>
+      </c>
+    </row>
+    <row r="87" spans="1:1">
+      <c r="A87">
+        <v>1.164315151769025</v>
+      </c>
+    </row>
+    <row r="88" spans="1:1">
+      <c r="A88">
+        <v>1.06</v>
+      </c>
+    </row>
+    <row r="89" spans="1:1">
+      <c r="A89">
+        <v>1.206666666666667</v>
+      </c>
+    </row>
+    <row r="90" spans="1:1">
+      <c r="A90">
+        <v>1.2125</v>
+      </c>
+    </row>
+    <row r="91" spans="1:1">
+      <c r="A91">
+        <v>1.0375</v>
+      </c>
+    </row>
+    <row r="92" spans="1:1">
+      <c r="A92">
+        <v>1.129625</v>
+      </c>
+    </row>
+    <row r="93" spans="1:1">
+      <c r="A93">
+        <v>1.155294117647059</v>
+      </c>
+    </row>
+    <row r="94" spans="1:1">
+      <c r="A94">
+        <v>1.205</v>
+      </c>
+    </row>
+    <row r="95" spans="1:1">
+      <c r="A95">
+        <v>1.2136875</v>
+      </c>
+    </row>
+    <row r="96" spans="1:1">
+      <c r="A96">
+        <v>1.2115625</v>
+      </c>
+    </row>
+    <row r="97" spans="1:1">
+      <c r="A97">
+        <v>1.139176470588235</v>
+      </c>
+    </row>
+    <row r="98" spans="1:1">
+      <c r="A98">
+        <v>1.042388888888889</v>
+      </c>
+    </row>
+    <row r="99" spans="1:1">
+      <c r="A99">
+        <v>1.044444444444445</v>
+      </c>
+    </row>
+    <row r="100" spans="1:1">
+      <c r="A100">
+        <v>1.087547798740395</v>
+      </c>
+    </row>
+    <row r="101" spans="1:1">
+      <c r="A101">
+        <v>0.9948992481203011</v>
+      </c>
+    </row>
+    <row r="102" spans="1:1">
+      <c r="A102">
+        <v>0.9705679943988564</v>
+      </c>
+    </row>
+    <row r="103" spans="1:1">
+      <c r="A103">
+        <v>0.9567543859649122</v>
+      </c>
+    </row>
+    <row r="104" spans="1:1">
+      <c r="A104">
+        <v>1.017125</v>
+      </c>
+    </row>
+    <row r="105" spans="1:1">
+      <c r="A105">
+        <v>1.048</v>
+      </c>
+    </row>
+    <row r="106" spans="1:1">
+      <c r="A106">
+        <v>1.215789473684211</v>
+      </c>
+    </row>
+    <row r="107" spans="1:1">
+      <c r="A107">
+        <v>0.9956504338545761</v>
+      </c>
+    </row>
+    <row r="108" spans="1:1">
+      <c r="A108">
+        <v>1.028890170900142</v>
+      </c>
+    </row>
+    <row r="109" spans="1:1">
+      <c r="A109">
+        <v>1.022513368983957</v>
+      </c>
+    </row>
+    <row r="110" spans="1:1">
+      <c r="A110">
+        <v>1.138493150684931</v>
+      </c>
+    </row>
+    <row r="111" spans="1:1">
+      <c r="A111">
+        <v>1.023875</v>
+      </c>
+    </row>
+    <row r="112" spans="1:1">
+      <c r="A112">
+        <v>1.098765432098765</v>
+      </c>
+    </row>
+    <row r="113" spans="1:1">
+      <c r="A113">
+        <v>1.27</v>
+      </c>
+    </row>
+    <row r="114" spans="1:1">
+      <c r="A114">
+        <v>1.052631578947368</v>
+      </c>
+    </row>
+    <row r="115" spans="1:1">
+      <c r="A115">
+        <v>1.032036082474227</v>
+      </c>
+    </row>
+    <row r="116" spans="1:1">
+      <c r="A116">
+        <v>1.030927835051546</v>
+      </c>
+    </row>
+    <row r="117" spans="1:1">
+      <c r="A117">
+        <v>0.9228245614035104</v>
+      </c>
+    </row>
+    <row r="118" spans="1:1">
+      <c r="A118">
+        <v>1.1561875</v>
+      </c>
+    </row>
+    <row r="119" spans="1:1">
+      <c r="A119">
+        <v>1.115121951219512</v>
+      </c>
+    </row>
+    <row r="120" spans="1:1">
+      <c r="A120">
+        <v>1.285714285714286</v>
+      </c>
+    </row>
+    <row r="121" spans="1:1">
+      <c r="A121">
+        <v>1.0925</v>
+      </c>
+    </row>
+    <row r="122" spans="1:1">
+      <c r="A122">
+        <v>1.044252873563218</v>
+      </c>
+    </row>
+    <row r="123" spans="1:1">
+      <c r="A123">
+        <v>0.9803030303030303</v>
+      </c>
+    </row>
+    <row r="124" spans="1:1">
+      <c r="A124">
+        <v>1.179039301310044</v>
+      </c>
+    </row>
+    <row r="125" spans="1:1">
+      <c r="A125">
+        <v>1.076929246123686</v>
+      </c>
+    </row>
+    <row r="126" spans="1:1">
+      <c r="A126">
+        <v>1.088077934787474</v>
+      </c>
+    </row>
+    <row r="127" spans="1:1">
+      <c r="A127">
+        <v>1.082526315789474</v>
+      </c>
+    </row>
+    <row r="128" spans="1:1">
+      <c r="A128">
+        <v>1.171894736842105</v>
+      </c>
+    </row>
+    <row r="129" spans="1:1">
+      <c r="A129">
+        <v>0.2215527733259426</v>
+      </c>
+    </row>
+    <row r="130" spans="1:1">
+      <c r="A130">
+        <v>1.295263157894737</v>
+      </c>
+    </row>
+    <row r="131" spans="1:1">
+      <c r="A131">
+        <v>0.9652509652509653</v>
+      </c>
+    </row>
+    <row r="132" spans="1:1">
+      <c r="A132">
+        <v>0.9784735812133072</v>
+      </c>
+    </row>
+    <row r="133" spans="1:1">
+      <c r="A133">
+        <v>0.9039956608208281</v>
+      </c>
+    </row>
+    <row r="134" spans="1:1">
+      <c r="A134">
+        <v>0.001135073779795687</v>
+      </c>
+    </row>
+    <row r="135" spans="1:1">
+      <c r="A135">
+        <v>1.266261460462019</v>
+      </c>
+    </row>
+    <row r="136" spans="1:1">
+      <c r="A136">
+        <v>0.07499999999999929</v>
+      </c>
+    </row>
+    <row r="137" spans="1:1">
+      <c r="A137">
+        <v>1.049203896717607</v>
+      </c>
+    </row>
+    <row r="138" spans="1:1">
+      <c r="A138">
+        <v>0.3333</v>
+      </c>
+    </row>
+    <row r="139" spans="1:1">
+      <c r="A139">
+        <v>0.275</v>
+      </c>
+    </row>
+    <row r="140" spans="1:1">
+      <c r="A140">
+        <v>1.041666666666667</v>
+      </c>
+    </row>
+    <row r="141" spans="1:1">
+      <c r="A141">
+        <v>0.7638888888888888</v>
+      </c>
+    </row>
+    <row r="142" spans="1:1">
+      <c r="A142">
+        <v>0.9412</v>
+      </c>
+    </row>
+    <row r="143" spans="1:1">
+      <c r="A143">
+        <v>0.9167000000000001</v>
+      </c>
+    </row>
+    <row r="144" spans="1:1">
+      <c r="A144">
+        <v>0.7142857142857143</v>
+      </c>
+    </row>
+    <row r="145" spans="1:1">
+      <c r="A145">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="146" spans="1:1">
+      <c r="A146">
+        <v>8.495912050318455E-05</v>
+      </c>
+    </row>
+    <row r="147" spans="1:1">
+      <c r="A147">
+        <v>1.001070326764465</v>
+      </c>
+    </row>
+    <row r="148" spans="1:1">
+      <c r="A148">
+        <v>1.074944444444444</v>
+      </c>
+    </row>
+    <row r="149" spans="1:1">
+      <c r="A149">
+        <v>1.062777777777778</v>
+      </c>
+    </row>
+    <row r="150" spans="1:1">
+      <c r="A150">
+        <v>1.085833333333333</v>
+      </c>
+    </row>
+    <row r="151" spans="1:1">
+      <c r="A151">
+        <v>0.9253333333333333</v>
+      </c>
+    </row>
+    <row r="152" spans="1:1">
+      <c r="A152">
+        <v>1.11575</v>
+      </c>
+    </row>
+    <row r="153" spans="1:1">
+      <c r="A153">
+        <v>1.075465277777778</v>
+      </c>
+    </row>
+    <row r="154" spans="1:1">
+      <c r="A154">
+        <v>0.8165289256198299</v>
+      </c>
+    </row>
+    <row r="155" spans="1:1">
+      <c r="A155">
+        <v>0.92012779552716</v>
+      </c>
+    </row>
+    <row r="156" spans="1:1">
+      <c r="A156">
+        <v>0.9724542838577928</v>
+      </c>
+    </row>
+    <row r="157" spans="1:1">
+      <c r="A157">
+        <v>0.8847944514062934</v>
+      </c>
+    </row>
+    <row r="158" spans="1:1">
+      <c r="A158">
+        <v>0.9392592592592593</v>
+      </c>
+    </row>
+    <row r="159" spans="1:1">
+      <c r="A159">
+        <v>0.65</v>
+      </c>
+    </row>
+    <row r="160" spans="1:1">
+      <c r="A160">
+        <v>0.9791666666666665</v>
+      </c>
+    </row>
+    <row r="161" spans="1:1">
+      <c r="A161">
+        <v>1.156866161616162</v>
+      </c>
+    </row>
+    <row r="162" spans="1:1">
+      <c r="A162">
+        <v>1.111740111740112</v>
+      </c>
+    </row>
+    <row r="163" spans="1:1">
+      <c r="A163">
+        <v>1.241322916666667</v>
+      </c>
+    </row>
+    <row r="164" spans="1:1">
+      <c r="A164">
+        <v>1.19034375</v>
+      </c>
+    </row>
+    <row r="165" spans="1:1">
+      <c r="A165">
+        <v>1.067555555555556</v>
+      </c>
+    </row>
+    <row r="166" spans="1:1">
+      <c r="A166">
+        <v>1.128045977011494</v>
+      </c>
+    </row>
+    <row r="167" spans="1:1">
+      <c r="A167">
+        <v>1.0022</v>
+      </c>
+    </row>
+    <row r="168" spans="1:1">
+      <c r="A168">
+        <v>1.0012</v>
+      </c>
+    </row>
+    <row r="169" spans="1:1">
+      <c r="A169">
+        <v>0.7223529411764705</v>
+      </c>
+    </row>
+    <row r="170" spans="1:1">
+      <c r="A170">
+        <v>1.03</v>
+      </c>
+    </row>
+    <row r="171" spans="1:1">
+      <c r="A171">
+        <v>1.137647058823529</v>
+      </c>
+    </row>
+    <row r="172" spans="1:1">
+      <c r="A172">
+        <v>0.9622641509433965</v>
+      </c>
+    </row>
+    <row r="173" spans="1:1">
+      <c r="A173">
+        <v>1.0431</v>
+      </c>
+    </row>
+    <row r="174" spans="1:1">
+      <c r="A174">
+        <v>0.18</v>
+      </c>
+    </row>
+    <row r="175" spans="1:1">
+      <c r="A175">
+        <v>0.15</v>
+      </c>
+    </row>
+    <row r="176" spans="1:1">
+      <c r="A176">
+        <v>1.23529705882355</v>
+      </c>
+    </row>
+    <row r="177" spans="1:1">
+      <c r="A177">
+        <v>0.9285714285714286</v>
+      </c>
+    </row>
+    <row r="178" spans="1:1">
+      <c r="A178">
+        <v>0.7</v>
+      </c>
+    </row>
+    <row r="179" spans="1:1">
+      <c r="A179">
+        <v>0.8714444444444445</v>
+      </c>
+    </row>
+    <row r="180" spans="1:1">
+      <c r="A180">
+        <v>1.03448275862069</v>
+      </c>
+    </row>
+    <row r="181" spans="1:1">
+      <c r="A181">
+        <v>1.105263157894737</v>
+      </c>
+    </row>
+    <row r="182" spans="1:1">
+      <c r="A182">
+        <v>1.235294117647059</v>
+      </c>
+    </row>
+    <row r="183" spans="1:1">
+      <c r="A183">
+        <v>0.8856499999999999</v>
+      </c>
+    </row>
+    <row r="184" spans="1:1">
+      <c r="A184">
+        <v>0.9687894736842105</v>
+      </c>
+    </row>
+    <row r="185" spans="1:1">
+      <c r="A185">
+        <v>0.9840896763821895</v>
+      </c>
+    </row>
+    <row r="186" spans="1:1">
+      <c r="A186">
+        <v>0.9313157894736841</v>
+      </c>
+    </row>
+    <row r="187" spans="1:1">
+      <c r="A187">
+        <v>0.8047368421052632</v>
+      </c>
+    </row>
+    <row r="188" spans="1:1">
+      <c r="A188">
+        <v>0.6217368421052631</v>
+      </c>
+    </row>
+    <row r="189" spans="1:1">
+      <c r="A189">
+        <v>1.276978417266187</v>
+      </c>
+    </row>
+    <row r="190" spans="1:1">
+      <c r="A190">
+        <v>1.28</v>
+      </c>
+    </row>
+    <row r="191" spans="1:1">
+      <c r="A191">
+        <v>0.976802605821255</v>
+      </c>
+    </row>
+    <row r="192" spans="1:1">
+      <c r="A192">
+        <v>1.019740259234822</v>
+      </c>
+    </row>
+    <row r="193" spans="1:1">
+      <c r="A193">
+        <v>1.03915</v>
+      </c>
+    </row>
+    <row r="194" spans="1:1">
+      <c r="A194">
+        <v>1.0572</v>
+      </c>
+    </row>
+    <row r="195" spans="1:1">
+      <c r="A195">
+        <v>1.1354375</v>
+      </c>
+    </row>
+    <row r="196" spans="1:1">
+      <c r="A196">
+        <v>1.110941176470588</v>
+      </c>
+    </row>
+    <row r="197" spans="1:1">
+      <c r="A197">
+        <v>1.005917159763314</v>
+      </c>
+    </row>
+    <row r="198" spans="1:1">
+      <c r="A198">
+        <v>0.9071117561683598</v>
+      </c>
+    </row>
+    <row r="199" spans="1:1">
+      <c r="A199">
+        <v>0.9781427363844946</v>
+      </c>
+    </row>
+    <row r="200" spans="1:1">
+      <c r="A200">
+        <v>0.9578997161778618</v>
+      </c>
+    </row>
+    <row r="201" spans="1:1">
+      <c r="A201">
+        <v>1.159776231409469</v>
+      </c>
+    </row>
+    <row r="202" spans="1:1">
+      <c r="A202">
+        <v>1.024705221785514</v>
+      </c>
+    </row>
+    <row r="203" spans="1:1">
+      <c r="A203">
+        <v>1.038011695906433</v>
+      </c>
+    </row>
+    <row r="204" spans="1:1">
+      <c r="A204">
+        <v>1.022196261682243</v>
+      </c>
+    </row>
+    <row r="205" spans="1:1">
+      <c r="A205">
+        <v>1.012291666666667</v>
+      </c>
+    </row>
+    <row r="206" spans="1:1">
+      <c r="A206">
+        <v>0.999278350515464</v>
+      </c>
+    </row>
+    <row r="207" spans="1:1">
+      <c r="A207">
+        <v>1.005</v>
+      </c>
+    </row>
+    <row r="208" spans="1:1">
+      <c r="A208">
+        <v>1.006836734693878</v>
+      </c>
+    </row>
+    <row r="209" spans="1:1">
+      <c r="A209">
+        <v>1.011111111111111</v>
+      </c>
+    </row>
+    <row r="210" spans="1:1">
+      <c r="A210">
+        <v>1.031111111111111</v>
+      </c>
+    </row>
+    <row r="211" spans="1:1">
+      <c r="A211">
+        <v>1.015217391304348</v>
+      </c>
+    </row>
+    <row r="212" spans="1:1">
+      <c r="A212">
+        <v>0.9935622317596566</v>
+      </c>
+    </row>
+    <row r="213" spans="1:1">
+      <c r="A213">
+        <v>0.3058823529411765</v>
+      </c>
+    </row>
+    <row r="214" spans="1:1">
+      <c r="A214">
+        <v>0.9210526315789473</v>
+      </c>
+    </row>
+    <row r="215" spans="1:1">
+      <c r="A215">
+        <v>0.9928888888888889</v>
+      </c>
+    </row>
+    <row r="216" spans="1:1">
+      <c r="A216">
+        <v>0.9876666666666667</v>
+      </c>
+    </row>
+    <row r="217" spans="1:1">
+      <c r="A217">
+        <v>0.4375</v>
+      </c>
+    </row>
+    <row r="218" spans="1:1">
+      <c r="A218">
+        <v>0.873</v>
+      </c>
+    </row>
+    <row r="219" spans="1:1">
+      <c r="A219">
+        <v>0.8545</v>
+      </c>
+    </row>
+    <row r="220" spans="1:1">
+      <c r="A220">
+        <v>0.7765151515151526</v>
+      </c>
+    </row>
+    <row r="221" spans="1:1">
+      <c r="A221">
+        <v>1.02974828375286</v>
+      </c>
+    </row>
+    <row r="222" spans="1:1">
+      <c r="A222">
+        <v>1.001684210526316</v>
+      </c>
+    </row>
+    <row r="223" spans="1:1">
+      <c r="A223">
+        <v>0.9184</v>
+      </c>
+    </row>
+    <row r="224" spans="1:1">
+      <c r="A224">
+        <v>1.0728</v>
+      </c>
+    </row>
+    <row r="225" spans="1:1">
+      <c r="A225">
+        <v>1.0994</v>
+      </c>
+    </row>
+    <row r="226" spans="1:1">
+      <c r="A226">
+        <v>1.073733333333333</v>
+      </c>
+    </row>
+    <row r="227" spans="1:1">
+      <c r="A227">
+        <v>0.7913</v>
+      </c>
+    </row>
+    <row r="228" spans="1:1">
+      <c r="A228">
+        <v>1.243445692883895</v>
+      </c>
+    </row>
+    <row r="229" spans="1:1">
+      <c r="A229">
+        <v>0.6776000000000001</v>
+      </c>
+    </row>
+    <row r="230" spans="1:1">
+      <c r="A230">
+        <v>1.099547511312217</v>
+      </c>
+    </row>
+    <row r="231" spans="1:1">
+      <c r="A231">
+        <v>0.8928571428571429</v>
+      </c>
+    </row>
+    <row r="232" spans="1:1">
+      <c r="A232">
+        <v>1.260869565217391</v>
+      </c>
+    </row>
+    <row r="233" spans="1:1">
+      <c r="A233">
+        <v>1.047619047619048</v>
+      </c>
+    </row>
+    <row r="234" spans="1:1">
+      <c r="A234">
+        <v>1.136363636363636</v>
+      </c>
+    </row>
+    <row r="235" spans="1:1">
+      <c r="A235">
+        <v>1.1285</v>
+      </c>
+    </row>
+    <row r="236" spans="1:1">
+      <c r="A236">
+        <v>1.013647058823529</v>
+      </c>
+    </row>
+    <row r="237" spans="1:1">
+      <c r="A237">
+        <v>0.7073170731707317</v>
+      </c>
+    </row>
+    <row r="238" spans="1:1">
+      <c r="A238">
+        <v>1.15</v>
+      </c>
+    </row>
+    <row r="239" spans="1:1">
+      <c r="A239">
+        <v>1.297222222222222</v>
+      </c>
+    </row>
+    <row r="240" spans="1:1">
+      <c r="A240">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="241" spans="1:1">
+      <c r="A241">
+        <v>1.29375</v>
+      </c>
+    </row>
+    <row r="242" spans="1:1">
+      <c r="A242">
+        <v>1.105</v>
+      </c>
+    </row>
+    <row r="243" spans="1:1">
+      <c r="A243">
+        <v>1.0663</v>
+      </c>
+    </row>
+    <row r="244" spans="1:1">
+      <c r="A244">
+        <v>1.254355400696864</v>
+      </c>
+    </row>
+    <row r="245" spans="1:1">
+      <c r="A245">
+        <v>1.004431818181818</v>
+      </c>
+    </row>
+    <row r="246" spans="1:1">
+      <c r="A246">
+        <v>1.009545454545455</v>
+      </c>
+    </row>
+    <row r="247" spans="1:1">
+      <c r="A247">
+        <v>1.012359550561798</v>
+      </c>
+    </row>
+    <row r="248" spans="1:1">
+      <c r="A248">
+        <v>1.173125</v>
+      </c>
+    </row>
+    <row r="249" spans="1:1">
+      <c r="A249">
+        <v>0.9871951219512195</v>
+      </c>
+    </row>
+    <row r="250" spans="1:1">
+      <c r="A250">
+        <v>1.147975</v>
+      </c>
+    </row>
+    <row r="251" spans="1:1">
+      <c r="A251">
+        <v>0.9523809523809523</v>
+      </c>
+    </row>
+    <row r="252" spans="1:1">
+      <c r="A252">
+        <v>1.01</v>
+      </c>
+    </row>
+    <row r="253" spans="1:1">
+      <c r="A253">
+        <v>1.176333333333333</v>
+      </c>
+    </row>
+    <row r="254" spans="1:1">
+      <c r="A254">
+        <v>1.27219833333335</v>
+      </c>
+    </row>
+    <row r="255" spans="1:1">
+      <c r="A255">
+        <v>1.1372</v>
+      </c>
+    </row>
+    <row r="256" spans="1:1">
+      <c r="A256">
+        <v>1.0245</v>
+      </c>
+    </row>
+    <row r="257" spans="1:1">
+      <c r="A257">
+        <v>0.5041</v>
+      </c>
+    </row>
+    <row r="258" spans="1:1">
+      <c r="A258">
+        <v>1.086135338345867</v>
+      </c>
+    </row>
+    <row r="259" spans="1:1">
+      <c r="A259">
+        <v>1.056612903225806</v>
+      </c>
+    </row>
+    <row r="260" spans="1:1">
+      <c r="A260">
+        <v>1.072204301075269</v>
+      </c>
+    </row>
+    <row r="261" spans="1:1">
+      <c r="A261">
+        <v>1.080941176470588</v>
+      </c>
+    </row>
+    <row r="262" spans="1:1">
+      <c r="A262">
+        <v>1.144470588235294</v>
+      </c>
+    </row>
+    <row r="263" spans="1:1">
+      <c r="A263">
+        <v>1.009180280706798</v>
+      </c>
+    </row>
+    <row r="264" spans="1:1">
+      <c r="A264">
+        <v>1.009722222222222</v>
+      </c>
+    </row>
+    <row r="265" spans="1:1">
+      <c r="A265">
+        <v>1.01010101010101</v>
+      </c>
+    </row>
+    <row r="266" spans="1:1">
+      <c r="A266">
+        <v>1.153846153846154</v>
+      </c>
+    </row>
+    <row r="267" spans="1:1">
+      <c r="A267">
+        <v>0.9941176470588236</v>
+      </c>
+    </row>
+    <row r="268" spans="1:1">
+      <c r="A268">
+        <v>1.114285714285714</v>
+      </c>
+    </row>
+    <row r="269" spans="1:1">
+      <c r="A269">
+        <v>1.083482689692428</v>
+      </c>
+    </row>
+    <row r="270" spans="1:1">
+      <c r="A270">
+        <v>1.003092869681518</v>
+      </c>
+    </row>
+    <row r="271" spans="1:1">
+      <c r="A271">
+        <v>1.053463260468791</v>
+      </c>
+    </row>
+    <row r="272" spans="1:1">
+      <c r="A272">
+        <v>0.51</v>
+      </c>
+    </row>
+    <row r="273" spans="1:1">
+      <c r="A273">
+        <v>0.44</v>
+      </c>
+    </row>
+    <row r="274" spans="1:1">
+      <c r="A274">
+        <v>1.045888138405023</v>
+      </c>
+    </row>
+    <row r="275" spans="1:1">
+      <c r="A275">
+        <v>1.137873563218391</v>
+      </c>
+    </row>
+    <row r="276" spans="1:1">
+      <c r="A276">
+        <v>1.057647058823529</v>
+      </c>
+    </row>
+    <row r="277" spans="1:1">
+      <c r="A277">
+        <v>1.082352941176471</v>
+      </c>
+    </row>
+    <row r="278" spans="1:1">
+      <c r="A278">
+        <v>1.013333333333333</v>
+      </c>
+    </row>
+    <row r="279" spans="1:1">
+      <c r="A279">
+        <v>1.039130434782609</v>
+      </c>
+    </row>
+    <row r="280" spans="1:1">
+      <c r="A280">
+        <v>0.99156641448592</v>
+      </c>
+    </row>
+    <row r="281" spans="1:1">
+      <c r="A281">
+        <v>1.015685321634592</v>
+      </c>
+    </row>
+    <row r="282" spans="1:1">
+      <c r="A282">
+        <v>1.016989795918367</v>
+      </c>
+    </row>
+    <row r="283" spans="1:1">
+      <c r="A283">
+        <v>1.1541</v>
+      </c>
+    </row>
+    <row r="284" spans="1:1">
+      <c r="A284">
+        <v>0.86</v>
+      </c>
+    </row>
+    <row r="285" spans="1:1">
+      <c r="A285">
+        <v>1.249951341040912</v>
+      </c>
+    </row>
+    <row r="286" spans="1:1">
+      <c r="A286">
+        <v>0.992</v>
+      </c>
+    </row>
+    <row r="287" spans="1:1">
+      <c r="A287">
+        <v>0.764</v>
+      </c>
+    </row>
+    <row r="288" spans="1:1">
+      <c r="A288">
+        <v>1.05</v>
+      </c>
+    </row>
+    <row r="289" spans="1:1">
+      <c r="A289">
+        <v>1.047222222222222</v>
+      </c>
+    </row>
+    <row r="290" spans="1:1">
+      <c r="A290">
+        <v>1.021505376344086</v>
+      </c>
+    </row>
+    <row r="291" spans="1:1">
+      <c r="A291">
+        <v>1.032258064516129</v>
+      </c>
+    </row>
+    <row r="292" spans="1:1">
+      <c r="A292">
+        <v>0.73775</v>
+      </c>
+    </row>
+    <row r="293" spans="1:1">
+      <c r="A293">
+        <v>0.98575</v>
+      </c>
+    </row>
+    <row r="294" spans="1:1">
+      <c r="A294">
+        <v>0.8933</v>
+      </c>
+    </row>
+    <row r="295" spans="1:1">
+      <c r="A295">
+        <v>1.23355</v>
+      </c>
+    </row>
+    <row r="296" spans="1:1">
+      <c r="A296">
+        <v>0.7855500000000001</v>
+      </c>
+    </row>
+    <row r="297" spans="1:1">
+      <c r="A297">
+        <v>0.70365</v>
+      </c>
+    </row>
+    <row r="298" spans="1:1">
+      <c r="A298">
+        <v>1.097701149425287</v>
+      </c>
+    </row>
+    <row r="299" spans="1:1">
+      <c r="A299">
+        <v>1.054597701149425</v>
+      </c>
+    </row>
+    <row r="300" spans="1:1">
+      <c r="A300">
+        <v>1.061111111111111</v>
+      </c>
+    </row>
+    <row r="301" spans="1:1">
+      <c r="A301">
+        <v>1.064516129032258</v>
+      </c>
+    </row>
+    <row r="302" spans="1:1">
+      <c r="A302">
+        <v>0.739616666666675</v>
+      </c>
+    </row>
+    <row r="303" spans="1:1">
+      <c r="A303">
+        <v>0.9852500000000001</v>
+      </c>
+    </row>
+    <row r="304" spans="1:1">
+      <c r="A304">
+        <v>1.01215</v>
+      </c>
+    </row>
+    <row r="305" spans="1:1">
+      <c r="A305">
+        <v>1.065894736842105</v>
+      </c>
+    </row>
+    <row r="306" spans="1:1">
+      <c r="A306">
+        <v>1.148421052631579</v>
+      </c>
+    </row>
+    <row r="307" spans="1:1">
+      <c r="A307">
+        <v>1.236947368421053</v>
+      </c>
+    </row>
+    <row r="308" spans="1:1">
+      <c r="A308">
+        <v>0.6077</v>
+      </c>
+    </row>
+    <row r="309" spans="1:1">
+      <c r="A309">
+        <v>1.2501</v>
+      </c>
+    </row>
+    <row r="310" spans="1:1">
+      <c r="A310">
+        <v>1.0711</v>
+      </c>
+    </row>
+    <row r="311" spans="1:1">
+      <c r="A311">
+        <v>1.038913043478261</v>
+      </c>
+    </row>
+    <row r="312" spans="1:1">
+      <c r="A312">
+        <v>1.0568938582028</v>
+      </c>
+    </row>
+    <row r="313" spans="1:1">
+      <c r="A313">
+        <v>0.97615</v>
+      </c>
+    </row>
+    <row r="314" spans="1:1">
+      <c r="A314">
+        <v>1.0326</v>
+      </c>
+    </row>
+    <row r="315" spans="1:1">
+      <c r="A315">
+        <v>0.5162</v>
+      </c>
+    </row>
+    <row r="316" spans="1:1">
+      <c r="A316">
+        <v>1.034636945020853</v>
+      </c>
+    </row>
+    <row r="317" spans="1:1">
+      <c r="A317">
+        <v>0.7892</v>
+      </c>
+    </row>
+    <row r="318" spans="1:1">
+      <c r="A318">
+        <v>1.08985854341735</v>
+      </c>
+    </row>
+    <row r="319" spans="1:1">
+      <c r="A319">
+        <v>0.9722499999999999</v>
+      </c>
+    </row>
+    <row r="320" spans="1:1">
+      <c r="A320">
+        <v>1.0594</v>
+      </c>
+    </row>
+    <row r="321" spans="1:1">
+      <c r="A321">
+        <v>0.4943</v>
+      </c>
+    </row>
+    <row r="322" spans="1:1">
+      <c r="A322">
+        <v>1.02130205659755</v>
+      </c>
+    </row>
+    <row r="323" spans="1:1">
+      <c r="A323">
+        <v>0.9591500000000001</v>
+      </c>
+    </row>
+    <row r="324" spans="1:1">
+      <c r="A324">
+        <v>0.9853000000000001</v>
+      </c>
+    </row>
+    <row r="325" spans="1:1">
+      <c r="A325">
+        <v>0.50905</v>
+      </c>
+    </row>
+    <row r="326" spans="1:1">
+      <c r="A326">
+        <v>1.29021164972635</v>
+      </c>
+    </row>
+    <row r="327" spans="1:1">
+      <c r="A327">
+        <v>1.10455</v>
+      </c>
+    </row>
+    <row r="328" spans="1:1">
+      <c r="A328">
+        <v>0.56785</v>
+      </c>
+    </row>
+    <row r="329" spans="1:1">
+      <c r="A329">
+        <v>1.13572352941175</v>
+      </c>
+    </row>
+    <row r="330" spans="1:1">
+      <c r="A330">
+        <v>0.9505</v>
+      </c>
+    </row>
+    <row r="331" spans="1:1">
+      <c r="A331">
+        <v>1.0208</v>
+      </c>
+    </row>
+    <row r="332" spans="1:1">
+      <c r="A332">
+        <v>0.4671</v>
+      </c>
+    </row>
+    <row r="333" spans="1:1">
+      <c r="A333">
+        <v>1.2493</v>
+      </c>
+    </row>
+    <row r="334" spans="1:1">
+      <c r="A334">
+        <v>0.8856000000000001</v>
+      </c>
+    </row>
+    <row r="335" spans="1:1">
+      <c r="A335">
+        <v>1.0889</v>
+      </c>
+    </row>
+    <row r="336" spans="1:1">
+      <c r="A336">
+        <v>1.2060243283327</v>
+      </c>
+    </row>
+    <row r="337" spans="1:1">
+      <c r="A337">
+        <v>0.9431999999999999</v>
+      </c>
+    </row>
+    <row r="338" spans="1:1">
+      <c r="A338">
+        <v>1.1273</v>
+      </c>
+    </row>
+    <row r="339" spans="1:1">
+      <c r="A339">
+        <v>0.4966666666666666</v>
+      </c>
+    </row>
+    <row r="340" spans="1:1">
+      <c r="A340">
+        <v>0.99249166666667</v>
+      </c>
+    </row>
+    <row r="341" spans="1:1">
+      <c r="A341">
+        <v>0.9992</v>
+      </c>
+    </row>
+    <row r="342" spans="1:1">
+      <c r="A342">
+        <v>0.9978</v>
+      </c>
+    </row>
+    <row r="343" spans="1:1">
+      <c r="A343">
+        <v>1.075268817204301</v>
+      </c>
+    </row>
+    <row r="344" spans="1:1">
+      <c r="A344">
+        <v>1.008</v>
+      </c>
+    </row>
+    <row r="345" spans="1:1">
+      <c r="A345">
+        <v>0.970873786407767</v>
+      </c>
+    </row>
+    <row r="346" spans="1:1">
+      <c r="A346">
+        <v>1.153846153846154</v>
+      </c>
+    </row>
+    <row r="347" spans="1:1">
+      <c r="A347">
+        <v>1.29445</v>
+      </c>
+    </row>
+    <row r="348" spans="1:1">
+      <c r="A348">
+        <v>1.111125</v>
+      </c>
+    </row>
+    <row r="349" spans="1:1">
+      <c r="A349">
+        <v>1.10125</v>
+      </c>
+    </row>
+    <row r="350" spans="1:1">
+      <c r="A350">
+        <v>1.150196428571431</v>
+      </c>
+    </row>
+    <row r="351" spans="1:1">
+      <c r="A351">
+        <v>1.1435</v>
+      </c>
+    </row>
+    <row r="352" spans="1:1">
+      <c r="A352">
+        <v>1.063333333333333</v>
+      </c>
+    </row>
+    <row r="353" spans="1:1">
+      <c r="A353">
+        <v>1.022666666666667</v>
+      </c>
+    </row>
+    <row r="354" spans="1:1">
+      <c r="A354">
+        <v>1.18305</v>
+      </c>
+    </row>
+    <row r="355" spans="1:1">
+      <c r="A355">
+        <v>1.1136</v>
+      </c>
+    </row>
+    <row r="356" spans="1:1">
+      <c r="A356">
+        <v>1.0453</v>
+      </c>
+    </row>
+    <row r="357" spans="1:1">
+      <c r="A357">
+        <v>1.2507</v>
+      </c>
+    </row>
+    <row r="358" spans="1:1">
+      <c r="A358">
+        <v>1.180555555555556</v>
+      </c>
+    </row>
+    <row r="359" spans="1:1">
+      <c r="A359">
+        <v>1.24</v>
+      </c>
+    </row>
+    <row r="360" spans="1:1">
+      <c r="A360">
+        <v>0.98</v>
+      </c>
+    </row>
+    <row r="361" spans="1:1">
+      <c r="A361">
+        <v>1.273242841204909</v>
+      </c>
+    </row>
+    <row r="362" spans="1:1">
+      <c r="A362">
+        <v>1.026574917163008</v>
+      </c>
+    </row>
+    <row r="363" spans="1:1">
+      <c r="A363">
+        <v>0.9628</v>
+      </c>
+    </row>
+    <row r="364" spans="1:1">
+      <c r="A364">
+        <v>0.9878</v>
+      </c>
+    </row>
+    <row r="365" spans="1:1">
+      <c r="A365">
+        <v>0.9887</v>
+      </c>
+    </row>
+    <row r="366" spans="1:1">
+      <c r="A366">
+        <v>0.96</v>
+      </c>
+    </row>
+    <row r="367" spans="1:1">
+      <c r="A367">
+        <v>0.9836</v>
+      </c>
+    </row>
+    <row r="368" spans="1:1">
+      <c r="A368">
+        <v>0.993</v>
+      </c>
+    </row>
+    <row r="369" spans="1:1">
+      <c r="A369">
+        <v>0.9439</v>
+      </c>
+    </row>
+    <row r="370" spans="1:1">
+      <c r="A370">
+        <v>0.9883</v>
+      </c>
+    </row>
+    <row r="371" spans="1:1">
+      <c r="A371">
+        <v>0.9799</v>
+      </c>
+    </row>
+    <row r="372" spans="1:1">
+      <c r="A372">
+        <v>0.95802222222222</v>
+      </c>
+    </row>
+    <row r="373" spans="1:1">
+      <c r="A373">
+        <v>0.9778</v>
+      </c>
+    </row>
+    <row r="374" spans="1:1">
+      <c r="A374">
+        <v>0.9961</v>
+      </c>
+    </row>
+    <row r="375" spans="1:1">
+      <c r="A375">
+        <v>0.9356</v>
+      </c>
+    </row>
+    <row r="376" spans="1:1">
+      <c r="A376">
+        <v>0.9667</v>
+      </c>
+    </row>
+    <row r="377" spans="1:1">
+      <c r="A377">
+        <v>1.2144</v>
+      </c>
+    </row>
+    <row r="378" spans="1:1">
+      <c r="A378">
+        <v>1.051428571428571</v>
+      </c>
+    </row>
+    <row r="379" spans="1:1">
+      <c r="A379">
+        <v>0.9875156054931337</v>
+      </c>
+    </row>
+    <row r="380" spans="1:1">
+      <c r="A380">
+        <v>1.024739583333333</v>
+      </c>
+    </row>
+    <row r="381" spans="1:1">
+      <c r="A381">
+        <v>0.9404761904761905</v>
+      </c>
+    </row>
+    <row r="382" spans="1:1">
+      <c r="A382">
+        <v>1.227642276422764</v>
+      </c>
+    </row>
+    <row r="383" spans="1:1">
+      <c r="A383">
+        <v>0.06521739130434782</v>
+      </c>
+    </row>
+    <row r="384" spans="1:1">
+      <c r="A384">
+        <v>1.222222222222222</v>
+      </c>
+    </row>
+    <row r="385" spans="1:1">
+      <c r="A385">
+        <v>1.051818181818182</v>
+      </c>
+    </row>
+    <row r="386" spans="1:1">
+      <c r="A386">
+        <v>0.9186875000000001</v>
+      </c>
+    </row>
+    <row r="387" spans="1:1">
+      <c r="A387">
+        <v>1.188118811881177</v>
+      </c>
+    </row>
+    <row r="388" spans="1:1">
+      <c r="A388">
+        <v>0.05521811154058531</v>
+      </c>
+    </row>
+    <row r="389" spans="1:1">
+      <c r="A389">
+        <v>0.05696382796923953</v>
+      </c>
+    </row>
+    <row r="390" spans="1:1">
+      <c r="A390">
+        <v>0.06060606060606061</v>
+      </c>
+    </row>
+    <row r="391" spans="1:1">
+      <c r="A391">
+        <v>1.142857142857143</v>
+      </c>
+    </row>
+    <row r="392" spans="1:1">
+      <c r="A392">
+        <v>1.067318562735053</v>
+      </c>
+    </row>
+    <row r="393" spans="1:1">
+      <c r="A393">
+        <v>1.083552547063557</v>
+      </c>
+    </row>
+    <row r="394" spans="1:1">
+      <c r="A394">
+        <v>1.176421052631579</v>
+      </c>
+    </row>
+    <row r="395" spans="1:1">
+      <c r="A395">
+        <v>1.104253086419756</v>
+      </c>
+    </row>
+    <row r="396" spans="1:1">
+      <c r="A396">
+        <v>0.8333333333333334</v>
+      </c>
+    </row>
+    <row r="397" spans="1:1">
+      <c r="A397">
+        <v>0.4761904761904762</v>
+      </c>
+    </row>
+    <row r="398" spans="1:1">
+      <c r="A398">
+        <v>0.5263157894736842</v>
+      </c>
+    </row>
+    <row r="399" spans="1:1">
+      <c r="A399">
+        <v>1.046148213048083</v>
+      </c>
+    </row>
+    <row r="400" spans="1:1">
+      <c r="A400">
+        <v>0.4422137218917903</v>
+      </c>
+    </row>
+    <row r="401" spans="1:1">
+      <c r="A401">
+        <v>0.3083421981715308</v>
+      </c>
+    </row>
+    <row r="402" spans="1:1">
+      <c r="A402">
+        <v>0.2521</v>
+      </c>
+    </row>
+    <row r="403" spans="1:1">
+      <c r="A403">
+        <v>1.265346087218498</v>
+      </c>
+    </row>
+    <row r="404" spans="1:1">
+      <c r="A404">
+        <v>1.19632557145909</v>
+      </c>
+    </row>
+    <row r="405" spans="1:1">
+      <c r="A405">
+        <v>0.9974088014033367</v>
+      </c>
+    </row>
+    <row r="406" spans="1:1">
+      <c r="A406">
+        <v>1.01515306122449</v>
+      </c>
+    </row>
+    <row r="407" spans="1:1">
+      <c r="A407">
+        <v>1.017908163265306</v>
+      </c>
+    </row>
+    <row r="408" spans="1:1">
+      <c r="A408">
+        <v>1.110221510541767</v>
+      </c>
+    </row>
+    <row r="409" spans="1:1">
+      <c r="A409">
+        <v>1.049629629629629</v>
+      </c>
+    </row>
+    <row r="410" spans="1:1">
+      <c r="A410">
+        <v>0.9364705882352941</v>
+      </c>
+    </row>
+    <row r="411" spans="1:1">
+      <c r="A411">
+        <v>1.077333333333333</v>
+      </c>
+    </row>
+    <row r="412" spans="1:1">
+      <c r="A412">
+        <v>1.000666666666667</v>
+      </c>
+    </row>
+    <row r="413" spans="1:1">
+      <c r="A413">
+        <v>1.035555555555556</v>
+      </c>
+    </row>
+    <row r="414" spans="1:1">
+      <c r="A414">
+        <v>1.2515</v>
+      </c>
+    </row>
+    <row r="415" spans="1:1">
+      <c r="A415">
+        <v>0.87</v>
+      </c>
+    </row>
+    <row r="416" spans="1:1">
+      <c r="A416">
+        <v>0.97345</v>
+      </c>
+    </row>
+    <row r="417" spans="1:1">
+      <c r="A417">
+        <v>1.115925</v>
+      </c>
+    </row>
+    <row r="418" spans="1:1">
+      <c r="A418">
+        <v>0.8</v>
+      </c>
+    </row>
+    <row r="419" spans="1:1">
+      <c r="A419">
+        <v>1.130925</v>
+      </c>
+    </row>
+    <row r="420" spans="1:1">
+      <c r="A420">
+        <v>1.142996108949417</v>
+      </c>
+    </row>
+    <row r="421" spans="1:1">
+      <c r="A421">
+        <v>1.05225</v>
+      </c>
+    </row>
+    <row r="422" spans="1:1">
+      <c r="A422">
+        <v>0.5683</v>
+      </c>
+    </row>
+    <row r="423" spans="1:1">
+      <c r="A423">
+        <v>1.134</v>
+      </c>
+    </row>
+    <row r="424" spans="1:1">
+      <c r="A424">
+        <v>1.0655</v>
+      </c>
+    </row>
+    <row r="425" spans="1:1">
+      <c r="A425">
+        <v>0.8033</v>
+      </c>
+    </row>
+    <row r="426" spans="1:1">
+      <c r="A426">
+        <v>1.2154</v>
+      </c>
+    </row>
+    <row r="427" spans="1:1">
+      <c r="A427">
+        <v>1.0875</v>
+      </c>
+    </row>
+    <row r="428" spans="1:1">
+      <c r="A428">
+        <v>0.9564</v>
+      </c>
+    </row>
+    <row r="429" spans="1:1">
+      <c r="A429">
+        <v>1.100917431192661</v>
+      </c>
+    </row>
+    <row r="430" spans="1:1">
+      <c r="A430">
+        <v>0.997</v>
+      </c>
+    </row>
+    <row r="431" spans="1:1">
+      <c r="A431">
+        <v>0.9913</v>
+      </c>
+    </row>
+    <row r="432" spans="1:1">
+      <c r="A432">
+        <v>0.9986</v>
+      </c>
+    </row>
+    <row r="433" spans="1:1">
+      <c r="A433">
+        <v>1.145833333333333</v>
+      </c>
+    </row>
+    <row r="434" spans="1:1">
+      <c r="A434">
+        <v>1.001761363636364</v>
+      </c>
+    </row>
+    <row r="435" spans="1:1">
+      <c r="A435">
+        <v>1.093662217185824</v>
+      </c>
+    </row>
+    <row r="436" spans="1:1">
+      <c r="A436">
+        <v>0.9082402811130974</v>
+      </c>
+    </row>
+    <row r="437" spans="1:1">
+      <c r="A437">
+        <v>0.9739999999999999</v>
+      </c>
+    </row>
+    <row r="438" spans="1:1">
+      <c r="A438">
+        <v>0.9625</v>
+      </c>
+    </row>
+    <row r="439" spans="1:1">
+      <c r="A439">
+        <v>0.7875</v>
+      </c>
+    </row>
+    <row r="440" spans="1:1">
+      <c r="A440">
+        <v>0.8375</v>
+      </c>
+    </row>
+    <row r="441" spans="1:1">
+      <c r="A441">
+        <v>1.15625</v>
+      </c>
+    </row>
+    <row r="442" spans="1:1">
+      <c r="A442">
+        <v>1.081444444444444</v>
+      </c>
+    </row>
+    <row r="443" spans="1:1">
+      <c r="A443">
+        <v>0.9841428571428571</v>
+      </c>
+    </row>
+    <row r="444" spans="1:1">
+      <c r="A444">
+        <v>1.02725</v>
+      </c>
+    </row>
+    <row r="445" spans="1:1">
+      <c r="A445">
+        <v>1.016842105263158</v>
+      </c>
+    </row>
+    <row r="446" spans="1:1">
+      <c r="A446">
+        <v>0.8820618556701031</v>
+      </c>
+    </row>
+    <row r="447" spans="1:1">
+      <c r="A447">
+        <v>1.043777777777778</v>
+      </c>
+    </row>
+    <row r="448" spans="1:1">
+      <c r="A448">
+        <v>0.9892307692307691</v>
+      </c>
+    </row>
+    <row r="449" spans="1:1">
+      <c r="A449">
+        <v>0.9583333333333333</v>
+      </c>
+    </row>
+    <row r="450" spans="1:1">
+      <c r="A450">
+        <v>1.006340206185567</v>
+      </c>
+    </row>
+    <row r="451" spans="1:1">
+      <c r="A451">
+        <v>1.1338</v>
+      </c>
+    </row>
+    <row r="452" spans="1:1">
+      <c r="A452">
+        <v>1.19375</v>
+      </c>
+    </row>
+    <row r="453" spans="1:1">
+      <c r="A453">
+        <v>1.096947368421053</v>
+      </c>
+    </row>
+    <row r="454" spans="1:1">
+      <c r="A454">
+        <v>0.7692307692307692</v>
+      </c>
+    </row>
+    <row r="455" spans="1:1">
+      <c r="A455">
+        <v>1.152200012207031</v>
+      </c>
+    </row>
+    <row r="456" spans="1:1">
+      <c r="A456">
+        <v>1.129400024414062</v>
+      </c>
+    </row>
+    <row r="457" spans="1:1">
+      <c r="A457">
+        <v>1.106100006103516</v>
+      </c>
+    </row>
+    <row r="458" spans="1:1">
+      <c r="A458">
+        <v>1.104300003051758</v>
+      </c>
+    </row>
+    <row r="459" spans="1:1">
+      <c r="A459">
+        <v>1.033499984741211</v>
+      </c>
+    </row>
+    <row r="460" spans="1:1">
+      <c r="A460">
+        <v>1.03379997253418</v>
+      </c>
+    </row>
+    <row r="461" spans="1:1">
+      <c r="A461">
+        <v>1.006500015258789</v>
+      </c>
+    </row>
+    <row r="462" spans="1:1">
+      <c r="A462">
+        <v>0.9988999938964844</v>
+      </c>
+    </row>
+    <row r="463" spans="1:1">
+      <c r="A463">
+        <v>0.9608999633789063</v>
+      </c>
+    </row>
+    <row r="464" spans="1:1">
+      <c r="A464">
+        <v>1.009700012207031</v>
+      </c>
+    </row>
+    <row r="465" spans="1:1">
+      <c r="A465">
+        <v>1.016699981689453</v>
+      </c>
+    </row>
+    <row r="466" spans="1:1">
+      <c r="A466">
+        <v>1.060899963378906</v>
+      </c>
+    </row>
+    <row r="467" spans="1:1">
+      <c r="A467">
+        <v>1.033899993896484</v>
+      </c>
+    </row>
+    <row r="468" spans="1:1">
+      <c r="A468">
+        <v>1.110899963378906</v>
+      </c>
+    </row>
+    <row r="469" spans="1:1">
+      <c r="A469">
+        <v>1.192300033569336</v>
+      </c>
+    </row>
+    <row r="470" spans="1:1">
+      <c r="A470">
+        <v>0.95</v>
+      </c>
+    </row>
+    <row r="471" spans="1:1">
+      <c r="A471">
+        <v>0.97</v>
+      </c>
+    </row>
+    <row r="472" spans="1:1">
+      <c r="A472">
+        <v>0.9875</v>
+      </c>
+    </row>
+    <row r="473" spans="1:1">
+      <c r="A473">
+        <v>0.9817</v>
+      </c>
+    </row>
+    <row r="474" spans="1:1">
+      <c r="A474">
+        <v>0.9937999999999999</v>
+      </c>
+    </row>
+    <row r="475" spans="1:1">
+      <c r="A475">
+        <v>0.9286</v>
+      </c>
+    </row>
+    <row r="476" spans="1:1">
+      <c r="A476">
+        <v>0.9917</v>
+      </c>
+    </row>
+    <row r="477" spans="1:1">
+      <c r="A477">
+        <v>0.9975000000000001</v>
+      </c>
+    </row>
+    <row r="478" spans="1:1">
+      <c r="A478">
+        <v>0.9740000000000001</v>
+      </c>
+    </row>
+    <row r="479" spans="1:1">
+      <c r="A479">
+        <v>0.9112</v>
+      </c>
+    </row>
+    <row r="480" spans="1:1">
+      <c r="A480">
+        <v>0.9451000000000001</v>
+      </c>
+    </row>
+    <row r="481" spans="1:1">
+      <c r="A481">
+        <v>0.8643000000000001</v>
+      </c>
+    </row>
+    <row r="482" spans="1:1">
+      <c r="A482">
+        <v>0.9399999999999999</v>
+      </c>
+    </row>
+    <row r="483" spans="1:1">
+      <c r="A483">
+        <v>0.946</v>
+      </c>
+    </row>
+    <row r="484" spans="1:1">
+      <c r="A484">
+        <v>0.8432999999999999</v>
+      </c>
+    </row>
+    <row r="485" spans="1:1">
+      <c r="A485">
+        <v>0.9159999999999999</v>
+      </c>
+    </row>
+    <row r="486" spans="1:1">
+      <c r="A486">
+        <v>0.84</v>
+      </c>
+    </row>
+    <row r="487" spans="1:1">
+      <c r="A487">
+        <v>0.9</v>
+      </c>
+    </row>
+    <row r="488" spans="1:1">
+      <c r="A488">
+        <v>0.9925</v>
+      </c>
+    </row>
+    <row r="489" spans="1:1">
+      <c r="A489">
+        <v>0.9151000213623047</v>
+      </c>
+    </row>
+    <row r="490" spans="1:1">
+      <c r="A490">
+        <v>0.8667</v>
+      </c>
+    </row>
+    <row r="491" spans="1:1">
+      <c r="A491">
+        <v>0.8895999999999999</v>
+      </c>
+    </row>
+    <row r="492" spans="1:1">
+      <c r="A492">
+        <v>0.9375</v>
+      </c>
+    </row>
+    <row r="493" spans="1:1">
+      <c r="A493">
+        <v>0.9417</v>
+      </c>
+    </row>
+    <row r="494" spans="1:1">
+      <c r="A494">
+        <v>0.9095</v>
+      </c>
+    </row>
+    <row r="495" spans="1:1">
+      <c r="A495">
+        <v>0.9773999999999999</v>
+      </c>
+    </row>
+    <row r="496" spans="1:1">
+      <c r="A496">
+        <v>0.8625</v>
+      </c>
+    </row>
+    <row r="497" spans="1:1">
+      <c r="A497">
+        <v>0.93</v>
+      </c>
+    </row>
+    <row r="498" spans="1:1">
+      <c r="A498">
+        <v>0.7368421052631579</v>
+      </c>
+    </row>
+    <row r="499" spans="1:1">
+      <c r="A499">
+        <v>0.8780487804878049</v>
+      </c>
+    </row>
+    <row r="500" spans="1:1">
+      <c r="A500">
+        <v>0.9795918367346939</v>
+      </c>
+    </row>
+    <row r="501" spans="1:1">
+      <c r="A501">
+        <v>0.987012987012987</v>
+      </c>
+    </row>
+    <row r="502" spans="1:1">
+      <c r="A502">
+        <v>0.9890109890109891</v>
+      </c>
+    </row>
+    <row r="503" spans="1:1">
+      <c r="A503">
+        <v>0.9333333333333333</v>
+      </c>
+    </row>
+    <row r="504" spans="1:1">
+      <c r="A504">
+        <v>0.9468085106382979</v>
+      </c>
+    </row>
+    <row r="505" spans="1:1">
+      <c r="A505">
+        <v>0.9690721649484536</v>
+      </c>
+    </row>
+    <row r="506" spans="1:1">
+      <c r="A506">
+        <v>0.9666666666666667</v>
+      </c>
+    </row>
+    <row r="507" spans="1:1">
+      <c r="A507">
+        <v>0.9897959183673469</v>
+      </c>
+    </row>
+    <row r="508" spans="1:1">
+      <c r="A508">
+        <v>0.9487179487179487</v>
+      </c>
+    </row>
+    <row r="509" spans="1:1">
+      <c r="A509">
+        <v>0.9473684210526315</v>
+      </c>
+    </row>
+    <row r="510" spans="1:1">
+      <c r="A510">
+        <v>0.9693877551020408</v>
+      </c>
+    </row>
+    <row r="511" spans="1:1">
+      <c r="A511">
+        <v>0.8571428571428571</v>
       </c>
     </row>
   </sheetData>
@@ -4427,12 +8111,3392 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1"/>
+  <dimension ref="A1:A678"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" t="s">
-        <v>418</v>
+        <v>555</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1">
+      <c r="A2">
+        <v>1.1375</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1">
+      <c r="A3">
+        <v>1.103125</v>
+      </c>
+    </row>
+    <row r="4" spans="1:1">
+      <c r="A4">
+        <v>1.084375</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1">
+      <c r="A5">
+        <v>1.005294117647059</v>
+      </c>
+    </row>
+    <row r="6" spans="1:1">
+      <c r="A6">
+        <v>1.049338364617541</v>
+      </c>
+    </row>
+    <row r="7" spans="1:1">
+      <c r="A7">
+        <v>1.018387371149503</v>
+      </c>
+    </row>
+    <row r="8" spans="1:1">
+      <c r="A8">
+        <v>1.013388888888889</v>
+      </c>
+    </row>
+    <row r="9" spans="1:1">
+      <c r="A9">
+        <v>1.008861111111111</v>
+      </c>
+    </row>
+    <row r="10" spans="1:1">
+      <c r="A10">
+        <v>1.008277777777778</v>
+      </c>
+    </row>
+    <row r="11" spans="1:1">
+      <c r="A11">
+        <v>1.061852933368728</v>
+      </c>
+    </row>
+    <row r="12" spans="1:1">
+      <c r="A12">
+        <v>1.111111111111111</v>
+      </c>
+    </row>
+    <row r="13" spans="1:1">
+      <c r="A13">
+        <v>1.081081081081081</v>
+      </c>
+    </row>
+    <row r="14" spans="1:1">
+      <c r="A14">
+        <v>1.025641025641026</v>
+      </c>
+    </row>
+    <row r="15" spans="1:1">
+      <c r="A15">
+        <v>0.8214285714285714</v>
+      </c>
+    </row>
+    <row r="16" spans="1:1">
+      <c r="A16">
+        <v>1.068092105263156</v>
+      </c>
+    </row>
+    <row r="17" spans="1:1">
+      <c r="A17">
+        <v>1.136371794871794</v>
+      </c>
+    </row>
+    <row r="18" spans="1:1">
+      <c r="A18">
+        <v>1.168625</v>
+      </c>
+    </row>
+    <row r="19" spans="1:1">
+      <c r="A19">
+        <v>1.1363125</v>
+      </c>
+    </row>
+    <row r="20" spans="1:1">
+      <c r="A20">
+        <v>0.9622988505747126</v>
+      </c>
+    </row>
+    <row r="21" spans="1:1">
+      <c r="A21">
+        <v>1.009278350515464</v>
+      </c>
+    </row>
+    <row r="22" spans="1:1">
+      <c r="A22">
+        <v>1.006529209621993</v>
+      </c>
+    </row>
+    <row r="23" spans="1:1">
+      <c r="A23">
+        <v>1.004458762886598</v>
+      </c>
+    </row>
+    <row r="24" spans="1:1">
+      <c r="A24">
+        <v>0.9867697594501716</v>
+      </c>
+    </row>
+    <row r="25" spans="1:1">
+      <c r="A25">
+        <v>0.9778350515463918</v>
+      </c>
+    </row>
+    <row r="26" spans="1:1">
+      <c r="A26">
+        <v>1.22</v>
+      </c>
+    </row>
+    <row r="27" spans="1:1">
+      <c r="A27">
+        <v>1.125</v>
+      </c>
+    </row>
+    <row r="28" spans="1:1">
+      <c r="A28">
+        <v>1.163088235294118</v>
+      </c>
+    </row>
+    <row r="29" spans="1:1">
+      <c r="A29">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="30" spans="1:1">
+      <c r="A30">
+        <v>1.2375</v>
+      </c>
+    </row>
+    <row r="31" spans="1:1">
+      <c r="A31">
+        <v>1.25</v>
+      </c>
+    </row>
+    <row r="32" spans="1:1">
+      <c r="A32">
+        <v>0.9934426229508201</v>
+      </c>
+    </row>
+    <row r="33" spans="1:1">
+      <c r="A33">
+        <v>1.020408163265306</v>
+      </c>
+    </row>
+    <row r="34" spans="1:1">
+      <c r="A34">
+        <v>1.110019646365422</v>
+      </c>
+    </row>
+    <row r="35" spans="1:1">
+      <c r="A35">
+        <v>0.983</v>
+      </c>
+    </row>
+    <row r="36" spans="1:1">
+      <c r="A36">
+        <v>0.99</v>
+      </c>
+    </row>
+    <row r="37" spans="1:1">
+      <c r="A37">
+        <v>5.756600000000013</v>
+      </c>
+    </row>
+    <row r="38" spans="1:1">
+      <c r="A38">
+        <v>4.553191489361702</v>
+      </c>
+    </row>
+    <row r="39" spans="1:1">
+      <c r="A39">
+        <v>10.90909090909091</v>
+      </c>
+    </row>
+    <row r="40" spans="1:1">
+      <c r="A40">
+        <v>10.19047619047619</v>
+      </c>
+    </row>
+    <row r="42" spans="1:1">
+      <c r="A42">
+        <v>1.00625</v>
+      </c>
+    </row>
+    <row r="43" spans="1:1">
+      <c r="A43">
+        <v>1.1875</v>
+      </c>
+    </row>
+    <row r="44" spans="1:1">
+      <c r="A44">
+        <v>1.075</v>
+      </c>
+    </row>
+    <row r="45" spans="1:1">
+      <c r="A45">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="1:1">
+      <c r="A46">
+        <v>1.092409596295854</v>
+      </c>
+    </row>
+    <row r="47" spans="1:1">
+      <c r="A47">
+        <v>1.0625</v>
+      </c>
+    </row>
+    <row r="48" spans="1:1">
+      <c r="A48">
+        <v>1.175</v>
+      </c>
+    </row>
+    <row r="49" spans="1:1">
+      <c r="A49">
+        <v>0.9175239389233949</v>
+      </c>
+    </row>
+    <row r="50" spans="1:1">
+      <c r="A50">
+        <v>0.975</v>
+      </c>
+    </row>
+    <row r="51" spans="1:1">
+      <c r="A51">
+        <v>0.875</v>
+      </c>
+    </row>
+    <row r="52" spans="1:1">
+      <c r="A52">
+        <v>1.14375</v>
+      </c>
+    </row>
+    <row r="53" spans="1:1">
+      <c r="A53">
+        <v>1.1584375</v>
+      </c>
+    </row>
+    <row r="54" spans="1:1">
+      <c r="A54">
+        <v>1.174166666666667</v>
+      </c>
+    </row>
+    <row r="55" spans="1:1">
+      <c r="A55">
+        <v>1.148235294117647</v>
+      </c>
+    </row>
+    <row r="56" spans="1:1">
+      <c r="A56">
+        <v>1.1</v>
+      </c>
+    </row>
+    <row r="57" spans="1:1">
+      <c r="A57">
+        <v>1.025</v>
+      </c>
+    </row>
+    <row r="58" spans="1:1">
+      <c r="A58">
+        <v>1.0125</v>
+      </c>
+    </row>
+    <row r="59" spans="1:1">
+      <c r="A59">
+        <v>0.925</v>
+      </c>
+    </row>
+    <row r="60" spans="1:1">
+      <c r="A60">
+        <v>1.1125</v>
+      </c>
+    </row>
+    <row r="61" spans="1:1">
+      <c r="A61">
+        <v>1.176470588235294</v>
+      </c>
+    </row>
+    <row r="62" spans="1:1">
+      <c r="A62">
+        <v>1.1625</v>
+      </c>
+    </row>
+    <row r="63" spans="1:1">
+      <c r="A63">
+        <v>1.225</v>
+      </c>
+    </row>
+    <row r="64" spans="1:1">
+      <c r="A64">
+        <v>1.021345268941676</v>
+      </c>
+    </row>
+    <row r="65" spans="1:1">
+      <c r="A65">
+        <v>0.9164420485175202</v>
+      </c>
+    </row>
+    <row r="66" spans="1:1">
+      <c r="A66">
+        <v>1.018268942797245</v>
+      </c>
+    </row>
+    <row r="67" spans="1:1">
+      <c r="A67">
+        <v>0.9721692718261532</v>
+      </c>
+    </row>
+    <row r="68" spans="1:1">
+      <c r="A68">
+        <v>0.9759831595062674</v>
+      </c>
+    </row>
+    <row r="69" spans="1:1">
+      <c r="A69">
+        <v>1.09653540903541</v>
+      </c>
+    </row>
+    <row r="70" spans="1:1">
+      <c r="A70">
+        <v>1.1373125</v>
+      </c>
+    </row>
+    <row r="71" spans="1:1">
+      <c r="A71">
+        <v>1.178979166666667</v>
+      </c>
+    </row>
+    <row r="72" spans="1:1">
+      <c r="A72">
+        <v>0.914</v>
+      </c>
+    </row>
+    <row r="73" spans="1:1">
+      <c r="A73">
+        <v>0.9900625</v>
+      </c>
+    </row>
+    <row r="74" spans="1:1">
+      <c r="A74">
+        <v>52.60305720909686</v>
+      </c>
+    </row>
+    <row r="75" spans="1:1">
+      <c r="A75">
+        <v>56.32131658729979</v>
+      </c>
+    </row>
+    <row r="76" spans="1:1">
+      <c r="A76">
+        <v>15.38671074380166</v>
+      </c>
+    </row>
+    <row r="77" spans="1:1">
+      <c r="A77">
+        <v>8.24295554164058</v>
+      </c>
+    </row>
+    <row r="78" spans="1:1">
+      <c r="A78">
+        <v>4.761904761904762</v>
+      </c>
+    </row>
+    <row r="79" spans="1:1">
+      <c r="A79">
+        <v>59.18396903047894</v>
+      </c>
+    </row>
+    <row r="80" spans="1:1">
+      <c r="A80">
+        <v>26.76728254883809</v>
+      </c>
+    </row>
+    <row r="81" spans="1:1">
+      <c r="A81">
+        <v>20.3143460949464</v>
+      </c>
+    </row>
+    <row r="82" spans="1:1">
+      <c r="A82">
+        <v>18.78904430655509</v>
+      </c>
+    </row>
+    <row r="83" spans="1:1">
+      <c r="A83">
+        <v>41.2280701754386</v>
+      </c>
+    </row>
+    <row r="84" spans="1:1">
+      <c r="A84">
+        <v>16.1399999999996</v>
+      </c>
+    </row>
+    <row r="85" spans="1:1">
+      <c r="A85">
+        <v>16.66666666666667</v>
+      </c>
+    </row>
+    <row r="86" spans="1:1">
+      <c r="A86">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="87" spans="1:1">
+      <c r="A87">
+        <v>12.5</v>
+      </c>
+    </row>
+    <row r="88" spans="1:1">
+      <c r="A88">
+        <v>1.274151011252328</v>
+      </c>
+    </row>
+    <row r="89" spans="1:1">
+      <c r="A89">
+        <v>1.180555670739568</v>
+      </c>
+    </row>
+    <row r="90" spans="1:1">
+      <c r="A90">
+        <v>1.468479758156837</v>
+      </c>
+    </row>
+    <row r="91" spans="1:1">
+      <c r="A91">
+        <v>1.102941176470588</v>
+      </c>
+    </row>
+    <row r="92" spans="1:1">
+      <c r="A92">
+        <v>1.412429378531074</v>
+      </c>
+    </row>
+    <row r="93" spans="1:1">
+      <c r="A93">
+        <v>1.159863945578231</v>
+      </c>
+    </row>
+    <row r="94" spans="1:1">
+      <c r="A94">
+        <v>1.2</v>
+      </c>
+    </row>
+    <row r="95" spans="1:1">
+      <c r="A95">
+        <v>1.002237136465324</v>
+      </c>
+    </row>
+    <row r="96" spans="1:1">
+      <c r="A96">
+        <v>1.018353514109951</v>
+      </c>
+    </row>
+    <row r="97" spans="1:1">
+      <c r="A97">
+        <v>1.101965279442938</v>
+      </c>
+    </row>
+    <row r="98" spans="1:1">
+      <c r="A98">
+        <v>1.525</v>
+      </c>
+    </row>
+    <row r="99" spans="1:1">
+      <c r="A99">
+        <v>1.46</v>
+      </c>
+    </row>
+    <row r="100" spans="1:1">
+      <c r="A100">
+        <v>1.235</v>
+      </c>
+    </row>
+    <row r="101" spans="1:1">
+      <c r="A101">
+        <v>1.75</v>
+      </c>
+    </row>
+    <row r="102" spans="1:1">
+      <c r="A102">
+        <v>1.183333333333333</v>
+      </c>
+    </row>
+    <row r="103" spans="1:1">
+      <c r="A103">
+        <v>1.61</v>
+      </c>
+    </row>
+    <row r="104" spans="1:1">
+      <c r="A104">
+        <v>1.533333333333333</v>
+      </c>
+    </row>
+    <row r="105" spans="1:1">
+      <c r="A105">
+        <v>0.4875</v>
+      </c>
+    </row>
+    <row r="106" spans="1:1">
+      <c r="A106">
+        <v>2.1186440677966</v>
+      </c>
+    </row>
+    <row r="107" spans="1:1">
+      <c r="A107">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="108" spans="1:1">
+      <c r="A108">
+        <v>1.955</v>
+      </c>
+    </row>
+    <row r="109" spans="1:1">
+      <c r="A109">
+        <v>1.68</v>
+      </c>
+    </row>
+    <row r="110" spans="1:1">
+      <c r="A110">
+        <v>0.4829782608695652</v>
+      </c>
+    </row>
+    <row r="111" spans="1:1">
+      <c r="A111">
+        <v>0.5860217391304348</v>
+      </c>
+    </row>
+    <row r="112" spans="1:1">
+      <c r="A112">
+        <v>0.3916326530612245</v>
+      </c>
+    </row>
+    <row r="113" spans="1:1">
+      <c r="A113">
+        <v>0.6111111111111112</v>
+      </c>
+    </row>
+    <row r="114" spans="1:1">
+      <c r="A114">
+        <v>0.9230769230769231</v>
+      </c>
+    </row>
+    <row r="115" spans="1:1">
+      <c r="A115">
+        <v>1.164315151769025</v>
+      </c>
+    </row>
+    <row r="116" spans="1:1">
+      <c r="A116">
+        <v>1.309333333333333</v>
+      </c>
+    </row>
+    <row r="117" spans="1:1">
+      <c r="A117">
+        <v>1.06</v>
+      </c>
+    </row>
+    <row r="118" spans="1:1">
+      <c r="A118">
+        <v>1.206666666666667</v>
+      </c>
+    </row>
+    <row r="119" spans="1:1">
+      <c r="A119">
+        <v>1.2125</v>
+      </c>
+    </row>
+    <row r="120" spans="1:1">
+      <c r="A120">
+        <v>1.0375</v>
+      </c>
+    </row>
+    <row r="121" spans="1:1">
+      <c r="A121">
+        <v>1.129625</v>
+      </c>
+    </row>
+    <row r="122" spans="1:1">
+      <c r="A122">
+        <v>1.155294117647059</v>
+      </c>
+    </row>
+    <row r="123" spans="1:1">
+      <c r="A123">
+        <v>1.333333333333333</v>
+      </c>
+    </row>
+    <row r="124" spans="1:1">
+      <c r="A124">
+        <v>2.333333333333333</v>
+      </c>
+    </row>
+    <row r="125" spans="1:1">
+      <c r="A125">
+        <v>1.205</v>
+      </c>
+    </row>
+    <row r="126" spans="1:1">
+      <c r="A126">
+        <v>1.2136875</v>
+      </c>
+    </row>
+    <row r="127" spans="1:1">
+      <c r="A127">
+        <v>1.2115625</v>
+      </c>
+    </row>
+    <row r="128" spans="1:1">
+      <c r="A128">
+        <v>1.139176470588235</v>
+      </c>
+    </row>
+    <row r="129" spans="1:1">
+      <c r="A129">
+        <v>1.042388888888889</v>
+      </c>
+    </row>
+    <row r="130" spans="1:1">
+      <c r="A130">
+        <v>1.044444444444445</v>
+      </c>
+    </row>
+    <row r="131" spans="1:1">
+      <c r="A131">
+        <v>1.754385964912281</v>
+      </c>
+    </row>
+    <row r="132" spans="1:1">
+      <c r="A132">
+        <v>1.087547798740395</v>
+      </c>
+    </row>
+    <row r="133" spans="1:1">
+      <c r="A133">
+        <v>0.9948992481203011</v>
+      </c>
+    </row>
+    <row r="134" spans="1:1">
+      <c r="A134">
+        <v>0.9705679943988564</v>
+      </c>
+    </row>
+    <row r="135" spans="1:1">
+      <c r="A135">
+        <v>0.9567543859649122</v>
+      </c>
+    </row>
+    <row r="136" spans="1:1">
+      <c r="A136">
+        <v>1.017125</v>
+      </c>
+    </row>
+    <row r="137" spans="1:1">
+      <c r="A137">
+        <v>1.048</v>
+      </c>
+    </row>
+    <row r="138" spans="1:1">
+      <c r="A138">
+        <v>1.215789473684211</v>
+      </c>
+    </row>
+    <row r="139" spans="1:1">
+      <c r="A139">
+        <v>0.9956504338545761</v>
+      </c>
+    </row>
+    <row r="140" spans="1:1">
+      <c r="A140">
+        <v>1.028890170900142</v>
+      </c>
+    </row>
+    <row r="141" spans="1:1">
+      <c r="A141">
+        <v>1.022513368983957</v>
+      </c>
+    </row>
+    <row r="142" spans="1:1">
+      <c r="A142">
+        <v>1.138493150684931</v>
+      </c>
+    </row>
+    <row r="143" spans="1:1">
+      <c r="A143">
+        <v>1.023875</v>
+      </c>
+    </row>
+    <row r="144" spans="1:1">
+      <c r="A144">
+        <v>1.098765432098765</v>
+      </c>
+    </row>
+    <row r="145" spans="1:1">
+      <c r="A145">
+        <v>1.7424</v>
+      </c>
+    </row>
+    <row r="146" spans="1:1">
+      <c r="A146">
+        <v>1.27</v>
+      </c>
+    </row>
+    <row r="147" spans="1:1">
+      <c r="A147">
+        <v>1.389932381667919</v>
+      </c>
+    </row>
+    <row r="148" spans="1:1">
+      <c r="A148">
+        <v>1.052631578947368</v>
+      </c>
+    </row>
+    <row r="149" spans="1:1">
+      <c r="A149">
+        <v>1.032036082474227</v>
+      </c>
+    </row>
+    <row r="150" spans="1:1">
+      <c r="A150">
+        <v>1.030927835051546</v>
+      </c>
+    </row>
+    <row r="151" spans="1:1">
+      <c r="A151">
+        <v>0.9228245614035104</v>
+      </c>
+    </row>
+    <row r="152" spans="1:1">
+      <c r="A152">
+        <v>1.321428571428571</v>
+      </c>
+    </row>
+    <row r="153" spans="1:1">
+      <c r="A153">
+        <v>1.1561875</v>
+      </c>
+    </row>
+    <row r="154" spans="1:1">
+      <c r="A154">
+        <v>1.115121951219512</v>
+      </c>
+    </row>
+    <row r="155" spans="1:1">
+      <c r="A155">
+        <v>1.285714285714286</v>
+      </c>
+    </row>
+    <row r="156" spans="1:1">
+      <c r="A156">
+        <v>1.0925</v>
+      </c>
+    </row>
+    <row r="157" spans="1:1">
+      <c r="A157">
+        <v>1.044252873563218</v>
+      </c>
+    </row>
+    <row r="158" spans="1:1">
+      <c r="A158">
+        <v>0.9803030303030303</v>
+      </c>
+    </row>
+    <row r="159" spans="1:1">
+      <c r="A159">
+        <v>1.179039301310044</v>
+      </c>
+    </row>
+    <row r="160" spans="1:1">
+      <c r="A160">
+        <v>1.076929246123686</v>
+      </c>
+    </row>
+    <row r="161" spans="1:1">
+      <c r="A161">
+        <v>1.088077934787474</v>
+      </c>
+    </row>
+    <row r="162" spans="1:1">
+      <c r="A162">
+        <v>1.082526315789474</v>
+      </c>
+    </row>
+    <row r="163" spans="1:1">
+      <c r="A163">
+        <v>1.171894736842105</v>
+      </c>
+    </row>
+    <row r="164" spans="1:1">
+      <c r="A164">
+        <v>0.2215527733259426</v>
+      </c>
+    </row>
+    <row r="165" spans="1:1">
+      <c r="A165">
+        <v>1.709157894736842</v>
+      </c>
+    </row>
+    <row r="166" spans="1:1">
+      <c r="A166">
+        <v>1.521368421052631</v>
+      </c>
+    </row>
+    <row r="167" spans="1:1">
+      <c r="A167">
+        <v>1.602526315789474</v>
+      </c>
+    </row>
+    <row r="168" spans="1:1">
+      <c r="A168">
+        <v>4.489578947368421</v>
+      </c>
+    </row>
+    <row r="169" spans="1:1">
+      <c r="A169">
+        <v>1.944421052631579</v>
+      </c>
+    </row>
+    <row r="170" spans="1:1">
+      <c r="A170">
+        <v>1.295263157894737</v>
+      </c>
+    </row>
+    <row r="171" spans="1:1">
+      <c r="A171">
+        <v>4.606790289121734</v>
+      </c>
+    </row>
+    <row r="172" spans="1:1">
+      <c r="A172">
+        <v>1.37</v>
+      </c>
+    </row>
+    <row r="173" spans="1:1">
+      <c r="A173">
+        <v>2.14</v>
+      </c>
+    </row>
+    <row r="174" spans="1:1">
+      <c r="A174">
+        <v>0.9652509652509653</v>
+      </c>
+    </row>
+    <row r="175" spans="1:1">
+      <c r="A175">
+        <v>0.9784735812133072</v>
+      </c>
+    </row>
+    <row r="176" spans="1:1">
+      <c r="A176">
+        <v>0.9039956608208281</v>
+      </c>
+    </row>
+    <row r="177" spans="1:1">
+      <c r="A177">
+        <v>0.001135073779795687</v>
+      </c>
+    </row>
+    <row r="178" spans="1:1">
+      <c r="A178">
+        <v>2.015393124822253</v>
+      </c>
+    </row>
+    <row r="179" spans="1:1">
+      <c r="A179">
+        <v>2.742822870632321</v>
+      </c>
+    </row>
+    <row r="180" spans="1:1">
+      <c r="A180">
+        <v>1.753614442924429</v>
+      </c>
+    </row>
+    <row r="181" spans="1:1">
+      <c r="A181">
+        <v>6.5832786490285</v>
+      </c>
+    </row>
+    <row r="182" spans="1:1">
+      <c r="A182">
+        <v>1.887620844696939</v>
+      </c>
+    </row>
+    <row r="183" spans="1:1">
+      <c r="A183">
+        <v>1.266261460462019</v>
+      </c>
+    </row>
+    <row r="184" spans="1:1">
+      <c r="A184">
+        <v>3.654458333333333</v>
+      </c>
+    </row>
+    <row r="185" spans="1:1">
+      <c r="A185">
+        <v>7.628518413137146</v>
+      </c>
+    </row>
+    <row r="186" spans="1:1">
+      <c r="A186">
+        <v>0.07499999999999929</v>
+      </c>
+    </row>
+    <row r="187" spans="1:1">
+      <c r="A187">
+        <v>1.049203896717607</v>
+      </c>
+    </row>
+    <row r="188" spans="1:1">
+      <c r="A188">
+        <v>8.315000000000001</v>
+      </c>
+    </row>
+    <row r="189" spans="1:1">
+      <c r="A189">
+        <v>11.9</v>
+      </c>
+    </row>
+    <row r="190" spans="1:1">
+      <c r="A190">
+        <v>0.3333</v>
+      </c>
+    </row>
+    <row r="191" spans="1:1">
+      <c r="A191">
+        <v>0.275</v>
+      </c>
+    </row>
+    <row r="192" spans="1:1">
+      <c r="A192">
+        <v>1.041666666666667</v>
+      </c>
+    </row>
+    <row r="193" spans="1:1">
+      <c r="A193">
+        <v>0.7638888888888888</v>
+      </c>
+    </row>
+    <row r="194" spans="1:1">
+      <c r="A194">
+        <v>0.9412</v>
+      </c>
+    </row>
+    <row r="195" spans="1:1">
+      <c r="A195">
+        <v>0.9167000000000001</v>
+      </c>
+    </row>
+    <row r="196" spans="1:1">
+      <c r="A196">
+        <v>0.7142857142857143</v>
+      </c>
+    </row>
+    <row r="197" spans="1:1">
+      <c r="A197">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="198" spans="1:1">
+      <c r="A198">
+        <v>20.41666666666667</v>
+      </c>
+    </row>
+    <row r="199" spans="1:1">
+      <c r="A199">
+        <v>20.5</v>
+      </c>
+    </row>
+    <row r="200" spans="1:1">
+      <c r="A200">
+        <v>19.41666666666667</v>
+      </c>
+    </row>
+    <row r="201" spans="1:1">
+      <c r="A201">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="202" spans="1:1">
+      <c r="A202">
+        <v>238.2449979782104</v>
+      </c>
+    </row>
+    <row r="203" spans="1:1">
+      <c r="A203">
+        <v>311.345</v>
+      </c>
+    </row>
+    <row r="204" spans="1:1">
+      <c r="A204">
+        <v>1765.555</v>
+      </c>
+    </row>
+    <row r="205" spans="1:1">
+      <c r="A205">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="206" spans="1:1">
+      <c r="A206">
+        <v>8.495912050318455E-05</v>
+      </c>
+    </row>
+    <row r="207" spans="1:1">
+      <c r="A207">
+        <v>1.001070326764465</v>
+      </c>
+    </row>
+    <row r="208" spans="1:1">
+      <c r="A208">
+        <v>35.3111</v>
+      </c>
+    </row>
+    <row r="209" spans="1:1">
+      <c r="A209">
+        <v>1.074944444444444</v>
+      </c>
+    </row>
+    <row r="210" spans="1:1">
+      <c r="A210">
+        <v>1.957428571428572</v>
+      </c>
+    </row>
+    <row r="211" spans="1:1">
+      <c r="A211">
+        <v>2.870571428571429</v>
+      </c>
+    </row>
+    <row r="212" spans="1:1">
+      <c r="A212">
+        <v>112.1267142857143</v>
+      </c>
+    </row>
+    <row r="213" spans="1:1">
+      <c r="A213">
+        <v>1.062777777777778</v>
+      </c>
+    </row>
+    <row r="214" spans="1:1">
+      <c r="A214">
+        <v>1.085833333333333</v>
+      </c>
+    </row>
+    <row r="215" spans="1:1">
+      <c r="A215">
+        <v>0.9253333333333333</v>
+      </c>
+    </row>
+    <row r="216" spans="1:1">
+      <c r="A216">
+        <v>1.612653791509528</v>
+      </c>
+    </row>
+    <row r="217" spans="1:1">
+      <c r="A217">
+        <v>1.645641134450872</v>
+      </c>
+    </row>
+    <row r="218" spans="1:1">
+      <c r="A218">
+        <v>1.11575</v>
+      </c>
+    </row>
+    <row r="219" spans="1:1">
+      <c r="A219">
+        <v>1.6964375</v>
+      </c>
+    </row>
+    <row r="220" spans="1:1">
+      <c r="A220">
+        <v>1.075465277777778</v>
+      </c>
+    </row>
+    <row r="221" spans="1:1">
+      <c r="A221">
+        <v>2.6443125</v>
+      </c>
+    </row>
+    <row r="222" spans="1:1">
+      <c r="A222">
+        <v>0.8165289256198299</v>
+      </c>
+    </row>
+    <row r="223" spans="1:1">
+      <c r="A223">
+        <v>0.92012779552716</v>
+      </c>
+    </row>
+    <row r="224" spans="1:1">
+      <c r="A224">
+        <v>0.9724542838577928</v>
+      </c>
+    </row>
+    <row r="225" spans="1:1">
+      <c r="A225">
+        <v>0.8847944514062934</v>
+      </c>
+    </row>
+    <row r="226" spans="1:1">
+      <c r="A226">
+        <v>0.9392592592592593</v>
+      </c>
+    </row>
+    <row r="227" spans="1:1">
+      <c r="A227">
+        <v>0.65</v>
+      </c>
+    </row>
+    <row r="228" spans="1:1">
+      <c r="A228">
+        <v>0.9791666666666665</v>
+      </c>
+    </row>
+    <row r="229" spans="1:1">
+      <c r="A229">
+        <v>1.156866161616162</v>
+      </c>
+    </row>
+    <row r="230" spans="1:1">
+      <c r="A230">
+        <v>1.111740111740112</v>
+      </c>
+    </row>
+    <row r="231" spans="1:1">
+      <c r="A231">
+        <v>1.241322916666667</v>
+      </c>
+    </row>
+    <row r="232" spans="1:1">
+      <c r="A232">
+        <v>1.19034375</v>
+      </c>
+    </row>
+    <row r="233" spans="1:1">
+      <c r="A233">
+        <v>1.067555555555556</v>
+      </c>
+    </row>
+    <row r="234" spans="1:1">
+      <c r="A234">
+        <v>1.923076923076923</v>
+      </c>
+    </row>
+    <row r="235" spans="1:1">
+      <c r="A235">
+        <v>1.128045977011494</v>
+      </c>
+    </row>
+    <row r="236" spans="1:1">
+      <c r="A236">
+        <v>1.0022</v>
+      </c>
+    </row>
+    <row r="237" spans="1:1">
+      <c r="A237">
+        <v>1.0012</v>
+      </c>
+    </row>
+    <row r="238" spans="1:1">
+      <c r="A238">
+        <v>0.7223529411764705</v>
+      </c>
+    </row>
+    <row r="239" spans="1:1">
+      <c r="A239">
+        <v>1.398518518518518</v>
+      </c>
+    </row>
+    <row r="240" spans="1:1">
+      <c r="A240">
+        <v>1.03</v>
+      </c>
+    </row>
+    <row r="241" spans="1:1">
+      <c r="A241">
+        <v>1.137647058823529</v>
+      </c>
+    </row>
+    <row r="242" spans="1:1">
+      <c r="A242">
+        <v>0.9622641509433965</v>
+      </c>
+    </row>
+    <row r="243" spans="1:1">
+      <c r="A243">
+        <v>1.616323529411765</v>
+      </c>
+    </row>
+    <row r="244" spans="1:1">
+      <c r="A244">
+        <v>1.36474622770919</v>
+      </c>
+    </row>
+    <row r="245" spans="1:1">
+      <c r="A245">
+        <v>1.0431</v>
+      </c>
+    </row>
+    <row r="246" spans="1:1">
+      <c r="A246">
+        <v>1.43884892086331</v>
+      </c>
+    </row>
+    <row r="247" spans="1:1">
+      <c r="A247">
+        <v>0.18</v>
+      </c>
+    </row>
+    <row r="248" spans="1:1">
+      <c r="A248">
+        <v>0.15</v>
+      </c>
+    </row>
+    <row r="249" spans="1:1">
+      <c r="A249">
+        <v>1.23529705882355</v>
+      </c>
+    </row>
+    <row r="250" spans="1:1">
+      <c r="A250">
+        <v>1.35295</v>
+      </c>
+    </row>
+    <row r="251" spans="1:1">
+      <c r="A251">
+        <v>0.9285714285714286</v>
+      </c>
+    </row>
+    <row r="252" spans="1:1">
+      <c r="A252">
+        <v>0.7</v>
+      </c>
+    </row>
+    <row r="253" spans="1:1">
+      <c r="A253">
+        <v>0.8714444444444445</v>
+      </c>
+    </row>
+    <row r="254" spans="1:1">
+      <c r="A254">
+        <v>1.03448275862069</v>
+      </c>
+    </row>
+    <row r="255" spans="1:1">
+      <c r="A255">
+        <v>1.105263157894737</v>
+      </c>
+    </row>
+    <row r="256" spans="1:1">
+      <c r="A256">
+        <v>1.235294117647059</v>
+      </c>
+    </row>
+    <row r="257" spans="1:1">
+      <c r="A257">
+        <v>1.456310679611651</v>
+      </c>
+    </row>
+    <row r="258" spans="1:1">
+      <c r="A258">
+        <v>1.363636363636364</v>
+      </c>
+    </row>
+    <row r="259" spans="1:1">
+      <c r="A259">
+        <v>1.428571428571429</v>
+      </c>
+    </row>
+    <row r="260" spans="1:1">
+      <c r="A260">
+        <v>1.8001800180018</v>
+      </c>
+    </row>
+    <row r="261" spans="1:1">
+      <c r="A261">
+        <v>0.8856499999999999</v>
+      </c>
+    </row>
+    <row r="262" spans="1:1">
+      <c r="A262">
+        <v>0.9687894736842105</v>
+      </c>
+    </row>
+    <row r="263" spans="1:1">
+      <c r="A263">
+        <v>0.9840896763821895</v>
+      </c>
+    </row>
+    <row r="264" spans="1:1">
+      <c r="A264">
+        <v>0.9313157894736841</v>
+      </c>
+    </row>
+    <row r="265" spans="1:1">
+      <c r="A265">
+        <v>0.8047368421052632</v>
+      </c>
+    </row>
+    <row r="266" spans="1:1">
+      <c r="A266">
+        <v>0.6217368421052631</v>
+      </c>
+    </row>
+    <row r="267" spans="1:1">
+      <c r="A267">
+        <v>1.276978417266187</v>
+      </c>
+    </row>
+    <row r="268" spans="1:1">
+      <c r="A268">
+        <v>1.28</v>
+      </c>
+    </row>
+    <row r="269" spans="1:1">
+      <c r="A269">
+        <v>1.65</v>
+      </c>
+    </row>
+    <row r="270" spans="1:1">
+      <c r="A270">
+        <v>3.83</v>
+      </c>
+    </row>
+    <row r="271" spans="1:1">
+      <c r="A271">
+        <v>4.57</v>
+      </c>
+    </row>
+    <row r="272" spans="1:1">
+      <c r="A272">
+        <v>4.3</v>
+      </c>
+    </row>
+    <row r="273" spans="1:1">
+      <c r="A273">
+        <v>16.17233646643447</v>
+      </c>
+    </row>
+    <row r="274" spans="1:1">
+      <c r="A274">
+        <v>16.86</v>
+      </c>
+    </row>
+    <row r="275" spans="1:1">
+      <c r="A275">
+        <v>19.93</v>
+      </c>
+    </row>
+    <row r="276" spans="1:1">
+      <c r="A276">
+        <v>0.976802605821255</v>
+      </c>
+    </row>
+    <row r="277" spans="1:1">
+      <c r="A277">
+        <v>1.019740259234822</v>
+      </c>
+    </row>
+    <row r="278" spans="1:1">
+      <c r="A278">
+        <v>1.03915</v>
+      </c>
+    </row>
+    <row r="279" spans="1:1">
+      <c r="A279">
+        <v>1.0572</v>
+      </c>
+    </row>
+    <row r="280" spans="1:1">
+      <c r="A280">
+        <v>1.3333125</v>
+      </c>
+    </row>
+    <row r="281" spans="1:1">
+      <c r="A281">
+        <v>1.1354375</v>
+      </c>
+    </row>
+    <row r="282" spans="1:1">
+      <c r="A282">
+        <v>1.110941176470588</v>
+      </c>
+    </row>
+    <row r="283" spans="1:1">
+      <c r="A283">
+        <v>1.005917159763314</v>
+      </c>
+    </row>
+    <row r="284" spans="1:1">
+      <c r="A284">
+        <v>0.9071117561683598</v>
+      </c>
+    </row>
+    <row r="285" spans="1:1">
+      <c r="A285">
+        <v>0.9781427363844946</v>
+      </c>
+    </row>
+    <row r="286" spans="1:1">
+      <c r="A286">
+        <v>0.9578997161778618</v>
+      </c>
+    </row>
+    <row r="287" spans="1:1">
+      <c r="A287">
+        <v>1.159776231409469</v>
+      </c>
+    </row>
+    <row r="288" spans="1:1">
+      <c r="A288">
+        <v>1.024705221785514</v>
+      </c>
+    </row>
+    <row r="289" spans="1:1">
+      <c r="A289">
+        <v>1.038011695906433</v>
+      </c>
+    </row>
+    <row r="290" spans="1:1">
+      <c r="A290">
+        <v>1.022196261682243</v>
+      </c>
+    </row>
+    <row r="291" spans="1:1">
+      <c r="A291">
+        <v>1.012291666666667</v>
+      </c>
+    </row>
+    <row r="292" spans="1:1">
+      <c r="A292">
+        <v>0.999278350515464</v>
+      </c>
+    </row>
+    <row r="293" spans="1:1">
+      <c r="A293">
+        <v>1.005</v>
+      </c>
+    </row>
+    <row r="294" spans="1:1">
+      <c r="A294">
+        <v>1.006836734693878</v>
+      </c>
+    </row>
+    <row r="295" spans="1:1">
+      <c r="A295">
+        <v>1.011111111111111</v>
+      </c>
+    </row>
+    <row r="296" spans="1:1">
+      <c r="A296">
+        <v>1.031111111111111</v>
+      </c>
+    </row>
+    <row r="297" spans="1:1">
+      <c r="A297">
+        <v>1.015217391304348</v>
+      </c>
+    </row>
+    <row r="298" spans="1:1">
+      <c r="A298">
+        <v>0.9935622317596566</v>
+      </c>
+    </row>
+    <row r="299" spans="1:1">
+      <c r="A299">
+        <v>1.323529411764706</v>
+      </c>
+    </row>
+    <row r="300" spans="1:1">
+      <c r="A300">
+        <v>0.3058823529411765</v>
+      </c>
+    </row>
+    <row r="301" spans="1:1">
+      <c r="A301">
+        <v>0.9210526315789473</v>
+      </c>
+    </row>
+    <row r="302" spans="1:1">
+      <c r="A302">
+        <v>0.9928888888888889</v>
+      </c>
+    </row>
+    <row r="303" spans="1:1">
+      <c r="A303">
+        <v>0.9876666666666667</v>
+      </c>
+    </row>
+    <row r="304" spans="1:1">
+      <c r="A304">
+        <v>6.441612246331</v>
+      </c>
+    </row>
+    <row r="305" spans="1:1">
+      <c r="A305">
+        <v>6.262961235299454</v>
+      </c>
+    </row>
+    <row r="306" spans="1:1">
+      <c r="A306">
+        <v>1.3125</v>
+      </c>
+    </row>
+    <row r="307" spans="1:1">
+      <c r="A307">
+        <v>12.02424752093617</v>
+      </c>
+    </row>
+    <row r="308" spans="1:1">
+      <c r="A308">
+        <v>5.296115753636645</v>
+      </c>
+    </row>
+    <row r="309" spans="1:1">
+      <c r="A309">
+        <v>2.801875000000001</v>
+      </c>
+    </row>
+    <row r="310" spans="1:1">
+      <c r="A310">
+        <v>0.4375</v>
+      </c>
+    </row>
+    <row r="311" spans="1:1">
+      <c r="A311">
+        <v>0.873</v>
+      </c>
+    </row>
+    <row r="312" spans="1:1">
+      <c r="A312">
+        <v>0.8545</v>
+      </c>
+    </row>
+    <row r="313" spans="1:1">
+      <c r="A313">
+        <v>21.50537634408602</v>
+      </c>
+    </row>
+    <row r="314" spans="1:1">
+      <c r="A314">
+        <v>0.7765151515151526</v>
+      </c>
+    </row>
+    <row r="315" spans="1:1">
+      <c r="A315">
+        <v>1.02974828375286</v>
+      </c>
+    </row>
+    <row r="316" spans="1:1">
+      <c r="A316">
+        <v>1.001684210526316</v>
+      </c>
+    </row>
+    <row r="317" spans="1:1">
+      <c r="A317">
+        <v>1.830950000000001</v>
+      </c>
+    </row>
+    <row r="318" spans="1:1">
+      <c r="A318">
+        <v>0.9184</v>
+      </c>
+    </row>
+    <row r="319" spans="1:1">
+      <c r="A319">
+        <v>1.0728</v>
+      </c>
+    </row>
+    <row r="320" spans="1:1">
+      <c r="A320">
+        <v>1.0994</v>
+      </c>
+    </row>
+    <row r="321" spans="1:1">
+      <c r="A321">
+        <v>1.565</v>
+      </c>
+    </row>
+    <row r="322" spans="1:1">
+      <c r="A322">
+        <v>1.755</v>
+      </c>
+    </row>
+    <row r="323" spans="1:1">
+      <c r="A323">
+        <v>1.073733333333333</v>
+      </c>
+    </row>
+    <row r="324" spans="1:1">
+      <c r="A324">
+        <v>2.326086956521739</v>
+      </c>
+    </row>
+    <row r="325" spans="1:1">
+      <c r="A325">
+        <v>4.1333</v>
+      </c>
+    </row>
+    <row r="326" spans="1:1">
+      <c r="A326">
+        <v>2.53125</v>
+      </c>
+    </row>
+    <row r="327" spans="1:1">
+      <c r="A327">
+        <v>1.609375</v>
+      </c>
+    </row>
+    <row r="328" spans="1:1">
+      <c r="A328">
+        <v>1.5467</v>
+      </c>
+    </row>
+    <row r="329" spans="1:1">
+      <c r="A329">
+        <v>1.976190476190476</v>
+      </c>
+    </row>
+    <row r="330" spans="1:1">
+      <c r="A330">
+        <v>0.7913</v>
+      </c>
+    </row>
+    <row r="331" spans="1:1">
+      <c r="A331">
+        <v>1.243445692883895</v>
+      </c>
+    </row>
+    <row r="332" spans="1:1">
+      <c r="A332">
+        <v>0.6776000000000001</v>
+      </c>
+    </row>
+    <row r="333" spans="1:1">
+      <c r="A333">
+        <v>1.099547511312217</v>
+      </c>
+    </row>
+    <row r="334" spans="1:1">
+      <c r="A334">
+        <v>0.8928571428571429</v>
+      </c>
+    </row>
+    <row r="335" spans="1:1">
+      <c r="A335">
+        <v>1.260869565217391</v>
+      </c>
+    </row>
+    <row r="336" spans="1:1">
+      <c r="A336">
+        <v>1.45</v>
+      </c>
+    </row>
+    <row r="337" spans="1:1">
+      <c r="A337">
+        <v>1.4</v>
+      </c>
+    </row>
+    <row r="338" spans="1:1">
+      <c r="A338">
+        <v>1.047619047619048</v>
+      </c>
+    </row>
+    <row r="339" spans="1:1">
+      <c r="A339">
+        <v>1.136363636363636</v>
+      </c>
+    </row>
+    <row r="340" spans="1:1">
+      <c r="A340">
+        <v>1.1285</v>
+      </c>
+    </row>
+    <row r="341" spans="1:1">
+      <c r="A341">
+        <v>1.013647058823529</v>
+      </c>
+    </row>
+    <row r="342" spans="1:1">
+      <c r="A342">
+        <v>0.7073170731707317</v>
+      </c>
+    </row>
+    <row r="343" spans="1:1">
+      <c r="A343">
+        <v>1.15</v>
+      </c>
+    </row>
+    <row r="344" spans="1:1">
+      <c r="A344">
+        <v>1.297222222222222</v>
+      </c>
+    </row>
+    <row r="345" spans="1:1">
+      <c r="A345">
+        <v>5.0217</v>
+      </c>
+    </row>
+    <row r="346" spans="1:1">
+      <c r="A346">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="347" spans="1:1">
+      <c r="A347">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="348" spans="1:1">
+      <c r="A348">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="349" spans="1:1">
+      <c r="A349">
+        <v>1.29375</v>
+      </c>
+    </row>
+    <row r="350" spans="1:1">
+      <c r="A350">
+        <v>1.57</v>
+      </c>
+    </row>
+    <row r="351" spans="1:1">
+      <c r="A351">
+        <v>1.105</v>
+      </c>
+    </row>
+    <row r="352" spans="1:1">
+      <c r="A352">
+        <v>1.0663</v>
+      </c>
+    </row>
+    <row r="353" spans="1:1">
+      <c r="A353">
+        <v>1.254355400696864</v>
+      </c>
+    </row>
+    <row r="354" spans="1:1">
+      <c r="A354">
+        <v>1.434782608695652</v>
+      </c>
+    </row>
+    <row r="355" spans="1:1">
+      <c r="A355">
+        <v>1.325842696629213</v>
+      </c>
+    </row>
+    <row r="356" spans="1:1">
+      <c r="A356">
+        <v>1.326530612244898</v>
+      </c>
+    </row>
+    <row r="357" spans="1:1">
+      <c r="A357">
+        <v>1.004431818181818</v>
+      </c>
+    </row>
+    <row r="358" spans="1:1">
+      <c r="A358">
+        <v>1.009545454545455</v>
+      </c>
+    </row>
+    <row r="359" spans="1:1">
+      <c r="A359">
+        <v>1.012359550561798</v>
+      </c>
+    </row>
+    <row r="360" spans="1:1">
+      <c r="A360">
+        <v>1.173125</v>
+      </c>
+    </row>
+    <row r="361" spans="1:1">
+      <c r="A361">
+        <v>0.9871951219512195</v>
+      </c>
+    </row>
+    <row r="362" spans="1:1">
+      <c r="A362">
+        <v>1.147975</v>
+      </c>
+    </row>
+    <row r="363" spans="1:1">
+      <c r="A363">
+        <v>2.531645569620253</v>
+      </c>
+    </row>
+    <row r="364" spans="1:1">
+      <c r="A364">
+        <v>5.555555555555555</v>
+      </c>
+    </row>
+    <row r="365" spans="1:1">
+      <c r="A365">
+        <v>0.9523809523809523</v>
+      </c>
+    </row>
+    <row r="366" spans="1:1">
+      <c r="A366">
+        <v>1.01</v>
+      </c>
+    </row>
+    <row r="367" spans="1:1">
+      <c r="A367">
+        <v>1.176333333333333</v>
+      </c>
+    </row>
+    <row r="368" spans="1:1">
+      <c r="A368">
+        <v>1.27219833333335</v>
+      </c>
+    </row>
+    <row r="369" spans="1:1">
+      <c r="A369">
+        <v>1.1372</v>
+      </c>
+    </row>
+    <row r="370" spans="1:1">
+      <c r="A370">
+        <v>1.0245</v>
+      </c>
+    </row>
+    <row r="371" spans="1:1">
+      <c r="A371">
+        <v>0.5041</v>
+      </c>
+    </row>
+    <row r="372" spans="1:1">
+      <c r="A372">
+        <v>1.086135338345867</v>
+      </c>
+    </row>
+    <row r="373" spans="1:1">
+      <c r="A373">
+        <v>1.056612903225806</v>
+      </c>
+    </row>
+    <row r="374" spans="1:1">
+      <c r="A374">
+        <v>1.072204301075269</v>
+      </c>
+    </row>
+    <row r="375" spans="1:1">
+      <c r="A375">
+        <v>1.080941176470588</v>
+      </c>
+    </row>
+    <row r="376" spans="1:1">
+      <c r="A376">
+        <v>1.144470588235294</v>
+      </c>
+    </row>
+    <row r="377" spans="1:1">
+      <c r="A377">
+        <v>6.666666666666667</v>
+      </c>
+    </row>
+    <row r="378" spans="1:1">
+      <c r="A378">
+        <v>2.222222222222222</v>
+      </c>
+    </row>
+    <row r="379" spans="1:1">
+      <c r="A379">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="380" spans="1:1">
+      <c r="A380">
+        <v>1.009180280706798</v>
+      </c>
+    </row>
+    <row r="381" spans="1:1">
+      <c r="A381">
+        <v>1.009722222222222</v>
+      </c>
+    </row>
+    <row r="382" spans="1:1">
+      <c r="A382">
+        <v>1.01010101010101</v>
+      </c>
+    </row>
+    <row r="383" spans="1:1">
+      <c r="A383">
+        <v>1.153846153846154</v>
+      </c>
+    </row>
+    <row r="384" spans="1:1">
+      <c r="A384">
+        <v>3.177</v>
+      </c>
+    </row>
+    <row r="385" spans="1:1">
+      <c r="A385">
+        <v>1.64916004403234</v>
+      </c>
+    </row>
+    <row r="386" spans="1:1">
+      <c r="A386">
+        <v>0.9941176470588236</v>
+      </c>
+    </row>
+    <row r="387" spans="1:1">
+      <c r="A387">
+        <v>1.114285714285714</v>
+      </c>
+    </row>
+    <row r="388" spans="1:1">
+      <c r="A388">
+        <v>1.083482689692428</v>
+      </c>
+    </row>
+    <row r="389" spans="1:1">
+      <c r="A389">
+        <v>1.003092869681518</v>
+      </c>
+    </row>
+    <row r="390" spans="1:1">
+      <c r="A390">
+        <v>1.053463260468791</v>
+      </c>
+    </row>
+    <row r="391" spans="1:1">
+      <c r="A391">
+        <v>4.45</v>
+      </c>
+    </row>
+    <row r="392" spans="1:1">
+      <c r="A392">
+        <v>0.51</v>
+      </c>
+    </row>
+    <row r="393" spans="1:1">
+      <c r="A393">
+        <v>0.44</v>
+      </c>
+    </row>
+    <row r="394" spans="1:1">
+      <c r="A394">
+        <v>1.045888138405023</v>
+      </c>
+    </row>
+    <row r="395" spans="1:1">
+      <c r="A395">
+        <v>1.137873563218391</v>
+      </c>
+    </row>
+    <row r="396" spans="1:1">
+      <c r="A396">
+        <v>1.057647058823529</v>
+      </c>
+    </row>
+    <row r="397" spans="1:1">
+      <c r="A397">
+        <v>1.082352941176471</v>
+      </c>
+    </row>
+    <row r="398" spans="1:1">
+      <c r="A398">
+        <v>1.013333333333333</v>
+      </c>
+    </row>
+    <row r="399" spans="1:1">
+      <c r="A399">
+        <v>1.039130434782609</v>
+      </c>
+    </row>
+    <row r="400" spans="1:1">
+      <c r="A400">
+        <v>0.99156641448592</v>
+      </c>
+    </row>
+    <row r="401" spans="1:1">
+      <c r="A401">
+        <v>1.015685321634592</v>
+      </c>
+    </row>
+    <row r="402" spans="1:1">
+      <c r="A402">
+        <v>1.016989795918367</v>
+      </c>
+    </row>
+    <row r="403" spans="1:1">
+      <c r="A403">
+        <v>1.1541</v>
+      </c>
+    </row>
+    <row r="404" spans="1:1">
+      <c r="A404">
+        <v>0.86</v>
+      </c>
+    </row>
+    <row r="405" spans="1:1">
+      <c r="A405">
+        <v>1.249951341040912</v>
+      </c>
+    </row>
+    <row r="406" spans="1:1">
+      <c r="A406">
+        <v>0.992</v>
+      </c>
+    </row>
+    <row r="407" spans="1:1">
+      <c r="A407">
+        <v>0.764</v>
+      </c>
+    </row>
+    <row r="408" spans="1:1">
+      <c r="A408">
+        <v>1.05</v>
+      </c>
+    </row>
+    <row r="409" spans="1:1">
+      <c r="A409">
+        <v>1.047222222222222</v>
+      </c>
+    </row>
+    <row r="410" spans="1:1">
+      <c r="A410">
+        <v>1.021505376344086</v>
+      </c>
+    </row>
+    <row r="411" spans="1:1">
+      <c r="A411">
+        <v>1.032258064516129</v>
+      </c>
+    </row>
+    <row r="412" spans="1:1">
+      <c r="A412">
+        <v>0.73775</v>
+      </c>
+    </row>
+    <row r="413" spans="1:1">
+      <c r="A413">
+        <v>0.98575</v>
+      </c>
+    </row>
+    <row r="414" spans="1:1">
+      <c r="A414">
+        <v>0.8933</v>
+      </c>
+    </row>
+    <row r="415" spans="1:1">
+      <c r="A415">
+        <v>1.6528637121818</v>
+      </c>
+    </row>
+    <row r="416" spans="1:1">
+      <c r="A416">
+        <v>1.23355</v>
+      </c>
+    </row>
+    <row r="417" spans="1:1">
+      <c r="A417">
+        <v>0.7855500000000001</v>
+      </c>
+    </row>
+    <row r="418" spans="1:1">
+      <c r="A418">
+        <v>0.70365</v>
+      </c>
+    </row>
+    <row r="419" spans="1:1">
+      <c r="A419">
+        <v>1.097701149425287</v>
+      </c>
+    </row>
+    <row r="420" spans="1:1">
+      <c r="A420">
+        <v>1.054597701149425</v>
+      </c>
+    </row>
+    <row r="421" spans="1:1">
+      <c r="A421">
+        <v>1.061111111111111</v>
+      </c>
+    </row>
+    <row r="422" spans="1:1">
+      <c r="A422">
+        <v>1.064516129032258</v>
+      </c>
+    </row>
+    <row r="423" spans="1:1">
+      <c r="A423">
+        <v>0.739616666666675</v>
+      </c>
+    </row>
+    <row r="424" spans="1:1">
+      <c r="A424">
+        <v>0.9852500000000001</v>
+      </c>
+    </row>
+    <row r="425" spans="1:1">
+      <c r="A425">
+        <v>1.01215</v>
+      </c>
+    </row>
+    <row r="426" spans="1:1">
+      <c r="A426">
+        <v>1.065894736842105</v>
+      </c>
+    </row>
+    <row r="427" spans="1:1">
+      <c r="A427">
+        <v>1.148421052631579</v>
+      </c>
+    </row>
+    <row r="428" spans="1:1">
+      <c r="A428">
+        <v>1.236947368421053</v>
+      </c>
+    </row>
+    <row r="429" spans="1:1">
+      <c r="A429">
+        <v>0.6077</v>
+      </c>
+    </row>
+    <row r="430" spans="1:1">
+      <c r="A430">
+        <v>1.2501</v>
+      </c>
+    </row>
+    <row r="431" spans="1:1">
+      <c r="A431">
+        <v>1.0711</v>
+      </c>
+    </row>
+    <row r="432" spans="1:1">
+      <c r="A432">
+        <v>1.038913043478261</v>
+      </c>
+    </row>
+    <row r="433" spans="1:1">
+      <c r="A433">
+        <v>1.0568938582028</v>
+      </c>
+    </row>
+    <row r="434" spans="1:1">
+      <c r="A434">
+        <v>0.97615</v>
+      </c>
+    </row>
+    <row r="435" spans="1:1">
+      <c r="A435">
+        <v>1.0326</v>
+      </c>
+    </row>
+    <row r="436" spans="1:1">
+      <c r="A436">
+        <v>0.5162</v>
+      </c>
+    </row>
+    <row r="437" spans="1:1">
+      <c r="A437">
+        <v>1.034636945020853</v>
+      </c>
+    </row>
+    <row r="438" spans="1:1">
+      <c r="A438">
+        <v>0.7892</v>
+      </c>
+    </row>
+    <row r="439" spans="1:1">
+      <c r="A439">
+        <v>1.08985854341735</v>
+      </c>
+    </row>
+    <row r="440" spans="1:1">
+      <c r="A440">
+        <v>0.9722499999999999</v>
+      </c>
+    </row>
+    <row r="441" spans="1:1">
+      <c r="A441">
+        <v>1.0594</v>
+      </c>
+    </row>
+    <row r="442" spans="1:1">
+      <c r="A442">
+        <v>0.4943</v>
+      </c>
+    </row>
+    <row r="443" spans="1:1">
+      <c r="A443">
+        <v>1.02130205659755</v>
+      </c>
+    </row>
+    <row r="444" spans="1:1">
+      <c r="A444">
+        <v>0.9591500000000001</v>
+      </c>
+    </row>
+    <row r="445" spans="1:1">
+      <c r="A445">
+        <v>0.9853000000000001</v>
+      </c>
+    </row>
+    <row r="446" spans="1:1">
+      <c r="A446">
+        <v>0.50905</v>
+      </c>
+    </row>
+    <row r="447" spans="1:1">
+      <c r="A447">
+        <v>1.29021164972635</v>
+      </c>
+    </row>
+    <row r="448" spans="1:1">
+      <c r="A448">
+        <v>1.10455</v>
+      </c>
+    </row>
+    <row r="449" spans="1:1">
+      <c r="A449">
+        <v>1.32415</v>
+      </c>
+    </row>
+    <row r="450" spans="1:1">
+      <c r="A450">
+        <v>0.56785</v>
+      </c>
+    </row>
+    <row r="451" spans="1:1">
+      <c r="A451">
+        <v>1.13572352941175</v>
+      </c>
+    </row>
+    <row r="452" spans="1:1">
+      <c r="A452">
+        <v>0.9505</v>
+      </c>
+    </row>
+    <row r="453" spans="1:1">
+      <c r="A453">
+        <v>1.0208</v>
+      </c>
+    </row>
+    <row r="454" spans="1:1">
+      <c r="A454">
+        <v>0.4671</v>
+      </c>
+    </row>
+    <row r="455" spans="1:1">
+      <c r="A455">
+        <v>1.2493</v>
+      </c>
+    </row>
+    <row r="456" spans="1:1">
+      <c r="A456">
+        <v>0.8856000000000001</v>
+      </c>
+    </row>
+    <row r="457" spans="1:1">
+      <c r="A457">
+        <v>1.0889</v>
+      </c>
+    </row>
+    <row r="458" spans="1:1">
+      <c r="A458">
+        <v>1.2060243283327</v>
+      </c>
+    </row>
+    <row r="459" spans="1:1">
+      <c r="A459">
+        <v>0.9431999999999999</v>
+      </c>
+    </row>
+    <row r="460" spans="1:1">
+      <c r="A460">
+        <v>1.1273</v>
+      </c>
+    </row>
+    <row r="461" spans="1:1">
+      <c r="A461">
+        <v>0.4966666666666666</v>
+      </c>
+    </row>
+    <row r="462" spans="1:1">
+      <c r="A462">
+        <v>0.99249166666667</v>
+      </c>
+    </row>
+    <row r="463" spans="1:1">
+      <c r="A463">
+        <v>0.9992</v>
+      </c>
+    </row>
+    <row r="464" spans="1:1">
+      <c r="A464">
+        <v>0.9978</v>
+      </c>
+    </row>
+    <row r="465" spans="1:1">
+      <c r="A465">
+        <v>1.075268817204301</v>
+      </c>
+    </row>
+    <row r="466" spans="1:1">
+      <c r="A466">
+        <v>1.4738</v>
+      </c>
+    </row>
+    <row r="467" spans="1:1">
+      <c r="A467">
+        <v>1.4521</v>
+      </c>
+    </row>
+    <row r="468" spans="1:1">
+      <c r="A468">
+        <v>1.008</v>
+      </c>
+    </row>
+    <row r="469" spans="1:1">
+      <c r="A469">
+        <v>0.970873786407767</v>
+      </c>
+    </row>
+    <row r="470" spans="1:1">
+      <c r="A470">
+        <v>1.153846153846154</v>
+      </c>
+    </row>
+    <row r="471" spans="1:1">
+      <c r="A471">
+        <v>3.12569285714285</v>
+      </c>
+    </row>
+    <row r="472" spans="1:1">
+      <c r="A472">
+        <v>1.553</v>
+      </c>
+    </row>
+    <row r="473" spans="1:1">
+      <c r="A473">
+        <v>1.383925</v>
+      </c>
+    </row>
+    <row r="474" spans="1:1">
+      <c r="A474">
+        <v>2.8039382352941</v>
+      </c>
+    </row>
+    <row r="475" spans="1:1">
+      <c r="A475">
+        <v>1.29445</v>
+      </c>
+    </row>
+    <row r="476" spans="1:1">
+      <c r="A476">
+        <v>2.04415</v>
+      </c>
+    </row>
+    <row r="477" spans="1:1">
+      <c r="A477">
+        <v>1.111125</v>
+      </c>
+    </row>
+    <row r="478" spans="1:1">
+      <c r="A478">
+        <v>1.10125</v>
+      </c>
+    </row>
+    <row r="479" spans="1:1">
+      <c r="A479">
+        <v>1.150196428571431</v>
+      </c>
+    </row>
+    <row r="480" spans="1:1">
+      <c r="A480">
+        <v>1.1435</v>
+      </c>
+    </row>
+    <row r="481" spans="1:1">
+      <c r="A481">
+        <v>1.063333333333333</v>
+      </c>
+    </row>
+    <row r="482" spans="1:1">
+      <c r="A482">
+        <v>1.022666666666667</v>
+      </c>
+    </row>
+    <row r="483" spans="1:1">
+      <c r="A483">
+        <v>2.456</v>
+      </c>
+    </row>
+    <row r="484" spans="1:1">
+      <c r="A484">
+        <v>2.2196</v>
+      </c>
+    </row>
+    <row r="485" spans="1:1">
+      <c r="A485">
+        <v>1.64105</v>
+      </c>
+    </row>
+    <row r="486" spans="1:1">
+      <c r="A486">
+        <v>1.18305</v>
+      </c>
+    </row>
+    <row r="487" spans="1:1">
+      <c r="A487">
+        <v>1.334</v>
+      </c>
+    </row>
+    <row r="488" spans="1:1">
+      <c r="A488">
+        <v>1.1136</v>
+      </c>
+    </row>
+    <row r="489" spans="1:1">
+      <c r="A489">
+        <v>1.0453</v>
+      </c>
+    </row>
+    <row r="490" spans="1:1">
+      <c r="A490">
+        <v>2.5143</v>
+      </c>
+    </row>
+    <row r="491" spans="1:1">
+      <c r="A491">
+        <v>3.3409</v>
+      </c>
+    </row>
+    <row r="492" spans="1:1">
+      <c r="A492">
+        <v>1.2507</v>
+      </c>
+    </row>
+    <row r="493" spans="1:1">
+      <c r="A493">
+        <v>1.180555555555556</v>
+      </c>
+    </row>
+    <row r="494" spans="1:1">
+      <c r="A494">
+        <v>1.586666666666667</v>
+      </c>
+    </row>
+    <row r="495" spans="1:1">
+      <c r="A495">
+        <v>11.76470588235294</v>
+      </c>
+    </row>
+    <row r="496" spans="1:1">
+      <c r="A496">
+        <v>1.661129568106313</v>
+      </c>
+    </row>
+    <row r="497" spans="1:1">
+      <c r="A497">
+        <v>1.24</v>
+      </c>
+    </row>
+    <row r="498" spans="1:1">
+      <c r="A498">
+        <v>0.98</v>
+      </c>
+    </row>
+    <row r="499" spans="1:1">
+      <c r="A499">
+        <v>1.273242841204909</v>
+      </c>
+    </row>
+    <row r="500" spans="1:1">
+      <c r="A500">
+        <v>1.026574917163008</v>
+      </c>
+    </row>
+    <row r="501" spans="1:1">
+      <c r="A501">
+        <v>0.9628</v>
+      </c>
+    </row>
+    <row r="502" spans="1:1">
+      <c r="A502">
+        <v>0.9878</v>
+      </c>
+    </row>
+    <row r="503" spans="1:1">
+      <c r="A503">
+        <v>0.9887</v>
+      </c>
+    </row>
+    <row r="504" spans="1:1">
+      <c r="A504">
+        <v>0.96</v>
+      </c>
+    </row>
+    <row r="505" spans="1:1">
+      <c r="A505">
+        <v>0.9836</v>
+      </c>
+    </row>
+    <row r="506" spans="1:1">
+      <c r="A506">
+        <v>0.993</v>
+      </c>
+    </row>
+    <row r="507" spans="1:1">
+      <c r="A507">
+        <v>0.9439</v>
+      </c>
+    </row>
+    <row r="508" spans="1:1">
+      <c r="A508">
+        <v>0.9883</v>
+      </c>
+    </row>
+    <row r="509" spans="1:1">
+      <c r="A509">
+        <v>0.9799</v>
+      </c>
+    </row>
+    <row r="510" spans="1:1">
+      <c r="A510">
+        <v>0.95802222222222</v>
+      </c>
+    </row>
+    <row r="511" spans="1:1">
+      <c r="A511">
+        <v>0.9778</v>
+      </c>
+    </row>
+    <row r="512" spans="1:1">
+      <c r="A512">
+        <v>0.9961</v>
+      </c>
+    </row>
+    <row r="513" spans="1:1">
+      <c r="A513">
+        <v>0.9356</v>
+      </c>
+    </row>
+    <row r="514" spans="1:1">
+      <c r="A514">
+        <v>0.9667</v>
+      </c>
+    </row>
+    <row r="515" spans="1:1">
+      <c r="A515">
+        <v>1.372277316268532</v>
+      </c>
+    </row>
+    <row r="516" spans="1:1">
+      <c r="A516">
+        <v>1.2144</v>
+      </c>
+    </row>
+    <row r="517" spans="1:1">
+      <c r="A517">
+        <v>1.051428571428571</v>
+      </c>
+    </row>
+    <row r="518" spans="1:1">
+      <c r="A518">
+        <v>0.9875156054931337</v>
+      </c>
+    </row>
+    <row r="519" spans="1:1">
+      <c r="A519">
+        <v>1.024739583333333</v>
+      </c>
+    </row>
+    <row r="520" spans="1:1">
+      <c r="A520">
+        <v>0.9404761904761905</v>
+      </c>
+    </row>
+    <row r="521" spans="1:1">
+      <c r="A521">
+        <v>1.481927710843373</v>
+      </c>
+    </row>
+    <row r="522" spans="1:1">
+      <c r="A522">
+        <v>1.227642276422764</v>
+      </c>
+    </row>
+    <row r="523" spans="1:1">
+      <c r="A523">
+        <v>0.06521739130434782</v>
+      </c>
+    </row>
+    <row r="524" spans="1:1">
+      <c r="A524">
+        <v>1.222222222222222</v>
+      </c>
+    </row>
+    <row r="525" spans="1:1">
+      <c r="A525">
+        <v>1.051818181818182</v>
+      </c>
+    </row>
+    <row r="526" spans="1:1">
+      <c r="A526">
+        <v>1.6469</v>
+      </c>
+    </row>
+    <row r="527" spans="1:1">
+      <c r="A527">
+        <v>0.9186875000000001</v>
+      </c>
+    </row>
+    <row r="528" spans="1:1">
+      <c r="A528">
+        <v>1.188118811881177</v>
+      </c>
+    </row>
+    <row r="529" spans="1:1">
+      <c r="A529">
+        <v>1.379310344827586</v>
+      </c>
+    </row>
+    <row r="530" spans="1:1">
+      <c r="A530">
+        <v>0.05521811154058531</v>
+      </c>
+    </row>
+    <row r="531" spans="1:1">
+      <c r="A531">
+        <v>0.05696382796923953</v>
+      </c>
+    </row>
+    <row r="532" spans="1:1">
+      <c r="A532">
+        <v>0.06060606060606061</v>
+      </c>
+    </row>
+    <row r="533" spans="1:1">
+      <c r="A533">
+        <v>1.433962264150943</v>
+      </c>
+    </row>
+    <row r="534" spans="1:1">
+      <c r="A534">
+        <v>1.142857142857143</v>
+      </c>
+    </row>
+    <row r="535" spans="1:1">
+      <c r="A535">
+        <v>1.36936936936937</v>
+      </c>
+    </row>
+    <row r="536" spans="1:1">
+      <c r="A536">
+        <v>1.067318562735053</v>
+      </c>
+    </row>
+    <row r="537" spans="1:1">
+      <c r="A537">
+        <v>1.083552547063557</v>
+      </c>
+    </row>
+    <row r="538" spans="1:1">
+      <c r="A538">
+        <v>1.176421052631579</v>
+      </c>
+    </row>
+    <row r="539" spans="1:1">
+      <c r="A539">
+        <v>1.104253086419756</v>
+      </c>
+    </row>
+    <row r="540" spans="1:1">
+      <c r="A540">
+        <v>0.8333333333333334</v>
+      </c>
+    </row>
+    <row r="541" spans="1:1">
+      <c r="A541">
+        <v>0.4761904761904762</v>
+      </c>
+    </row>
+    <row r="542" spans="1:1">
+      <c r="A542">
+        <v>0.5263157894736842</v>
+      </c>
+    </row>
+    <row r="543" spans="1:1">
+      <c r="A543">
+        <v>1.046148213048083</v>
+      </c>
+    </row>
+    <row r="544" spans="1:1">
+      <c r="A544">
+        <v>0.4422137218917903</v>
+      </c>
+    </row>
+    <row r="545" spans="1:1">
+      <c r="A545">
+        <v>0.3083421981715308</v>
+      </c>
+    </row>
+    <row r="546" spans="1:1">
+      <c r="A546">
+        <v>0.2521</v>
+      </c>
+    </row>
+    <row r="547" spans="1:1">
+      <c r="A547">
+        <v>1.897304622797772</v>
+      </c>
+    </row>
+    <row r="548" spans="1:1">
+      <c r="A548">
+        <v>1.265346087218498</v>
+      </c>
+    </row>
+    <row r="549" spans="1:1">
+      <c r="A549">
+        <v>1.380670611439842</v>
+      </c>
+    </row>
+    <row r="550" spans="1:1">
+      <c r="A550">
+        <v>1.19632557145909</v>
+      </c>
+    </row>
+    <row r="551" spans="1:1">
+      <c r="A551">
+        <v>0.9974088014033367</v>
+      </c>
+    </row>
+    <row r="552" spans="1:1">
+      <c r="A552">
+        <v>1.01515306122449</v>
+      </c>
+    </row>
+    <row r="553" spans="1:1">
+      <c r="A553">
+        <v>1.017908163265306</v>
+      </c>
+    </row>
+    <row r="554" spans="1:1">
+      <c r="A554">
+        <v>1.110221510541767</v>
+      </c>
+    </row>
+    <row r="555" spans="1:1">
+      <c r="A555">
+        <v>2.09</v>
+      </c>
+    </row>
+    <row r="556" spans="1:1">
+      <c r="A556">
+        <v>1.818181818181818</v>
+      </c>
+    </row>
+    <row r="557" spans="1:1">
+      <c r="A557">
+        <v>1.666666666666667</v>
+      </c>
+    </row>
+    <row r="558" spans="1:1">
+      <c r="A558">
+        <v>1.049629629629629</v>
+      </c>
+    </row>
+    <row r="559" spans="1:1">
+      <c r="A559">
+        <v>0.9364705882352941</v>
+      </c>
+    </row>
+    <row r="560" spans="1:1">
+      <c r="A560">
+        <v>1.077333333333333</v>
+      </c>
+    </row>
+    <row r="561" spans="1:1">
+      <c r="A561">
+        <v>1.000666666666667</v>
+      </c>
+    </row>
+    <row r="562" spans="1:1">
+      <c r="A562">
+        <v>1.035555555555556</v>
+      </c>
+    </row>
+    <row r="563" spans="1:1">
+      <c r="A563">
+        <v>3.491764705882353</v>
+      </c>
+    </row>
+    <row r="564" spans="1:1">
+      <c r="A564">
+        <v>1.2515</v>
+      </c>
+    </row>
+    <row r="565" spans="1:1">
+      <c r="A565">
+        <v>1.3</v>
+      </c>
+    </row>
+    <row r="566" spans="1:1">
+      <c r="A566">
+        <v>1.51135</v>
+      </c>
+    </row>
+    <row r="567" spans="1:1">
+      <c r="A567">
+        <v>2.133333333333333</v>
+      </c>
+    </row>
+    <row r="568" spans="1:1">
+      <c r="A568">
+        <v>0.87</v>
+      </c>
+    </row>
+    <row r="569" spans="1:1">
+      <c r="A569">
+        <v>0.97345</v>
+      </c>
+    </row>
+    <row r="570" spans="1:1">
+      <c r="A570">
+        <v>1.115925</v>
+      </c>
+    </row>
+    <row r="571" spans="1:1">
+      <c r="A571">
+        <v>0.8</v>
+      </c>
+    </row>
+    <row r="572" spans="1:1">
+      <c r="A572">
+        <v>1.130925</v>
+      </c>
+    </row>
+    <row r="573" spans="1:1">
+      <c r="A573">
+        <v>1.142996108949417</v>
+      </c>
+    </row>
+    <row r="574" spans="1:1">
+      <c r="A574">
+        <v>1.05225</v>
+      </c>
+    </row>
+    <row r="575" spans="1:1">
+      <c r="A575">
+        <v>0.5683</v>
+      </c>
+    </row>
+    <row r="576" spans="1:1">
+      <c r="A576">
+        <v>1.134</v>
+      </c>
+    </row>
+    <row r="577" spans="1:1">
+      <c r="A577">
+        <v>1.0655</v>
+      </c>
+    </row>
+    <row r="578" spans="1:1">
+      <c r="A578">
+        <v>0.8033</v>
+      </c>
+    </row>
+    <row r="579" spans="1:1">
+      <c r="A579">
+        <v>1.2154</v>
+      </c>
+    </row>
+    <row r="580" spans="1:1">
+      <c r="A580">
+        <v>1.0875</v>
+      </c>
+    </row>
+    <row r="581" spans="1:1">
+      <c r="A581">
+        <v>0.9564</v>
+      </c>
+    </row>
+    <row r="582" spans="1:1">
+      <c r="A582">
+        <v>1.100917431192661</v>
+      </c>
+    </row>
+    <row r="583" spans="1:1">
+      <c r="A583">
+        <v>0.997</v>
+      </c>
+    </row>
+    <row r="584" spans="1:1">
+      <c r="A584">
+        <v>0.9913</v>
+      </c>
+    </row>
+    <row r="585" spans="1:1">
+      <c r="A585">
+        <v>0.9986</v>
+      </c>
+    </row>
+    <row r="586" spans="1:1">
+      <c r="A586">
+        <v>9.165000000000001</v>
+      </c>
+    </row>
+    <row r="587" spans="1:1">
+      <c r="A587">
+        <v>1.145833333333333</v>
+      </c>
+    </row>
+    <row r="588" spans="1:1">
+      <c r="A588">
+        <v>1.001761363636364</v>
+      </c>
+    </row>
+    <row r="589" spans="1:1">
+      <c r="A589">
+        <v>2.943</v>
+      </c>
+    </row>
+    <row r="590" spans="1:1">
+      <c r="A590">
+        <v>1.093662217185824</v>
+      </c>
+    </row>
+    <row r="591" spans="1:1">
+      <c r="A591">
+        <v>0.9082402811130974</v>
+      </c>
+    </row>
+    <row r="592" spans="1:1">
+      <c r="A592">
+        <v>0.9739999999999999</v>
+      </c>
+    </row>
+    <row r="593" spans="1:1">
+      <c r="A593">
+        <v>0.9625</v>
+      </c>
+    </row>
+    <row r="594" spans="1:1">
+      <c r="A594">
+        <v>0.7875</v>
+      </c>
+    </row>
+    <row r="595" spans="1:1">
+      <c r="A595">
+        <v>0.8375</v>
+      </c>
+    </row>
+    <row r="596" spans="1:1">
+      <c r="A596">
+        <v>1.15625</v>
+      </c>
+    </row>
+    <row r="597" spans="1:1">
+      <c r="A597">
+        <v>1.081444444444444</v>
+      </c>
+    </row>
+    <row r="598" spans="1:1">
+      <c r="A598">
+        <v>0.9841428571428571</v>
+      </c>
+    </row>
+    <row r="599" spans="1:1">
+      <c r="A599">
+        <v>1.375</v>
+      </c>
+    </row>
+    <row r="600" spans="1:1">
+      <c r="A600">
+        <v>2.8129</v>
+      </c>
+    </row>
+    <row r="601" spans="1:1">
+      <c r="A601">
+        <v>1.02725</v>
+      </c>
+    </row>
+    <row r="602" spans="1:1">
+      <c r="A602">
+        <v>1.016842105263158</v>
+      </c>
+    </row>
+    <row r="603" spans="1:1">
+      <c r="A603">
+        <v>1.634222222222222</v>
+      </c>
+    </row>
+    <row r="604" spans="1:1">
+      <c r="A604">
+        <v>0.8820618556701031</v>
+      </c>
+    </row>
+    <row r="605" spans="1:1">
+      <c r="A605">
+        <v>1.043777777777778</v>
+      </c>
+    </row>
+    <row r="606" spans="1:1">
+      <c r="A606">
+        <v>1.33965</v>
+      </c>
+    </row>
+    <row r="607" spans="1:1">
+      <c r="A607">
+        <v>1.5142</v>
+      </c>
+    </row>
+    <row r="608" spans="1:1">
+      <c r="A608">
+        <v>1.3431</v>
+      </c>
+    </row>
+    <row r="609" spans="1:1">
+      <c r="A609">
+        <v>1.7115</v>
+      </c>
+    </row>
+    <row r="610" spans="1:1">
+      <c r="A610">
+        <v>1.8504</v>
+      </c>
+    </row>
+    <row r="611" spans="1:1">
+      <c r="A611">
+        <v>0.9892307692307691</v>
+      </c>
+    </row>
+    <row r="612" spans="1:1">
+      <c r="A612">
+        <v>0.9583333333333333</v>
+      </c>
+    </row>
+    <row r="613" spans="1:1">
+      <c r="A613">
+        <v>1.006340206185567</v>
+      </c>
+    </row>
+    <row r="614" spans="1:1">
+      <c r="A614">
+        <v>1.7475</v>
+      </c>
+    </row>
+    <row r="615" spans="1:1">
+      <c r="A615">
+        <v>2.0625</v>
+      </c>
+    </row>
+    <row r="616" spans="1:1">
+      <c r="A616">
+        <v>1.1338</v>
+      </c>
+    </row>
+    <row r="617" spans="1:1">
+      <c r="A617">
+        <v>1.19375</v>
+      </c>
+    </row>
+    <row r="618" spans="1:1">
+      <c r="A618">
+        <v>1.625</v>
+      </c>
+    </row>
+    <row r="619" spans="1:1">
+      <c r="A619">
+        <v>1.096947368421053</v>
+      </c>
+    </row>
+    <row r="620" spans="1:1">
+      <c r="A620">
+        <v>0.7692307692307692</v>
+      </c>
+    </row>
+    <row r="621" spans="1:1">
+      <c r="A621">
+        <v>1.152200012207031</v>
+      </c>
+    </row>
+    <row r="622" spans="1:1">
+      <c r="A622">
+        <v>1.129400024414062</v>
+      </c>
+    </row>
+    <row r="623" spans="1:1">
+      <c r="A623">
+        <v>1.106100006103516</v>
+      </c>
+    </row>
+    <row r="624" spans="1:1">
+      <c r="A624">
+        <v>1.104300003051758</v>
+      </c>
+    </row>
+    <row r="625" spans="1:1">
+      <c r="A625">
+        <v>1.033499984741211</v>
+      </c>
+    </row>
+    <row r="626" spans="1:1">
+      <c r="A626">
+        <v>1.03379997253418</v>
+      </c>
+    </row>
+    <row r="627" spans="1:1">
+      <c r="A627">
+        <v>1.006500015258789</v>
+      </c>
+    </row>
+    <row r="628" spans="1:1">
+      <c r="A628">
+        <v>0.9988999938964844</v>
+      </c>
+    </row>
+    <row r="629" spans="1:1">
+      <c r="A629">
+        <v>0.9608999633789063</v>
+      </c>
+    </row>
+    <row r="630" spans="1:1">
+      <c r="A630">
+        <v>1.009700012207031</v>
+      </c>
+    </row>
+    <row r="631" spans="1:1">
+      <c r="A631">
+        <v>1.016699981689453</v>
+      </c>
+    </row>
+    <row r="632" spans="1:1">
+      <c r="A632">
+        <v>1.060899963378906</v>
+      </c>
+    </row>
+    <row r="633" spans="1:1">
+      <c r="A633">
+        <v>1.033899993896484</v>
+      </c>
+    </row>
+    <row r="634" spans="1:1">
+      <c r="A634">
+        <v>1.3675</v>
+      </c>
+    </row>
+    <row r="635" spans="1:1">
+      <c r="A635">
+        <v>1.110899963378906</v>
+      </c>
+    </row>
+    <row r="636" spans="1:1">
+      <c r="A636">
+        <v>1.192300033569336</v>
+      </c>
+    </row>
+    <row r="637" spans="1:1">
+      <c r="A637">
+        <v>0.95</v>
+      </c>
+    </row>
+    <row r="638" spans="1:1">
+      <c r="A638">
+        <v>0.97</v>
+      </c>
+    </row>
+    <row r="639" spans="1:1">
+      <c r="A639">
+        <v>0.9875</v>
+      </c>
+    </row>
+    <row r="640" spans="1:1">
+      <c r="A640">
+        <v>0.9817</v>
+      </c>
+    </row>
+    <row r="641" spans="1:1">
+      <c r="A641">
+        <v>0.9937999999999999</v>
+      </c>
+    </row>
+    <row r="642" spans="1:1">
+      <c r="A642">
+        <v>0.9286</v>
+      </c>
+    </row>
+    <row r="643" spans="1:1">
+      <c r="A643">
+        <v>0.9917</v>
+      </c>
+    </row>
+    <row r="644" spans="1:1">
+      <c r="A644">
+        <v>0.9975000000000001</v>
+      </c>
+    </row>
+    <row r="645" spans="1:1">
+      <c r="A645">
+        <v>0.9740000000000001</v>
+      </c>
+    </row>
+    <row r="646" spans="1:1">
+      <c r="A646">
+        <v>0.9112</v>
+      </c>
+    </row>
+    <row r="647" spans="1:1">
+      <c r="A647">
+        <v>0.9451000000000001</v>
+      </c>
+    </row>
+    <row r="648" spans="1:1">
+      <c r="A648">
+        <v>0.8643000000000001</v>
+      </c>
+    </row>
+    <row r="649" spans="1:1">
+      <c r="A649">
+        <v>0.9399999999999999</v>
+      </c>
+    </row>
+    <row r="650" spans="1:1">
+      <c r="A650">
+        <v>0.946</v>
+      </c>
+    </row>
+    <row r="651" spans="1:1">
+      <c r="A651">
+        <v>0.8432999999999999</v>
+      </c>
+    </row>
+    <row r="652" spans="1:1">
+      <c r="A652">
+        <v>0.9159999999999999</v>
+      </c>
+    </row>
+    <row r="653" spans="1:1">
+      <c r="A653">
+        <v>0.84</v>
+      </c>
+    </row>
+    <row r="654" spans="1:1">
+      <c r="A654">
+        <v>0.9</v>
+      </c>
+    </row>
+    <row r="655" spans="1:1">
+      <c r="A655">
+        <v>0.9925</v>
+      </c>
+    </row>
+    <row r="656" spans="1:1">
+      <c r="A656">
+        <v>0.9151000213623047</v>
+      </c>
+    </row>
+    <row r="657" spans="1:1">
+      <c r="A657">
+        <v>0.8667</v>
+      </c>
+    </row>
+    <row r="658" spans="1:1">
+      <c r="A658">
+        <v>0.8895999999999999</v>
+      </c>
+    </row>
+    <row r="659" spans="1:1">
+      <c r="A659">
+        <v>0.9375</v>
+      </c>
+    </row>
+    <row r="660" spans="1:1">
+      <c r="A660">
+        <v>0.9417</v>
+      </c>
+    </row>
+    <row r="661" spans="1:1">
+      <c r="A661">
+        <v>0.9095</v>
+      </c>
+    </row>
+    <row r="662" spans="1:1">
+      <c r="A662">
+        <v>0.9773999999999999</v>
+      </c>
+    </row>
+    <row r="663" spans="1:1">
+      <c r="A663">
+        <v>0.8625</v>
+      </c>
+    </row>
+    <row r="664" spans="1:1">
+      <c r="A664">
+        <v>0.93</v>
+      </c>
+    </row>
+    <row r="665" spans="1:1">
+      <c r="A665">
+        <v>0.7368421052631579</v>
+      </c>
+    </row>
+    <row r="666" spans="1:1">
+      <c r="A666">
+        <v>0.8780487804878049</v>
+      </c>
+    </row>
+    <row r="667" spans="1:1">
+      <c r="A667">
+        <v>0.9795918367346939</v>
+      </c>
+    </row>
+    <row r="668" spans="1:1">
+      <c r="A668">
+        <v>0.987012987012987</v>
+      </c>
+    </row>
+    <row r="669" spans="1:1">
+      <c r="A669">
+        <v>0.9890109890109891</v>
+      </c>
+    </row>
+    <row r="670" spans="1:1">
+      <c r="A670">
+        <v>0.9333333333333333</v>
+      </c>
+    </row>
+    <row r="671" spans="1:1">
+      <c r="A671">
+        <v>0.9468085106382979</v>
+      </c>
+    </row>
+    <row r="672" spans="1:1">
+      <c r="A672">
+        <v>0.9690721649484536</v>
+      </c>
+    </row>
+    <row r="673" spans="1:1">
+      <c r="A673">
+        <v>0.9666666666666667</v>
+      </c>
+    </row>
+    <row r="674" spans="1:1">
+      <c r="A674">
+        <v>0.9897959183673469</v>
+      </c>
+    </row>
+    <row r="675" spans="1:1">
+      <c r="A675">
+        <v>0.9487179487179487</v>
+      </c>
+    </row>
+    <row r="676" spans="1:1">
+      <c r="A676">
+        <v>0.9473684210526315</v>
+      </c>
+    </row>
+    <row r="677" spans="1:1">
+      <c r="A677">
+        <v>0.9693877551020408</v>
+      </c>
+    </row>
+    <row r="678" spans="1:1">
+      <c r="A678">
+        <v>0.8571428571428571</v>
       </c>
     </row>
   </sheetData>
@@ -4442,82 +11506,87 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A15"/>
+  <dimension ref="A1:A17"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" t="s">
-        <v>419</v>
+        <v>556</v>
       </c>
     </row>
     <row r="2" spans="1:1">
       <c r="A2" t="s">
-        <v>420</v>
+        <v>557</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" t="s">
-        <v>421</v>
+        <v>558</v>
       </c>
     </row>
     <row r="4" spans="1:1">
       <c r="A4" t="s">
-        <v>422</v>
+        <v>559</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>423</v>
+        <v>560</v>
       </c>
     </row>
     <row r="6" spans="1:1">
       <c r="A6" t="s">
-        <v>424</v>
+        <v>561</v>
       </c>
     </row>
     <row r="7" spans="1:1">
       <c r="A7" t="s">
-        <v>425</v>
+        <v>562</v>
       </c>
     </row>
     <row r="8" spans="1:1">
       <c r="A8" t="s">
-        <v>426</v>
+        <v>563</v>
       </c>
     </row>
     <row r="9" spans="1:1">
       <c r="A9" t="s">
-        <v>427</v>
+        <v>564</v>
       </c>
     </row>
     <row r="10" spans="1:1">
       <c r="A10" t="s">
-        <v>428</v>
+        <v>565</v>
       </c>
     </row>
     <row r="11" spans="1:1">
       <c r="A11" t="s">
-        <v>429</v>
+        <v>566</v>
       </c>
     </row>
     <row r="12" spans="1:1">
       <c r="A12" t="s">
-        <v>430</v>
+        <v>567</v>
       </c>
     </row>
     <row r="13" spans="1:1">
-      <c r="A13" t="s">
-        <v>431</v>
+      <c r="A13">
+        <v>0</v>
       </c>
     </row>
     <row r="14" spans="1:1">
       <c r="A14" t="s">
-        <v>432</v>
+        <v>568</v>
       </c>
     </row>
     <row r="15" spans="1:1">
-      <c r="A15">
-        <v>0</v>
+      <c r="A15" t="s">
+        <v>569</v>
+      </c>
+    </row>
+    <row r="17" spans="1:1">
+      <c r="A17" t="s">
+        <v>570</v>
       </c>
     </row>
   </sheetData>
@@ -4532,7 +11601,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" t="s">
-        <v>433</v>
+        <v>571</v>
       </c>
     </row>
     <row r="2" spans="1:1">
